--- a/Data/Results/Visualizations/INTERCITY/Route_Wise/Pondicherry_to_Chennai/Average/Master_Results.xlsx
+++ b/Data/Results/Visualizations/INTERCITY/Route_Wise/Pondicherry_to_Chennai/Average/Master_Results.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Phase_Difference_Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Descriptive_Statistics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Route_Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Plot_Audit" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,296 +430,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>pair_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>pair_number</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pair_class</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>operation_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>workbook_path</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ev_tat_min</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ice_tat_min</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ev_distance_km</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ice_distance_km</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ev_moving_speed_kmh</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ice_moving_speed_kmh</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tat_min_diff</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>distance_km_diff</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>moving_speed_kmh_diff</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>stationary_time_min_diff</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ev_charging_refueling_time_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ice_charging_refueling_time_min</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>charging_refueling_time_diff_min</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ev_charging_refueling_distance_km</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ice_charging_refueling_distance_km</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>charging_refueling_distance_diff_km</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ev_stop_time_min</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ice_stop_time_min</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>stop_time_diff_min</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ev_stop_distance_km</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ice_stop_distance_km</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stop_distance_diff_km</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ev_idle_time_min</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ice_idle_time_min</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>idle_time_diff_min</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ev_idle_distance_km</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ice_idle_distance_km</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>idle_distance_diff_km</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ev_inch_time_min</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ice_inch_time_min</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>inch_time_diff_min</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ev_inch_distance_km</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>ice_inch_distance_km</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>inch_distance_diff_km</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>ev_acc_time_min</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ice_acc_time_min</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>acc_time_diff_min</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>ev_acc_distance_km</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ice_acc_distance_km</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>acc_distance_diff_km</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>ev_dec_time_min</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>ice_dec_time_min</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dec_time_diff_min</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>ev_dec_distance_km</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>ice_dec_distance_km</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dec_distance_diff_km</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>ev_cruise_time_min</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>ice_cruise_time_min</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>cruise_time_diff_min</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>ev_cruise_distance_km</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>ice_cruise_distance_km</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>cruise_distance_diff_km</t>
         </is>
@@ -715,11 +728,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_006</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -738,7 +751,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_006_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_010_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -754,10 +767,10 @@
         <v>143.7061031155876</v>
       </c>
       <c r="K2" t="n">
-        <v>43.15630919960726</v>
+        <v>44.63387255371435</v>
       </c>
       <c r="L2" t="n">
-        <v>42.008597388821</v>
+        <v>42.34188357413701</v>
       </c>
       <c r="M2" t="n">
         <v>-0.2421166666667034</v>
@@ -766,64 +779,64 @@
         <v>-0.02777565792860059</v>
       </c>
       <c r="O2" t="n">
-        <v>1.147711810786255</v>
+        <v>2.29198897957734</v>
       </c>
       <c r="P2" t="n">
-        <v>29.43553333333333</v>
+        <v>9.552200000000013</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>42.53553333333333</v>
+        <v>43.48553333333334</v>
       </c>
       <c r="X2" t="n">
-        <v>13.1</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>29.43553333333333</v>
+        <v>6.502200000000016</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6596733987548126</v>
+        <v>1.332101358262426</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3335967503409809</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3260766484138317</v>
+        <v>0.8980233192540306</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.7541054091629448</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.038955216433607</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-1.284849807270662</v>
       </c>
       <c r="AI2" t="n">
         <v>4.1</v>
@@ -847,65 +860,65 @@
         <v>52.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>43.73333333333333</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.766666666666673</v>
+        <v>10.06666666666667</v>
       </c>
       <c r="AR2" t="n">
         <v>42.76805623685773</v>
       </c>
       <c r="AS2" t="n">
-        <v>31.25618145550666</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.51187478135107</v>
+        <v>12.17007709217261</v>
       </c>
       <c r="AU2" t="n">
-        <v>38.05478333333333</v>
+        <v>37.47145</v>
       </c>
       <c r="AV2" t="n">
         <v>34.95</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.10478333333333</v>
+        <v>2.521449999999994</v>
       </c>
       <c r="AX2" t="n">
-        <v>30.13874197108473</v>
+        <v>29.77502417243205</v>
       </c>
       <c r="AY2" t="n">
         <v>25.11354425718663</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.025197713898102</v>
+        <v>4.661479915245422</v>
       </c>
       <c r="BA2" t="n">
-        <v>104.1833333333333</v>
+        <v>96.26666666666667</v>
       </c>
       <c r="BB2" t="n">
-        <v>124.3324333333333</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="BC2" t="n">
-        <v>-20.1491</v>
+        <v>-24.86576666666663</v>
       </c>
       <c r="BD2" t="n">
-        <v>69.67242471935344</v>
+        <v>68.60960914933557</v>
       </c>
       <c r="BE2" t="n">
-        <v>86.63218730858281</v>
+        <v>85.25143440297076</v>
       </c>
       <c r="BF2" t="n">
-        <v>-16.95976258922937</v>
+        <v>-16.64182525363519</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_007</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,7 +937,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_007_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_011_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -940,10 +953,10 @@
         <v>126.4504264596244</v>
       </c>
       <c r="K3" t="n">
-        <v>51.80910898442515</v>
+        <v>51.96681218238075</v>
       </c>
       <c r="L3" t="n">
-        <v>46.12090225545156</v>
+        <v>46.52364975832732</v>
       </c>
       <c r="M3" t="n">
         <v>-16.52128333333329</v>
@@ -952,146 +965,146 @@
         <v>0.05284572164660517</v>
       </c>
       <c r="O3" t="n">
-        <v>5.68820672897359</v>
+        <v>5.443162424053426</v>
       </c>
       <c r="P3" t="n">
-        <v>25.41886666666667</v>
+        <v>0.9188666666666663</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>26.36886666666667</v>
+      </c>
+      <c r="X3" t="n">
         <v>23.71666666666667</v>
       </c>
-      <c r="S3" t="n">
-        <v>-23.71666666666667</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="Y3" t="n">
+        <v>2.652200000000001</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.9969610105345994</v>
+      </c>
+      <c r="AA3" t="n">
         <v>0.1169990422600451</v>
       </c>
-      <c r="V3" t="n">
-        <v>-0.1169990422600451</v>
-      </c>
-      <c r="W3" t="n">
-        <v>25.41886666666667</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>25.41886666666667</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.3245330510269857</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
       <c r="AB3" t="n">
-        <v>0.3245330510269857</v>
+        <v>0.8799619682745543</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-1.733333333333333</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.3292747005187303</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.7448250731105075</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.4155503725917772</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2.3</v>
+        <v>-1.3</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.2122753364088935</v>
+        <v>0.1079082363261396</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.2122753364088935</v>
+        <v>-0.1079082363261396</v>
       </c>
       <c r="AO3" t="n">
         <v>43.56666666666667</v>
       </c>
       <c r="AP3" t="n">
-        <v>45.5</v>
+        <v>45.08333333333334</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.93333333333333</v>
+        <v>-1.516666666666673</v>
       </c>
       <c r="AR3" t="n">
         <v>38.51537746372311</v>
       </c>
       <c r="AS3" t="n">
-        <v>34.12509917533455</v>
+        <v>33.88390179261686</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.390278288388565</v>
+        <v>4.631475671106251</v>
       </c>
       <c r="AU3" t="n">
-        <v>32.13333333333333</v>
+        <v>31.55</v>
       </c>
       <c r="AV3" t="n">
         <v>29.80076666666667</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.332566666666661</v>
+        <v>1.749233333333329</v>
       </c>
       <c r="AX3" t="n">
-        <v>27.33010874041363</v>
+        <v>26.96639094176094</v>
       </c>
       <c r="AY3" t="n">
         <v>22.73451919053936</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.595589549874269</v>
+        <v>4.231871751221583</v>
       </c>
       <c r="BA3" t="n">
-        <v>70.42728333333334</v>
+        <v>69.41061666666666</v>
       </c>
       <c r="BB3" t="n">
-        <v>86.75</v>
+        <v>85.78333333333333</v>
       </c>
       <c r="BC3" t="n">
-        <v>-16.32271666666666</v>
+        <v>-16.37271666666668</v>
       </c>
       <c r="BD3" t="n">
-        <v>60.33325292610726</v>
+        <v>59.6952680647336</v>
       </c>
       <c r="BE3" t="n">
-        <v>69.26153371508154</v>
+        <v>68.86227312477148</v>
       </c>
       <c r="BF3" t="n">
-        <v>-8.928280788974284</v>
+        <v>-9.16700506003788</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_008</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1110,7 +1123,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_008_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1126,10 +1139,10 @@
         <v>126.5641866441461</v>
       </c>
       <c r="K4" t="n">
-        <v>46.70774678068461</v>
+        <v>48.84353918109128</v>
       </c>
       <c r="L4" t="n">
-        <v>49.76956595619203</v>
+        <v>49.97551623726486</v>
       </c>
       <c r="M4" t="n">
         <v>3.589966666666697</v>
@@ -1138,64 +1151,64 @@
         <v>0.04042040413020231</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.061819175507424</v>
+        <v>-1.131977056173582</v>
       </c>
       <c r="P4" t="n">
-        <v>17.46666666666666</v>
+        <v>-0.6631</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>21.48333333333333</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1</v>
+        <v>27.98333333333333</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.38333333333333</v>
+        <v>-6.5</v>
       </c>
       <c r="Z4" t="n">
         <v>0.237667416199215</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1135008893025534</v>
+        <v>0.2139821779699679</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1241665268966616</v>
+        <v>0.02368523822924709</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.08333333333333333</v>
+        <v>8.303566666666667</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.08333333333333333</v>
+        <v>5.8369</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.9134082250757436</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.531702164179549</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0.6182939391038054</v>
       </c>
       <c r="AI4" t="n">
         <v>1.683333333333333</v>
@@ -1219,65 +1232,65 @@
         <v>48.81666666666667</v>
       </c>
       <c r="AP4" t="n">
-        <v>35.28333333333333</v>
+        <v>34.15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.53333333333334</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="AR4" t="n">
         <v>38.82861695950649</v>
       </c>
       <c r="AS4" t="n">
-        <v>26.65829138970381</v>
+        <v>26.10973756311647</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.17032556980268</v>
+        <v>12.71887939639002</v>
       </c>
       <c r="AU4" t="n">
-        <v>35.46666666666667</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="AV4" t="n">
         <v>27.01666666666667</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.449999999999999</v>
+        <v>8.116666666666664</v>
       </c>
       <c r="AX4" t="n">
-        <v>27.95827681357427</v>
+        <v>27.71428406489335</v>
       </c>
       <c r="AY4" t="n">
         <v>21.58020657782552</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.378070235748748</v>
+        <v>6.134077487067827</v>
       </c>
       <c r="BA4" t="n">
-        <v>76.36221666666667</v>
+        <v>68.47531666666667</v>
       </c>
       <c r="BB4" t="n">
-        <v>89.67225000000001</v>
+        <v>88.33891666666666</v>
       </c>
       <c r="BC4" t="n">
-        <v>-13.31003333333334</v>
+        <v>-19.86359999999999</v>
       </c>
       <c r="BD4" t="n">
-        <v>59.27885788112761</v>
+        <v>58.60944240473279</v>
       </c>
       <c r="BE4" t="n">
-        <v>77.94451962578719</v>
+        <v>76.961371288195</v>
       </c>
       <c r="BF4" t="n">
-        <v>-18.66566174465959</v>
+        <v>-18.35192888346221</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_009</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1296,7 +1309,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_009_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1312,10 +1325,10 @@
         <v>123.941936072907</v>
       </c>
       <c r="K5" t="n">
-        <v>43.25878919401418</v>
+        <v>44.92387297676966</v>
       </c>
       <c r="L5" t="n">
-        <v>42.80552488152868</v>
+        <v>42.76203218085404</v>
       </c>
       <c r="M5" t="n">
         <v>10.79548333333329</v>
@@ -1324,64 +1337,64 @@
         <v>-0.02334038713590303</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4532643124854943</v>
+        <v>2.161840795915616</v>
       </c>
       <c r="P5" t="n">
-        <v>34.55</v>
+        <v>20.1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="X5" t="n">
         <v>21.38333333333333</v>
       </c>
-      <c r="S5" t="n">
-        <v>-21.38333333333333</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="Y5" t="n">
+        <v>14.11666666666667</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.156478673390982</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0.1090721560237224</v>
       </c>
-      <c r="V5" t="n">
-        <v>-0.1090721560237224</v>
-      </c>
-      <c r="W5" t="n">
-        <v>34.55</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>34.55</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.4840507138833688</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
       <c r="AB5" t="n">
-        <v>0.4840507138833688</v>
+        <v>1.04740651736726</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.983333333333333</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>5.983333333333333</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.5163595282581407</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.8385213433327759</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0.3221618150746353</v>
       </c>
       <c r="AI5" t="n">
         <v>4.1</v>
@@ -1405,65 +1418,65 @@
         <v>44.28333333333333</v>
       </c>
       <c r="AP5" t="n">
-        <v>39.51666666666667</v>
+        <v>39.18333333333333</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.766666666666659</v>
+        <v>5.100000000000001</v>
       </c>
       <c r="AR5" t="n">
         <v>35.86032280254005</v>
       </c>
       <c r="AS5" t="n">
-        <v>28.52077529734963</v>
+        <v>28.21320161975721</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.339547505190417</v>
+        <v>7.647121182782836</v>
       </c>
       <c r="AU5" t="n">
-        <v>31.8</v>
+        <v>31.21666666666667</v>
       </c>
       <c r="AV5" t="n">
-        <v>30.8</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AX5" t="n">
-        <v>25.29976226838916</v>
+        <v>24.93604446973648</v>
       </c>
       <c r="AY5" t="n">
-        <v>21.13389550628888</v>
+        <v>20.93633895165053</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.165866762100279</v>
+        <v>3.99970551808595</v>
       </c>
       <c r="BA5" t="n">
-        <v>91.02055</v>
+        <v>83.67055000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>103.2584</v>
+        <v>102.9250666666667</v>
       </c>
       <c r="BC5" t="n">
-        <v>-12.23784999999999</v>
+        <v>-19.25451666666669</v>
       </c>
       <c r="BD5" t="n">
-        <v>61.83502876935029</v>
+        <v>61.00995908023722</v>
       </c>
       <c r="BE5" t="n">
-        <v>74.17819311324479</v>
+        <v>73.8448020021428</v>
       </c>
       <c r="BF5" t="n">
-        <v>-12.3431643438945</v>
+        <v>-12.83484292190558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1482,7 +1495,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_010_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1498,10 +1511,10 @@
         <v>143.7030109884508</v>
       </c>
       <c r="K6" t="n">
-        <v>45.56809333466344</v>
+        <v>46.2946098216972</v>
       </c>
       <c r="L6" t="n">
-        <v>42.0076907503904</v>
+        <v>42.3414520907443</v>
       </c>
       <c r="M6" t="n">
         <v>-18.57378333333341</v>
@@ -1510,64 +1523,64 @@
         <v>0.01254862469119189</v>
       </c>
       <c r="O6" t="n">
-        <v>3.560402584273035</v>
+        <v>3.953157730952903</v>
       </c>
       <c r="P6" t="n">
-        <v>21.39703333333333</v>
+        <v>-3.30296666666667</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>34.49703333333333</v>
       </c>
       <c r="X6" t="n">
-        <v>13.1</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>21.39703333333333</v>
+        <v>-2.4863</v>
       </c>
       <c r="Z6" t="n">
         <v>0.521661623484558</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3335967503409809</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1880648731435771</v>
+        <v>0.0875835844761626</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.683333333333333</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-0.8166666666666669</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.5589577464659954</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.037302319652247</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-1.478344573186251</v>
       </c>
       <c r="AI6" t="n">
         <v>5.266666666666667</v>
@@ -1591,69 +1604,69 @@
         <v>54.2</v>
       </c>
       <c r="AP6" t="n">
-        <v>43.73333333333333</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.46666666666668</v>
+        <v>11.76666666666667</v>
       </c>
       <c r="AR6" t="n">
         <v>43.32090510862054</v>
       </c>
       <c r="AS6" t="n">
-        <v>31.2545285587253</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AT6" t="n">
-        <v>12.06637654989524</v>
+        <v>12.72292596393542</v>
       </c>
       <c r="AU6" t="n">
-        <v>35.34495</v>
+        <v>34.92828333333333</v>
       </c>
       <c r="AV6" t="n">
         <v>34.95</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.3949499999999944</v>
+        <v>-0.02171666666666994</v>
       </c>
       <c r="AX6" t="n">
-        <v>28.54498304892895</v>
+        <v>28.28601681705657</v>
       </c>
       <c r="AY6" t="n">
         <v>25.11354425718663</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.431438791742323</v>
+        <v>3.172472559869941</v>
       </c>
       <c r="BA6" t="n">
-        <v>93.73333333333333</v>
+        <v>90.46666666666667</v>
       </c>
       <c r="BB6" t="n">
-        <v>124.3324333333333</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="BC6" t="n">
-        <v>-30.59909999999996</v>
+        <v>-30.66576666666663</v>
       </c>
       <c r="BD6" t="n">
-        <v>70.9731865628885</v>
+        <v>70.67319504829489</v>
       </c>
       <c r="BE6" t="n">
-        <v>86.63074807822738</v>
+        <v>85.24999517261531</v>
       </c>
       <c r="BF6" t="n">
-        <v>-15.65756151533888</v>
+        <v>-14.57680012432043</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1668,178 +1681,178 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_014_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>184.8726166666667</v>
+        <v>72.03223333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>189.8237333333333</v>
+        <v>78.34408333333334</v>
       </c>
       <c r="I7" t="n">
-        <v>126.797111280885</v>
+        <v>44.14952488525887</v>
       </c>
       <c r="J7" t="n">
-        <v>126.7676219192398</v>
+        <v>44.09816148211158</v>
       </c>
       <c r="K7" t="n">
-        <v>46.49901997986691</v>
+        <v>49.19356496670422</v>
       </c>
       <c r="L7" t="n">
-        <v>45.74782714011837</v>
+        <v>48.98583197131639</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.951116666666621</v>
+        <v>-6.311850000000007</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02948936164520433</v>
+        <v>0.05136340314729182</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7511928397485406</v>
+        <v>0.2077329953878362</v>
       </c>
       <c r="P7" t="n">
-        <v>21.56666666666666</v>
+        <v>-7.033333333333328</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>21.48333333333333</v>
+        <v>14.45</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>23.88333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>21.48333333333333</v>
+        <v>-9.43333333333333</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.237667416199215</v>
+        <v>0.1157287174312111</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.1004812886674145</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.237667416199215</v>
+        <v>0.0152474287637966</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.08333333333333333</v>
+        <v>4.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.08333333333333333</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>0.1431061962259462</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>0.8813714304575493</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0.7382652342316031</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.683333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.633333333333333</v>
+        <v>0.35</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.95</v>
+        <v>0.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.3011879778687425</v>
+        <v>0.04717006116255434</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.2267712765180789</v>
+        <v>0.1671868728596241</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.07441670135066361</v>
+        <v>-0.1200168116970698</v>
       </c>
       <c r="AO7" t="n">
-        <v>48.91905</v>
+        <v>19.35811666666667</v>
       </c>
       <c r="AP7" t="n">
-        <v>45.67373333333333</v>
+        <v>11.07741666666667</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.245316666666668</v>
+        <v>8.280700000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>38.90083595250158</v>
+        <v>14.57763861092875</v>
       </c>
       <c r="AS7" t="n">
-        <v>34.23732716182031</v>
+        <v>8.407639114756291</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.66350879068127</v>
+        <v>6.169999496172458</v>
       </c>
       <c r="AU7" t="n">
-        <v>35.46666666666667</v>
+        <v>13.61666666666667</v>
       </c>
       <c r="AV7" t="n">
-        <v>29.9</v>
+        <v>9.266666666666667</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.56666666666667</v>
+        <v>4.350000000000003</v>
       </c>
       <c r="AX7" t="n">
-        <v>27.95827681357427</v>
+        <v>10.50996594053165</v>
       </c>
       <c r="AY7" t="n">
-        <v>22.79241179514765</v>
+        <v>7.155594247738707</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.165865018426619</v>
+        <v>3.354371692792943</v>
       </c>
       <c r="BA7" t="n">
-        <v>77.23690000000001</v>
+        <v>19.60745</v>
       </c>
       <c r="BB7" t="n">
-        <v>87.90000000000001</v>
+        <v>32.11666666666667</v>
       </c>
       <c r="BC7" t="n">
-        <v>-10.6631</v>
+        <v>-12.50921666666667</v>
       </c>
       <c r="BD7" t="n">
-        <v>59.39914312074116</v>
+        <v>18.75591535897876</v>
       </c>
       <c r="BE7" t="n">
-        <v>69.39411264349368</v>
+        <v>27.38588852763199</v>
       </c>
       <c r="BF7" t="n">
-        <v>-9.994969522752527</v>
+        <v>-8.62997316865323</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1854,174 +1867,174 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_020_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>139.3205333333333</v>
+        <v>184.8726166666667</v>
       </c>
       <c r="H8" t="n">
-        <v>149.51085</v>
+        <v>189.8237333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>106.7510397234517</v>
+        <v>126.797111280885</v>
       </c>
       <c r="J8" t="n">
-        <v>106.7303536725813</v>
+        <v>126.7676219192398</v>
       </c>
       <c r="K8" t="n">
-        <v>51.59099322590557</v>
+        <v>48.60919773277766</v>
       </c>
       <c r="L8" t="n">
-        <v>49.9289852595555</v>
+        <v>46.13403705248899</v>
       </c>
       <c r="M8" t="n">
-        <v>-10.19031666666672</v>
+        <v>-4.951116666666621</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02068605087039543</v>
+        <v>0.02948936164520433</v>
       </c>
       <c r="O8" t="n">
-        <v>1.662007966350068</v>
+        <v>2.475160680288667</v>
       </c>
       <c r="P8" t="n">
-        <v>15.3</v>
+        <v>3.686899999999994</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>15.21666666666667</v>
+        <v>21.48333333333333</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.21666666666667</v>
+        <v>-2.233333333333338</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1119981388984077</v>
+        <v>0.237667416199215</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1119981388984077</v>
+        <v>0.1206683739391699</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.08333333333333333</v>
+        <v>8.303566666666667</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.08333333333333333</v>
+        <v>5.920233333333334</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.9162394150268994</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.7633432107826125</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>0.152896204244287</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.35</v>
+        <v>1.683333333333333</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.633333333333333</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.1868101281681779</v>
+        <v>0.3011879778687425</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>0.122404176435325</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.1868101281681779</v>
+        <v>0.1787838014334175</v>
       </c>
       <c r="AO8" t="n">
-        <v>41.28333333333333</v>
+        <v>48.91905</v>
       </c>
       <c r="AP8" t="n">
-        <v>31.65</v>
+        <v>45.25706666666667</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.633333333333333</v>
+        <v>3.661983333333332</v>
       </c>
       <c r="AR8" t="n">
-        <v>33.31093548904284</v>
+        <v>38.90083595250158</v>
       </c>
       <c r="AS8" t="n">
-        <v>24.16360873509058</v>
+        <v>33.99612977910262</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.14732675395226</v>
+        <v>4.904706173398964</v>
       </c>
       <c r="AU8" t="n">
-        <v>29.13333333333333</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="AV8" t="n">
-        <v>23.28333333333333</v>
+        <v>29.9</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.849999999999998</v>
+        <v>5.233333333333334</v>
       </c>
       <c r="AX8" t="n">
-        <v>23.76335197186532</v>
+        <v>27.71428406489335</v>
       </c>
       <c r="AY8" t="n">
-        <v>17.08447986676835</v>
+        <v>22.79241179514765</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.678872105096968</v>
+        <v>4.921872269745698</v>
       </c>
       <c r="BA8" t="n">
-        <v>52.25386666666667</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>73.19418333333333</v>
+        <v>86.93333333333334</v>
       </c>
       <c r="BC8" t="n">
-        <v>-20.94031666666666</v>
+        <v>-17.58333333333334</v>
       </c>
       <c r="BD8" t="n">
-        <v>49.37794399547691</v>
+        <v>58.72689645439518</v>
       </c>
       <c r="BE8" t="n">
-        <v>65.37319291469859</v>
+        <v>68.97633391551152</v>
       </c>
       <c r="BF8" t="n">
-        <v>-15.99524891922168</v>
+        <v>-10.24943746111634</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2040,350 +2053,908 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_016_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_021_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>166.3452166666667</v>
+        <v>139.3205333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>188.0674333333333</v>
+        <v>149.51085</v>
       </c>
       <c r="I9" t="n">
-        <v>126.5111630773044</v>
+        <v>106.7510397234517</v>
       </c>
       <c r="J9" t="n">
-        <v>126.4609732010443</v>
+        <v>106.7303536725813</v>
       </c>
       <c r="K9" t="n">
-        <v>53.18742578062445</v>
+        <v>51.58938782842431</v>
       </c>
       <c r="L9" t="n">
-        <v>46.12475258422111</v>
+        <v>49.91426587048593</v>
       </c>
       <c r="M9" t="n">
-        <v>-21.72221666666661</v>
+        <v>-10.19031666666672</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05018987626010585</v>
+        <v>0.02068605087039543</v>
       </c>
       <c r="O9" t="n">
-        <v>7.062673196403338</v>
+        <v>1.67512195793838</v>
       </c>
       <c r="P9" t="n">
-        <v>23.84703333333334</v>
+        <v>-6.571449999999992</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>23.84703333333334</v>
+        <v>15.21666666666667</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="Y9" t="n">
-        <v>23.84703333333334</v>
+        <v>-6.166666666666659</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1926372453796382</v>
+        <v>0.1119981388984077</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1926372453796382</v>
+        <v>0.002925982874685304</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.42855</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>-0.4047833333333334</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.3001436458890005</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>0.724686338784539</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-0.4245426928955385</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-2.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>0.1868101281681779</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.2122753364088935</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.2122753364088935</v>
+        <v>0.1868101281681779</v>
       </c>
       <c r="AO9" t="n">
-        <v>44.66666666666666</v>
+        <v>41.28333333333333</v>
       </c>
       <c r="AP9" t="n">
-        <v>45.5</v>
+        <v>31.31666666666667</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.8333333333333428</v>
+        <v>9.966666666666661</v>
       </c>
       <c r="AR9" t="n">
-        <v>38.02172328104655</v>
+        <v>33.31093548904284</v>
       </c>
       <c r="AS9" t="n">
-        <v>34.12509917533455</v>
+        <v>23.85603505749816</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.896624105712</v>
+        <v>9.454900431544679</v>
       </c>
       <c r="AU9" t="n">
-        <v>28.4</v>
+        <v>28.96666666666667</v>
       </c>
       <c r="AV9" t="n">
-        <v>29.80076666666667</v>
+        <v>22.95</v>
       </c>
       <c r="AW9" t="n">
-        <v>-1.400766666666673</v>
+        <v>6.016666666666669</v>
       </c>
       <c r="AX9" t="n">
-        <v>24.68780327217065</v>
+        <v>23.64150595454553</v>
       </c>
       <c r="AY9" t="n">
-        <v>22.74674445845141</v>
+        <v>16.88692331213</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.941058813719241</v>
+        <v>6.754582642415528</v>
       </c>
       <c r="BA9" t="n">
-        <v>69.43151666666667</v>
+        <v>52.07531666666667</v>
       </c>
       <c r="BB9" t="n">
-        <v>86.75</v>
+        <v>73.02751666666667</v>
       </c>
       <c r="BC9" t="n">
-        <v>-17.31848333333333</v>
+        <v>-20.9522</v>
       </c>
       <c r="BD9" t="n">
-        <v>63.6089992787075</v>
+        <v>49.1996463669077</v>
       </c>
       <c r="BE9" t="n">
-        <v>69.25985518858938</v>
+        <v>65.15363680814482</v>
       </c>
       <c r="BF9" t="n">
-        <v>-5.650855909881884</v>
+        <v>-15.95399044123712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_022_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>166.3452166666667</v>
+      </c>
+      <c r="H10" t="n">
+        <v>188.0674333333333</v>
+      </c>
+      <c r="I10" t="n">
+        <v>126.5111630773044</v>
+      </c>
+      <c r="J10" t="n">
+        <v>126.4609732010443</v>
+      </c>
+      <c r="K10" t="n">
+        <v>54.3571101011709</v>
+      </c>
+      <c r="L10" t="n">
+        <v>46.52817854574852</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-21.72221666666661</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.05018987626010585</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7.828931555422386</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.430366666666671</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>23.84703333333334</v>
+      </c>
+      <c r="X10" t="n">
+        <v>23.71666666666667</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.1303666666666707</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.1926372453796382</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.1169990422600451</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.0756382031195931</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.683333333333333</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.383333333333333</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.5589577464659954</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.7431465466183387</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.1841888001523433</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.1079082363261396</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.1079082363261396</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>44.66666666666666</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>45.08333333333334</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.4166666666666856</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>38.02172328104655</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>33.88390179261686</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.137821488429687</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>27.98333333333333</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>29.80076666666667</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-1.817433333333341</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>24.42883704029827</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>22.74674445845141</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.68209258184686</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>66.16485</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>85.78333333333333</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-19.61848333333333</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>63.30900776411389</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>68.86227312477148</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-5.553265360657583</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>23</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_023_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>72.03223333333334</v>
+      </c>
+      <c r="H11" t="n">
+        <v>81.07328333333334</v>
+      </c>
+      <c r="I11" t="n">
+        <v>44.14425672881129</v>
+      </c>
+      <c r="J11" t="n">
+        <v>44.07790624114242</v>
+      </c>
+      <c r="K11" t="n">
+        <v>49.18766031137466</v>
+      </c>
+      <c r="L11" t="n">
+        <v>46.38866788428458</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-9.041049999999998</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.06635048766887053</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.798992427090077</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-6.016666666666669</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="X11" t="n">
+        <v>23.71666666666667</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-9.266666666666669</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1157287174312111</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1169990422600451</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.001270324828833991</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1431061962259462</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.2344720787358082</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.091365882509862</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.04717006116255434</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.04717006116255434</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>19.35811666666667</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>16.17328333333333</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.184833333333341</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>14.5716785028715</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>11.42860053715295</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.143077965718549</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>13.61666666666667</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10.23333333333333</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3.38333333333334</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.50996594053165</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>7.866765487152254</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.643200453379396</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>19.60745</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-10.54255</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18.75660731058842</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>24.43106909584137</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-5.674461785252948</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>STRICT</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>INTERCITY</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Pondicherry to Chennai</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_018_STRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_026_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>187.65295</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H12" t="n">
         <v>194.9584</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I12" t="n">
         <v>123.9926446469637</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>123.9802750677086</v>
       </c>
-      <c r="K10" t="n">
-        <v>46.87226586428536</v>
-      </c>
-      <c r="L10" t="n">
-        <v>42.81877758960633</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="K12" t="n">
+        <v>46.88285886366883</v>
+      </c>
+      <c r="L12" t="n">
+        <v>42.76169445348732</v>
+      </c>
+      <c r="M12" t="n">
         <v>-7.305450000000008</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N12" t="n">
         <v>0.0123695792550933</v>
       </c>
-      <c r="O10" t="n">
-        <v>4.053488274679033</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="O12" t="n">
+        <v>4.121164410181507</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.210583333333336</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
         <v>29.48333333333333</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="X12" t="n">
         <v>21.38333333333333</v>
       </c>
-      <c r="S10" t="n">
-        <v>-21.38333333333333</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="Y12" t="n">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.4298392460953699</v>
+      </c>
+      <c r="AA12" t="n">
         <v>0.1090721560237224</v>
       </c>
-      <c r="V10" t="n">
-        <v>-0.1090721560237224</v>
-      </c>
-      <c r="W10" t="n">
-        <v>29.48333333333333</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>29.48333333333333</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.4298392460953699</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.4298392460953699</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
+      <c r="AB12" t="n">
+        <v>0.3207670900716475</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.1105833333333333</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.8894166666666667</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.05848286929177889</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.8778317268481433</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.8193488575563643</v>
+      </c>
+      <c r="AI12" t="n">
         <v>5.266666666666667</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
         <v>5.266666666666667</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AL12" t="n">
         <v>0.3548232692194973</v>
       </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
         <v>0.3548232692194973</v>
       </c>
-      <c r="AO10" t="n">
-        <v>45.59391666666667</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>39.51666666666667</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>6.077249999999999</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>37.16754455699814</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>28.52077529734963</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8.646769259648508</v>
-      </c>
-      <c r="AU10" t="n">
+      <c r="AO12" t="n">
+        <v>45.48333333333333</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>39.18333333333333</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.299999999999997</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>37.10906168770636</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>28.21320161975721</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.895860067949148</v>
+      </c>
+      <c r="AU12" t="n">
         <v>28.73333333333333</v>
       </c>
-      <c r="AV10" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-2.06666666666667</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="AV12" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-1.733333333333338</v>
+      </c>
+      <c r="AX12" t="n">
         <v>23.38414305111067</v>
       </c>
-      <c r="AY10" t="n">
-        <v>21.13389550628888</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.250247544821789</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="AY12" t="n">
+        <v>20.93633895165053</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.447804099460139</v>
+      </c>
+      <c r="BA12" t="n">
         <v>78.57570000000001</v>
       </c>
-      <c r="BB10" t="n">
-        <v>103.2584</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-24.68269999999998</v>
-      </c>
-      <c r="BD10" t="n">
+      <c r="BB12" t="n">
+        <v>102.9250666666667</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-24.34936666666668</v>
+      </c>
+      <c r="BD12" t="n">
         <v>62.65629452354004</v>
       </c>
-      <c r="BE10" t="n">
-        <v>74.21653210804637</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>-11.56023758450632</v>
+      <c r="BE12" t="n">
+        <v>73.84383061342899</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-11.18753608988895</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>29</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_029_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>42.85905</v>
+      </c>
+      <c r="H13" t="n">
+        <v>45.4903</v>
+      </c>
+      <c r="I13" t="n">
+        <v>34.43958194459641</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.32677600023323</v>
+      </c>
+      <c r="K13" t="n">
+        <v>49.88240215190034</v>
+      </c>
+      <c r="L13" t="n">
+        <v>45.25609711599014</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-2.631249999999994</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1128059443631813</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.6263050359102</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.05476919925384444</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.1405968038522134</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.08582760459836897</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.01267380267082223</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.01267380267082223</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>15.90041666666667</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.950416666666671</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.25093473030296</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.219513195924231</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.03142153437873</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>12.59196666666667</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.74196666666667</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.785494672181397</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6.487184809227589</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.298309862953808</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>25.52363333333333</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-12.82363333333333</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>11.33570954018739</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>19.4794811912292</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-8.143771651041812</v>
       </c>
     </row>
   </sheetData>
@@ -2397,46 +2968,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>pair_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>phase</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ev_time_min</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ice_time_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>time_diff_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ev_distance_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ice_distance_km</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>distance_diff_km</t>
         </is>
@@ -2445,7 +3016,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_006</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2457,25 +3028,25 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_006</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2484,28 +3055,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.53553333333333</v>
+        <v>43.48553333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>13.1</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>29.43553333333333</v>
+        <v>6.502200000000016</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6596733987548126</v>
+        <v>1.332101358262426</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3335967503409809</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3260766484138317</v>
+        <v>0.8980233192540306</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_006</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2514,28 +3085,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.7541054091629448</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2.038955216433607</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-1.284849807270662</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_006</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2565,7 +3136,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_006</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2577,25 +3148,25 @@
         <v>52.5</v>
       </c>
       <c r="D6" t="n">
-        <v>43.73333333333333</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>8.766666666666673</v>
+        <v>10.06666666666667</v>
       </c>
       <c r="F6" t="n">
         <v>42.76805623685773</v>
       </c>
       <c r="G6" t="n">
-        <v>31.25618145550666</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="H6" t="n">
-        <v>11.51187478135107</v>
+        <v>12.17007709217261</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_006</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2604,28 +3175,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38.05478333333333</v>
+        <v>37.47145</v>
       </c>
       <c r="D7" t="n">
         <v>34.95</v>
       </c>
       <c r="E7" t="n">
-        <v>3.10478333333333</v>
+        <v>2.521449999999994</v>
       </c>
       <c r="F7" t="n">
-        <v>30.13874197108473</v>
+        <v>29.77502417243205</v>
       </c>
       <c r="G7" t="n">
         <v>25.11354425718663</v>
       </c>
       <c r="H7" t="n">
-        <v>5.025197713898102</v>
+        <v>4.661479915245422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_006</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2634,28 +3205,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>104.1833333333333</v>
+        <v>96.26666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>124.3324333333333</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>-20.1491</v>
+        <v>-24.86576666666663</v>
       </c>
       <c r="F8" t="n">
-        <v>69.67242471935344</v>
+        <v>68.60960914933557</v>
       </c>
       <c r="G8" t="n">
-        <v>86.63218730858281</v>
+        <v>85.25143440297076</v>
       </c>
       <c r="H8" t="n">
-        <v>-16.95976258922937</v>
+        <v>-16.64182525363519</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_007</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2667,25 +3238,25 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_007</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2694,28 +3265,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.41886666666667</v>
+        <v>26.36886666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>25.41886666666667</v>
+        <v>2.652200000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3245330510269857</v>
+        <v>0.9969610105345994</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3245330510269857</v>
+        <v>0.8799619682745543</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_007</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2724,28 +3295,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1.733333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.3292747005187303</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.7448250731105075</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0.4155503725917772</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_007</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2757,25 +3328,25 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3</v>
+        <v>-1.3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2122753364088935</v>
+        <v>0.1079082363261396</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2122753364088935</v>
+        <v>-0.1079082363261396</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_007</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2787,25 +3358,25 @@
         <v>43.56666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>45.5</v>
+        <v>45.08333333333334</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.93333333333333</v>
+        <v>-1.516666666666673</v>
       </c>
       <c r="F13" t="n">
         <v>38.51537746372311</v>
       </c>
       <c r="G13" t="n">
-        <v>34.12509917533455</v>
+        <v>33.88390179261686</v>
       </c>
       <c r="H13" t="n">
-        <v>4.390278288388565</v>
+        <v>4.631475671106251</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAIR_007</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2814,28 +3385,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32.13333333333333</v>
+        <v>31.55</v>
       </c>
       <c r="D14" t="n">
         <v>29.80076666666667</v>
       </c>
       <c r="E14" t="n">
-        <v>2.332566666666661</v>
+        <v>1.749233333333329</v>
       </c>
       <c r="F14" t="n">
-        <v>27.33010874041363</v>
+        <v>26.96639094176094</v>
       </c>
       <c r="G14" t="n">
         <v>22.73451919053936</v>
       </c>
       <c r="H14" t="n">
-        <v>4.595589549874269</v>
+        <v>4.231871751221583</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAIR_007</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2844,28 +3415,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>70.42728333333334</v>
+        <v>69.41061666666666</v>
       </c>
       <c r="D15" t="n">
-        <v>86.75</v>
+        <v>85.78333333333333</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.32271666666666</v>
+        <v>-16.37271666666668</v>
       </c>
       <c r="F15" t="n">
-        <v>60.33325292610726</v>
+        <v>59.6952680647336</v>
       </c>
       <c r="G15" t="n">
-        <v>69.26153371508154</v>
+        <v>68.86227312477148</v>
       </c>
       <c r="H15" t="n">
-        <v>-8.928280788974284</v>
+        <v>-9.16700506003788</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAIR_008</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2877,25 +3448,25 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAIR_008</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2907,25 +3478,25 @@
         <v>21.48333333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1</v>
+        <v>27.98333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>17.38333333333333</v>
+        <v>-6.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.237667416199215</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1135008893025534</v>
+        <v>0.2139821779699679</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1241665268966616</v>
+        <v>0.02368523822924709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAIR_008</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2934,28 +3505,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.08333333333333333</v>
+        <v>8.303566666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08333333333333333</v>
+        <v>5.8369</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.9134082250757436</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.531702164179549</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.6182939391038054</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAIR_008</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2985,7 +3556,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAIR_008</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2997,25 +3568,25 @@
         <v>48.81666666666667</v>
       </c>
       <c r="D20" t="n">
-        <v>35.28333333333333</v>
+        <v>34.15</v>
       </c>
       <c r="E20" t="n">
-        <v>13.53333333333334</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="F20" t="n">
         <v>38.82861695950649</v>
       </c>
       <c r="G20" t="n">
-        <v>26.65829138970381</v>
+        <v>26.10973756311647</v>
       </c>
       <c r="H20" t="n">
-        <v>12.17032556980268</v>
+        <v>12.71887939639002</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAIR_008</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3024,28 +3595,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35.46666666666667</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="D21" t="n">
         <v>27.01666666666667</v>
       </c>
       <c r="E21" t="n">
-        <v>8.449999999999999</v>
+        <v>8.116666666666664</v>
       </c>
       <c r="F21" t="n">
-        <v>27.95827681357427</v>
+        <v>27.71428406489335</v>
       </c>
       <c r="G21" t="n">
         <v>21.58020657782552</v>
       </c>
       <c r="H21" t="n">
-        <v>6.378070235748748</v>
+        <v>6.134077487067827</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAIR_008</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3054,28 +3625,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>76.36221666666667</v>
+        <v>68.47531666666667</v>
       </c>
       <c r="D22" t="n">
-        <v>89.67225000000001</v>
+        <v>88.33891666666666</v>
       </c>
       <c r="E22" t="n">
-        <v>-13.31003333333334</v>
+        <v>-19.86359999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>59.27885788112761</v>
+        <v>58.60944240473279</v>
       </c>
       <c r="G22" t="n">
-        <v>77.94451962578719</v>
+        <v>76.961371288195</v>
       </c>
       <c r="H22" t="n">
-        <v>-18.66566174465959</v>
+        <v>-18.35192888346221</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PAIR_009</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3087,25 +3658,25 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1090721560237224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PAIR_009</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3114,28 +3685,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>34.55</v>
+        <v>35.5</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>34.55</v>
+        <v>14.11666666666667</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4840507138833688</v>
+        <v>1.156478673390982</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4840507138833688</v>
+        <v>1.04740651736726</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAIR_009</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3144,28 +3715,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>6.983333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>5.983333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.5163595282581407</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.8385213433327759</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-0.3221618150746353</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAIR_009</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3195,7 +3766,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAIR_009</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3207,25 +3778,25 @@
         <v>44.28333333333333</v>
       </c>
       <c r="D27" t="n">
-        <v>39.51666666666667</v>
+        <v>39.18333333333333</v>
       </c>
       <c r="E27" t="n">
-        <v>4.766666666666659</v>
+        <v>5.100000000000001</v>
       </c>
       <c r="F27" t="n">
         <v>35.86032280254005</v>
       </c>
       <c r="G27" t="n">
-        <v>28.52077529734963</v>
+        <v>28.21320161975721</v>
       </c>
       <c r="H27" t="n">
-        <v>7.339547505190417</v>
+        <v>7.647121182782836</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAIR_009</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3234,28 +3805,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31.8</v>
+        <v>31.21666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>30.8</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F28" t="n">
-        <v>25.29976226838916</v>
+        <v>24.93604446973648</v>
       </c>
       <c r="G28" t="n">
-        <v>21.13389550628888</v>
+        <v>20.93633895165053</v>
       </c>
       <c r="H28" t="n">
-        <v>4.165866762100279</v>
+        <v>3.99970551808595</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PAIR_009</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3264,28 +3835,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>91.02055</v>
+        <v>83.67055000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>103.2584</v>
+        <v>102.9250666666667</v>
       </c>
       <c r="E29" t="n">
-        <v>-12.23784999999999</v>
+        <v>-19.25451666666669</v>
       </c>
       <c r="F29" t="n">
-        <v>61.83502876935029</v>
+        <v>61.00995908023722</v>
       </c>
       <c r="G29" t="n">
-        <v>74.17819311324479</v>
+        <v>73.8448020021428</v>
       </c>
       <c r="H29" t="n">
-        <v>-12.3431643438945</v>
+        <v>-12.83484292190558</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,25 +3868,25 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3327,25 +3898,25 @@
         <v>34.49703333333333</v>
       </c>
       <c r="D31" t="n">
-        <v>13.1</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="E31" t="n">
-        <v>21.39703333333333</v>
+        <v>-2.4863</v>
       </c>
       <c r="F31" t="n">
         <v>0.521661623484558</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3335967503409809</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1880648731435771</v>
+        <v>0.0875835844761626</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3354,28 +3925,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>3.683333333333333</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-0.8166666666666669</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.5589577464659954</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2.037302319652247</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-1.478344573186251</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3405,7 +3976,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3417,25 +3988,25 @@
         <v>54.2</v>
       </c>
       <c r="D34" t="n">
-        <v>43.73333333333333</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="E34" t="n">
-        <v>10.46666666666668</v>
+        <v>11.76666666666667</v>
       </c>
       <c r="F34" t="n">
         <v>43.32090510862054</v>
       </c>
       <c r="G34" t="n">
-        <v>31.2545285587253</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="H34" t="n">
-        <v>12.06637654989524</v>
+        <v>12.72292596393542</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3444,28 +4015,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>35.34495</v>
+        <v>34.92828333333333</v>
       </c>
       <c r="D35" t="n">
         <v>34.95</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3949499999999944</v>
+        <v>-0.02171666666666994</v>
       </c>
       <c r="F35" t="n">
-        <v>28.54498304892895</v>
+        <v>28.28601681705657</v>
       </c>
       <c r="G35" t="n">
         <v>25.11354425718663</v>
       </c>
       <c r="H35" t="n">
-        <v>3.431438791742323</v>
+        <v>3.172472559869941</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3474,28 +4045,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>93.73333333333333</v>
+        <v>90.46666666666667</v>
       </c>
       <c r="D36" t="n">
-        <v>124.3324333333333</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="E36" t="n">
-        <v>-30.59909999999996</v>
+        <v>-30.66576666666663</v>
       </c>
       <c r="F36" t="n">
-        <v>70.9731865628885</v>
+        <v>70.67319504829489</v>
       </c>
       <c r="G36" t="n">
-        <v>86.63074807822738</v>
+        <v>85.24999517261531</v>
       </c>
       <c r="H36" t="n">
-        <v>-15.65756151533888</v>
+        <v>-14.57680012432043</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3507,25 +4078,25 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3534,28 +4105,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>21.48333333333333</v>
+        <v>14.45</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>23.88333333333333</v>
       </c>
       <c r="E38" t="n">
-        <v>21.48333333333333</v>
+        <v>-9.43333333333333</v>
       </c>
       <c r="F38" t="n">
-        <v>0.237667416199215</v>
+        <v>0.1157287174312111</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.1004812886674145</v>
       </c>
       <c r="H38" t="n">
-        <v>0.237667416199215</v>
+        <v>0.0152474287637966</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3564,28 +4135,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.08333333333333333</v>
+        <v>4.05</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="E39" t="n">
-        <v>0.08333333333333333</v>
+        <v>2.4</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.1431061962259462</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.8813714304575493</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-0.7382652342316031</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3594,28 +4165,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.683333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="D40" t="n">
-        <v>2.633333333333333</v>
+        <v>0.35</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.95</v>
+        <v>0.6</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3011879778687425</v>
+        <v>0.04717006116255434</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2267712765180789</v>
+        <v>0.1671868728596241</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07441670135066361</v>
+        <v>-0.1200168116970698</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3624,28 +4195,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>48.91905</v>
+        <v>19.35811666666667</v>
       </c>
       <c r="D41" t="n">
-        <v>45.67373333333333</v>
+        <v>11.07741666666667</v>
       </c>
       <c r="E41" t="n">
-        <v>3.245316666666668</v>
+        <v>8.280700000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>38.90083595250158</v>
+        <v>14.57763861092875</v>
       </c>
       <c r="G41" t="n">
-        <v>34.23732716182031</v>
+        <v>8.407639114756291</v>
       </c>
       <c r="H41" t="n">
-        <v>4.66350879068127</v>
+        <v>6.169999496172458</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3654,28 +4225,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>35.46666666666667</v>
+        <v>13.61666666666667</v>
       </c>
       <c r="D42" t="n">
-        <v>29.9</v>
+        <v>9.266666666666667</v>
       </c>
       <c r="E42" t="n">
-        <v>5.56666666666667</v>
+        <v>4.350000000000003</v>
       </c>
       <c r="F42" t="n">
-        <v>27.95827681357427</v>
+        <v>10.50996594053165</v>
       </c>
       <c r="G42" t="n">
-        <v>22.79241179514765</v>
+        <v>7.155594247738707</v>
       </c>
       <c r="H42" t="n">
-        <v>5.165865018426619</v>
+        <v>3.354371692792943</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3684,28 +4255,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>77.23690000000001</v>
+        <v>19.60745</v>
       </c>
       <c r="D43" t="n">
-        <v>87.90000000000001</v>
+        <v>32.11666666666667</v>
       </c>
       <c r="E43" t="n">
-        <v>-10.6631</v>
+        <v>-12.50921666666667</v>
       </c>
       <c r="F43" t="n">
-        <v>59.39914312074116</v>
+        <v>18.75591535897876</v>
       </c>
       <c r="G43" t="n">
-        <v>69.39411264349368</v>
+        <v>27.38588852763199</v>
       </c>
       <c r="H43" t="n">
-        <v>-9.994969522752527</v>
+        <v>-8.62997316865323</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3717,25 +4288,25 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1090721560237224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3744,28 +4315,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>15.21666666666667</v>
+        <v>21.48333333333333</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="E45" t="n">
-        <v>15.21666666666667</v>
+        <v>-2.233333333333338</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1119981388984077</v>
+        <v>0.237667416199215</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1119981388984077</v>
+        <v>0.1206683739391699</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3774,28 +4345,28 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.08333333333333333</v>
+        <v>8.303566666666667</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="E46" t="n">
-        <v>0.08333333333333333</v>
+        <v>5.920233333333334</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.9162394150268994</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.7633432107826125</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.152896204244287</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3804,28 +4375,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.35</v>
+        <v>1.683333333333333</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1.633333333333333</v>
       </c>
       <c r="E47" t="n">
-        <v>1.35</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1868101281681779</v>
+        <v>0.3011879778687425</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.122404176435325</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1868101281681779</v>
+        <v>0.1787838014334175</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3834,28 +4405,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>41.28333333333333</v>
+        <v>48.91905</v>
       </c>
       <c r="D48" t="n">
-        <v>31.65</v>
+        <v>45.25706666666667</v>
       </c>
       <c r="E48" t="n">
-        <v>9.633333333333333</v>
+        <v>3.661983333333332</v>
       </c>
       <c r="F48" t="n">
-        <v>33.31093548904284</v>
+        <v>38.90083595250158</v>
       </c>
       <c r="G48" t="n">
-        <v>24.16360873509058</v>
+        <v>33.99612977910262</v>
       </c>
       <c r="H48" t="n">
-        <v>9.14732675395226</v>
+        <v>4.904706173398964</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3864,28 +4435,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>29.13333333333333</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="D49" t="n">
-        <v>23.28333333333333</v>
+        <v>29.9</v>
       </c>
       <c r="E49" t="n">
-        <v>5.849999999999998</v>
+        <v>5.233333333333334</v>
       </c>
       <c r="F49" t="n">
-        <v>23.76335197186532</v>
+        <v>27.71428406489335</v>
       </c>
       <c r="G49" t="n">
-        <v>17.08447986676835</v>
+        <v>22.79241179514765</v>
       </c>
       <c r="H49" t="n">
-        <v>6.678872105096968</v>
+        <v>4.921872269745698</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3894,28 +4465,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>52.25386666666667</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>73.19418333333333</v>
+        <v>86.93333333333334</v>
       </c>
       <c r="E50" t="n">
-        <v>-20.94031666666666</v>
+        <v>-17.58333333333334</v>
       </c>
       <c r="F50" t="n">
-        <v>49.37794399547691</v>
+        <v>58.72689645439518</v>
       </c>
       <c r="G50" t="n">
-        <v>65.37319291469859</v>
+        <v>68.97633391551152</v>
       </c>
       <c r="H50" t="n">
-        <v>-15.99524891922168</v>
+        <v>-10.24943746111634</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3927,25 +4498,25 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3954,28 +4525,28 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>23.84703333333334</v>
+        <v>15.21666666666667</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="E52" t="n">
-        <v>23.84703333333334</v>
+        <v>-6.166666666666659</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1926372453796382</v>
+        <v>0.1119981388984077</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1926372453796382</v>
+        <v>0.002925982874685304</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3984,28 +4555,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.42855</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>-0.4047833333333334</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>0.3001436458890005</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.724686338784539</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-0.4245426928955385</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4014,28 +4585,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="D54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>-2.3</v>
+        <v>1.35</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.1868101281681779</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2122753364088935</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2122753364088935</v>
+        <v>0.1868101281681779</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4044,28 +4615,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>44.66666666666666</v>
+        <v>41.28333333333333</v>
       </c>
       <c r="D55" t="n">
-        <v>45.5</v>
+        <v>31.31666666666667</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.8333333333333428</v>
+        <v>9.966666666666661</v>
       </c>
       <c r="F55" t="n">
-        <v>38.02172328104655</v>
+        <v>33.31093548904284</v>
       </c>
       <c r="G55" t="n">
-        <v>34.12509917533455</v>
+        <v>23.85603505749816</v>
       </c>
       <c r="H55" t="n">
-        <v>3.896624105712</v>
+        <v>9.454900431544679</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4074,28 +4645,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>28.4</v>
+        <v>28.96666666666667</v>
       </c>
       <c r="D56" t="n">
-        <v>29.80076666666667</v>
+        <v>22.95</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.400766666666673</v>
+        <v>6.016666666666669</v>
       </c>
       <c r="F56" t="n">
-        <v>24.68780327217065</v>
+        <v>23.64150595454553</v>
       </c>
       <c r="G56" t="n">
-        <v>22.74674445845141</v>
+        <v>16.88692331213</v>
       </c>
       <c r="H56" t="n">
-        <v>1.941058813719241</v>
+        <v>6.754582642415528</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4104,28 +4675,28 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>69.43151666666667</v>
+        <v>52.07531666666667</v>
       </c>
       <c r="D57" t="n">
-        <v>86.75</v>
+        <v>73.02751666666667</v>
       </c>
       <c r="E57" t="n">
-        <v>-17.31848333333333</v>
+        <v>-20.9522</v>
       </c>
       <c r="F57" t="n">
-        <v>63.6089992787075</v>
+        <v>49.1996463669077</v>
       </c>
       <c r="G57" t="n">
-        <v>69.25985518858938</v>
+        <v>65.15363680814482</v>
       </c>
       <c r="H57" t="n">
-        <v>-5.650855909881884</v>
+        <v>-15.95399044123712</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4137,25 +4708,25 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>-21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1090721560237224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4164,28 +4735,28 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>29.48333333333333</v>
+        <v>23.84703333333334</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="E59" t="n">
-        <v>29.48333333333333</v>
+        <v>0.1303666666666707</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4298392460953699</v>
+        <v>0.1926372453796382</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="H59" t="n">
-        <v>0.4298392460953699</v>
+        <v>0.0756382031195931</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4194,28 +4765,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>3.683333333333333</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>0.5589577464659954</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.7431465466183387</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>-0.1841888001523433</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4224,28 +4795,28 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5.266666666666667</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.266666666666667</v>
+        <v>-1.3</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3548232692194973</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.1079082363261396</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3548232692194973</v>
+        <v>-0.1079082363261396</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4254,28 +4825,28 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>45.59391666666667</v>
+        <v>44.66666666666666</v>
       </c>
       <c r="D62" t="n">
-        <v>39.51666666666667</v>
+        <v>45.08333333333334</v>
       </c>
       <c r="E62" t="n">
-        <v>6.077249999999999</v>
+        <v>-0.4166666666666856</v>
       </c>
       <c r="F62" t="n">
-        <v>37.16754455699814</v>
+        <v>38.02172328104655</v>
       </c>
       <c r="G62" t="n">
-        <v>28.52077529734963</v>
+        <v>33.88390179261686</v>
       </c>
       <c r="H62" t="n">
-        <v>8.646769259648508</v>
+        <v>4.137821488429687</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4284,28 +4855,28 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>28.73333333333333</v>
+        <v>27.98333333333333</v>
       </c>
       <c r="D63" t="n">
-        <v>30.8</v>
+        <v>29.80076666666667</v>
       </c>
       <c r="E63" t="n">
-        <v>-2.06666666666667</v>
+        <v>-1.817433333333341</v>
       </c>
       <c r="F63" t="n">
-        <v>23.38414305111067</v>
+        <v>24.42883704029827</v>
       </c>
       <c r="G63" t="n">
-        <v>21.13389550628888</v>
+        <v>22.74674445845141</v>
       </c>
       <c r="H63" t="n">
-        <v>2.250247544821789</v>
+        <v>1.68209258184686</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4314,22 +4885,652 @@
         </is>
       </c>
       <c r="C64" t="n">
+        <v>66.16485</v>
+      </c>
+      <c r="D64" t="n">
+        <v>85.78333333333333</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-19.61848333333333</v>
+      </c>
+      <c r="F64" t="n">
+        <v>63.30900776411389</v>
+      </c>
+      <c r="G64" t="n">
+        <v>68.86227312477148</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-5.553265360657583</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="D66" t="n">
+        <v>23.71666666666667</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-9.266666666666669</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.1157287174312111</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.1169990422600451</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.001270324828833991</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.1431061962259462</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.2344720787358082</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.091365882509862</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.04717006116255434</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.04717006116255434</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>19.35811666666667</v>
+      </c>
+      <c r="D69" t="n">
+        <v>16.17328333333333</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3.184833333333341</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14.5716785028715</v>
+      </c>
+      <c r="G69" t="n">
+        <v>11.42860053715295</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.143077965718549</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>13.61666666666667</v>
+      </c>
+      <c r="D70" t="n">
+        <v>10.23333333333333</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3.38333333333334</v>
+      </c>
+      <c r="F70" t="n">
+        <v>10.50996594053165</v>
+      </c>
+      <c r="G70" t="n">
+        <v>7.866765487152254</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2.643200453379396</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>19.60745</v>
+      </c>
+      <c r="D71" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-10.54255</v>
+      </c>
+      <c r="F71" t="n">
+        <v>18.75660731058842</v>
+      </c>
+      <c r="G71" t="n">
+        <v>24.43106909584137</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-5.674461785252948</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>29.48333333333333</v>
+      </c>
+      <c r="D73" t="n">
+        <v>21.38333333333333</v>
+      </c>
+      <c r="E73" t="n">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.4298392460953699</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.1090721560237224</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.3207670900716475</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.1105833333333333</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.8894166666666667</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.05848286929177889</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.8778317268481433</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-0.8193488575563643</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.3548232692194973</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.3548232692194973</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>45.48333333333333</v>
+      </c>
+      <c r="D76" t="n">
+        <v>39.18333333333333</v>
+      </c>
+      <c r="E76" t="n">
+        <v>6.299999999999997</v>
+      </c>
+      <c r="F76" t="n">
+        <v>37.10906168770636</v>
+      </c>
+      <c r="G76" t="n">
+        <v>28.21320161975721</v>
+      </c>
+      <c r="H76" t="n">
+        <v>8.895860067949148</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>28.73333333333333</v>
+      </c>
+      <c r="D77" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-1.733333333333338</v>
+      </c>
+      <c r="F77" t="n">
+        <v>23.38414305111067</v>
+      </c>
+      <c r="G77" t="n">
+        <v>20.93633895165053</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2.447804099460139</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
         <v>78.57570000000001</v>
       </c>
-      <c r="D64" t="n">
-        <v>103.2584</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-24.68269999999998</v>
-      </c>
-      <c r="F64" t="n">
+      <c r="D78" t="n">
+        <v>102.9250666666667</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-24.34936666666668</v>
+      </c>
+      <c r="F78" t="n">
         <v>62.65629452354004</v>
       </c>
-      <c r="G64" t="n">
-        <v>74.21653210804637</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-11.56023758450632</v>
+      <c r="G78" t="n">
+        <v>73.84383061342899</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-11.18753608988895</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.05476919925384444</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.1405968038522134</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.08582760459836897</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.01267380267082223</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.01267380267082223</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>15.90041666666667</v>
+      </c>
+      <c r="D83" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4.950416666666671</v>
+      </c>
+      <c r="F83" t="n">
+        <v>13.25093473030296</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8.219513195924231</v>
+      </c>
+      <c r="H83" t="n">
+        <v>5.03142153437873</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>12.59196666666667</v>
+      </c>
+      <c r="D84" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3.74196666666667</v>
+      </c>
+      <c r="F84" t="n">
+        <v>9.785494672181397</v>
+      </c>
+      <c r="G84" t="n">
+        <v>6.487184809227589</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.298309862953808</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D85" t="n">
+        <v>25.52363333333333</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-12.82363333333333</v>
+      </c>
+      <c r="F85" t="n">
+        <v>11.33570954018739</v>
+      </c>
+      <c r="G85" t="n">
+        <v>19.4794811912292</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-8.143771651041812</v>
       </c>
     </row>
   </sheetData>
@@ -4347,37 +5548,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>phase</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>EV_Mean_Time_min</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ICE_Mean_Time_min</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_Time_Diff_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Median_Time_Diff_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EV_Mean_Distance_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ICE_Mean_Distance_km</t>
         </is>
@@ -4393,19 +5594,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>22.99444444444444</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-22.99444444444444</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1088508289837273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4415,22 +5616,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.61279259259259</v>
+        <v>23.35542777777778</v>
       </c>
       <c r="C3" t="n">
-        <v>3.366666666666666</v>
+        <v>23.7375</v>
       </c>
       <c r="D3" t="n">
-        <v>24.24612592592593</v>
+        <v>-0.3820722222222197</v>
       </c>
       <c r="E3" t="n">
-        <v>23.84703333333334</v>
+        <v>-1.116666666666669</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3555253611023967</v>
+        <v>0.4540391302755695</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08674382110939058</v>
+        <v>0.1648193484804601</v>
       </c>
     </row>
     <row r="4">
@@ -4440,22 +5641,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02777777777777778</v>
+        <v>4.108022222222222</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.005555555555556</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02777777777777778</v>
+        <v>2.102466666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.866666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.4372425731550805</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.9630628543989909</v>
       </c>
     </row>
     <row r="5">
@@ -4465,22 +5666,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.605555555555556</v>
+        <v>2.126388888888889</v>
       </c>
       <c r="C5" t="n">
-        <v>1.201851851851852</v>
+        <v>0.6805555555555555</v>
       </c>
       <c r="D5" t="n">
-        <v>1.403703703703704</v>
+        <v>1.445833333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>1.35</v>
+        <v>1.141666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2641883206179052</v>
+        <v>0.2070590675464231</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1509703258668645</v>
+        <v>0.1010682087844285</v>
       </c>
     </row>
     <row r="6">
@@ -4490,22 +5691,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47.09218148148148</v>
+        <v>39.86130833333333</v>
       </c>
       <c r="C6" t="n">
-        <v>41.12300740740741</v>
+        <v>33.52703611111111</v>
       </c>
       <c r="D6" t="n">
-        <v>5.969174074074075</v>
+        <v>6.334272222222221</v>
       </c>
       <c r="E6" t="n">
-        <v>6.077249999999999</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>38.52159087231522</v>
+        <v>32.41967390213737</v>
       </c>
       <c r="G6" t="n">
-        <v>30.31796513846833</v>
+        <v>24.78398503013909</v>
       </c>
     </row>
     <row r="7">
@@ -4515,22 +5716,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.7258962962963</v>
+        <v>27.578475</v>
       </c>
       <c r="C7" t="n">
-        <v>30.14461481481482</v>
+        <v>24.88762777777778</v>
       </c>
       <c r="D7" t="n">
-        <v>2.581281481481479</v>
+        <v>2.690847222222221</v>
       </c>
       <c r="E7" t="n">
-        <v>2.332566666666661</v>
+        <v>2.952391666666667</v>
       </c>
       <c r="F7" t="n">
-        <v>26.56282755012352</v>
+        <v>22.30432976083099</v>
       </c>
       <c r="G7" t="n">
-        <v>22.15924904618704</v>
+        <v>18.3625096913239</v>
       </c>
     </row>
     <row r="8">
@@ -4540,22 +5741,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>79.24718888888889</v>
+        <v>60.53088194444445</v>
       </c>
       <c r="C8" t="n">
-        <v>97.71645555555556</v>
+        <v>79.64764444444445</v>
       </c>
       <c r="D8" t="n">
-        <v>-18.46926666666666</v>
+        <v>-19.1167625</v>
       </c>
       <c r="E8" t="n">
-        <v>-17.31848333333333</v>
+        <v>-19.43650000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>61.9039035308103</v>
+        <v>50.11146258883712</v>
       </c>
       <c r="G8" t="n">
-        <v>74.76565274397242</v>
+        <v>61.52519910560456</v>
       </c>
     </row>
   </sheetData>
@@ -4573,47 +5774,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
@@ -4626,28 +5827,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>11.44444444444444</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>4.362084109434134</v>
+        <v>6.310164959664828</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>12.75</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>22.25</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -4657,25 +5858,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>189.3113925925926</v>
+        <v>157.5605041666666</v>
       </c>
       <c r="D3" t="n">
-        <v>30.64413994732189</v>
+        <v>63.51246875352096</v>
       </c>
       <c r="E3" t="n">
-        <v>139.3205333333333</v>
+        <v>42.85905</v>
       </c>
       <c r="F3" t="n">
-        <v>171.54615</v>
+        <v>122.4984583333333</v>
       </c>
       <c r="G3" t="n">
-        <v>184.8726166666667</v>
+        <v>177.72085</v>
       </c>
       <c r="H3" t="n">
-        <v>205.7538833333333</v>
+        <v>192.1781833333333</v>
       </c>
       <c r="I3" t="n">
         <v>241.37365</v>
@@ -4688,22 +5889,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>196.5470407407407</v>
+        <v>164.4859194444444</v>
       </c>
       <c r="D4" t="n">
-        <v>29.00996853703209</v>
+        <v>63.61954168314264</v>
       </c>
       <c r="E4" t="n">
-        <v>149.51085</v>
+        <v>45.4903</v>
       </c>
       <c r="F4" t="n">
+        <v>132.4014583333333</v>
+      </c>
+      <c r="G4" t="n">
         <v>188.0674333333333</v>
-      </c>
-      <c r="G4" t="n">
-        <v>189.8237333333333</v>
       </c>
       <c r="H4" t="n">
         <v>194.9584</v>
@@ -4719,25 +5920,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>127.6080356349694</v>
+        <v>105.9338070227826</v>
       </c>
       <c r="D5" t="n">
-        <v>11.08767336107307</v>
+        <v>40.40489612793964</v>
       </c>
       <c r="E5" t="n">
-        <v>106.7510397234517</v>
+        <v>34.43958194459641</v>
       </c>
       <c r="F5" t="n">
-        <v>123.9926446469637</v>
+        <v>91.10066101390349</v>
       </c>
       <c r="G5" t="n">
-        <v>126.5111630773044</v>
+        <v>125.2479584141173</v>
       </c>
       <c r="H5" t="n">
-        <v>126.797111280885</v>
+        <v>126.6527331064285</v>
       </c>
       <c r="I5" t="n">
         <v>143.715559613142</v>
@@ -4750,25 +5951,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>127.5894319045878</v>
+        <v>105.9006442387314</v>
       </c>
       <c r="D6" t="n">
-        <v>11.096864181859</v>
+        <v>40.4330773390023</v>
       </c>
       <c r="E6" t="n">
-        <v>106.7303536725813</v>
+        <v>34.32677600023323</v>
       </c>
       <c r="F6" t="n">
-        <v>123.9802750677086</v>
+        <v>91.07230562496387</v>
       </c>
       <c r="G6" t="n">
-        <v>126.4609732010443</v>
+        <v>125.2153507636665</v>
       </c>
       <c r="H6" t="n">
-        <v>126.7676219192398</v>
+        <v>126.6150454629195</v>
       </c>
       <c r="I6" t="n">
         <v>143.7061031155876</v>
@@ -4781,28 +5982,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>47.62775026045299</v>
+        <v>48.86374072263951</v>
       </c>
       <c r="D7" t="n">
-        <v>3.710054501047124</v>
+        <v>2.899695284002024</v>
       </c>
       <c r="E7" t="n">
-        <v>43.15630919960726</v>
+        <v>44.63387255371435</v>
       </c>
       <c r="F7" t="n">
-        <v>45.56809333466344</v>
+        <v>46.73579660317592</v>
       </c>
       <c r="G7" t="n">
-        <v>46.70774678068461</v>
+        <v>49.01559974623297</v>
       </c>
       <c r="H7" t="n">
-        <v>51.59099322590557</v>
+        <v>50.30914857103133</v>
       </c>
       <c r="I7" t="n">
-        <v>53.18742578062445</v>
+        <v>54.3571101011709</v>
       </c>
     </row>
     <row r="8">
@@ -4812,28 +6013,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>45.25918042287611</v>
+        <v>45.82610889459411</v>
       </c>
       <c r="D8" t="n">
-        <v>3.10233131743509</v>
+        <v>2.839526058759173</v>
       </c>
       <c r="E8" t="n">
-        <v>42.0076907503904</v>
+        <v>42.3414520907443</v>
       </c>
       <c r="F8" t="n">
-        <v>42.80552488152868</v>
+        <v>42.76194774901236</v>
       </c>
       <c r="G8" t="n">
-        <v>45.74782714011837</v>
+        <v>46.26135246838679</v>
       </c>
       <c r="H8" t="n">
-        <v>46.12475258422111</v>
+        <v>47.14259190214048</v>
       </c>
       <c r="I8" t="n">
-        <v>49.9289852595555</v>
+        <v>49.97551623726486</v>
       </c>
     </row>
     <row r="9">
@@ -4843,25 +6044,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.235648148148152</v>
+        <v>-6.92541527777778</v>
       </c>
       <c r="D9" t="n">
-        <v>10.78086349369812</v>
+        <v>9.312623735961781</v>
       </c>
       <c r="E9" t="n">
         <v>-21.72221666666661</v>
       </c>
       <c r="F9" t="n">
-        <v>-16.52128333333329</v>
+        <v>-11.77305833333336</v>
       </c>
       <c r="G9" t="n">
-        <v>-7.305450000000008</v>
+        <v>-6.808650000000007</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2421166666667034</v>
+        <v>-2.033966666666672</v>
       </c>
       <c r="I9" t="n">
         <v>10.79548333333329</v>
@@ -4874,28 +6075,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01860373038158829</v>
+        <v>0.03316278405113652</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02905788287382128</v>
+        <v>0.03865735028547934</v>
       </c>
       <c r="E10" t="n">
         <v>-0.02777565792860059</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0123695792550933</v>
+        <v>0.01250386333216724</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02068605087039543</v>
+        <v>0.03495488288770332</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04042040413020231</v>
+        <v>0.05173398277212016</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05284572164660517</v>
+        <v>0.1128059443631813</v>
       </c>
     </row>
     <row r="11">
@@ -4905,28 +6106,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>2.368569837576881</v>
+        <v>3.037631828045396</v>
       </c>
       <c r="D11" t="n">
-        <v>3.063436863032252</v>
+        <v>2.378424959438441</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.061819175507424</v>
+        <v>-1.131977056173582</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7511928397485406</v>
+        <v>2.040161086421307</v>
       </c>
       <c r="G11" t="n">
-        <v>1.662007966350068</v>
+        <v>2.637076553689372</v>
       </c>
       <c r="H11" t="n">
-        <v>4.053488274679033</v>
+        <v>4.24744956661368</v>
       </c>
       <c r="I11" t="n">
-        <v>7.062673196403338</v>
+        <v>7.828931555422386</v>
       </c>
     </row>
     <row r="12">
@@ -4936,28 +6137,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>24.2739037037037</v>
+        <v>1.720394444444447</v>
       </c>
       <c r="D12" t="n">
-        <v>6.157788060195814</v>
+        <v>7.805548885961061</v>
       </c>
       <c r="E12" t="n">
-        <v>15.3</v>
+        <v>-7.033333333333328</v>
       </c>
       <c r="F12" t="n">
-        <v>21.39703333333333</v>
+        <v>-3.98139166666667</v>
       </c>
       <c r="G12" t="n">
-        <v>23.84703333333334</v>
+        <v>1.1261</v>
       </c>
       <c r="H12" t="n">
-        <v>29.43553333333333</v>
+        <v>4.56782083333333</v>
       </c>
       <c r="I12" t="n">
-        <v>34.55</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="13">
@@ -4967,7 +6168,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -4998,28 +6199,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>22.99444444444444</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1.210486587194497</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5029,28 +6230,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>-22.99444444444444</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1.210486587194497</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-21.38333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5060,7 +6261,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -5091,28 +6292,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1088508289837273</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.007154323090657667</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5122,28 +6323,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1088508289837273</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.007154323090657667</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1004812886674145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5153,28 +6354,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>27.61279259259259</v>
+        <v>23.35542777777778</v>
       </c>
       <c r="D19" t="n">
-        <v>8.437294178440702</v>
+        <v>11.68160588698122</v>
       </c>
       <c r="E19" t="n">
-        <v>15.21666666666667</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>21.48333333333333</v>
+        <v>15.025</v>
       </c>
       <c r="G19" t="n">
-        <v>25.41886666666667</v>
+        <v>22.66518333333334</v>
       </c>
       <c r="H19" t="n">
-        <v>34.49703333333333</v>
+        <v>30.73675833333333</v>
       </c>
       <c r="I19" t="n">
-        <v>42.53553333333333</v>
+        <v>43.48553333333334</v>
       </c>
     </row>
     <row r="20">
@@ -5184,28 +6385,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>3.366666666666666</v>
+        <v>23.7375</v>
       </c>
       <c r="D20" t="n">
-        <v>5.67912845426127</v>
+        <v>9.288553629890583</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>24.90833333333333</v>
       </c>
       <c r="I20" t="n">
-        <v>13.1</v>
+        <v>36.98333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -5215,28 +6416,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>24.24612592592593</v>
+        <v>-0.3820722222222199</v>
       </c>
       <c r="D21" t="n">
-        <v>6.189124691136724</v>
+        <v>7.253678846338935</v>
       </c>
       <c r="E21" t="n">
-        <v>15.21666666666667</v>
+        <v>-9.43333333333333</v>
       </c>
       <c r="F21" t="n">
-        <v>21.39703333333333</v>
+        <v>-6.249999999999995</v>
       </c>
       <c r="G21" t="n">
-        <v>23.84703333333334</v>
+        <v>-1.116666666666669</v>
       </c>
       <c r="H21" t="n">
-        <v>29.43553333333333</v>
+        <v>3.614700000000004</v>
       </c>
       <c r="I21" t="n">
-        <v>34.55</v>
+        <v>14.11666666666667</v>
       </c>
     </row>
     <row r="22">
@@ -5246,28 +6447,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3555253611023967</v>
+        <v>0.4540391302755695</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1791396683219084</v>
+        <v>0.4551076812848201</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1119981388984077</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>0.1157287174312111</v>
+      </c>
+      <c r="G22" t="n">
         <v>0.237667416199215</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.3245330510269857</v>
-      </c>
       <c r="H22" t="n">
-        <v>0.4840507138833688</v>
+        <v>0.6404864702470684</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6596733987548126</v>
+        <v>1.332101358262426</v>
       </c>
     </row>
     <row r="23">
@@ -5277,28 +6478,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08674382110939058</v>
+        <v>0.1648193484804601</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1447996983088511</v>
+        <v>0.1338902696497004</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1135008893025534</v>
+        <v>0.1412448261875258</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3335967503409809</v>
+        <v>0.4340780390083954</v>
       </c>
     </row>
     <row r="24">
@@ -5308,28 +6509,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2687815399930062</v>
+        <v>0.2892197817951094</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1310758949208772</v>
+        <v>0.4051610710295109</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1119981388984077</v>
+        <v>-0.001270324828833991</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1880648731435771</v>
+        <v>0.01216706729151878</v>
       </c>
       <c r="G24" t="n">
-        <v>0.237667416199215</v>
+        <v>0.08161089379787785</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3260766484138317</v>
+        <v>0.4605658096223742</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4840507138833688</v>
+        <v>1.04740651736726</v>
       </c>
     </row>
     <row r="25">
@@ -5339,28 +6540,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02777777777777778</v>
+        <v>4.108022222222221</v>
       </c>
       <c r="D25" t="n">
-        <v>0.04166666666666666</v>
+        <v>3.074306972100168</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.1105833333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.2875</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3.866666666666666</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08333333333333333</v>
+        <v>7.125</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08333333333333333</v>
+        <v>8.303566666666667</v>
       </c>
     </row>
     <row r="26">
@@ -5370,28 +6571,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2.005555555555556</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1.396194925273785</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.016666666666667</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2.404166666666666</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="27">
@@ -5401,28 +6602,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02777777777777778</v>
+        <v>2.102466666666667</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04166666666666666</v>
+        <v>2.7894855719308</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-1.733333333333333</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0.5077541666666667</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1.866666666666667</v>
       </c>
       <c r="H27" t="n">
-        <v>0.08333333333333333</v>
+        <v>3.896725</v>
       </c>
       <c r="I27" t="n">
-        <v>0.08333333333333333</v>
+        <v>5.983333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -5432,28 +6633,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.4372425731550805</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.3141645208409238</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.05476919925384444</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.1431061962259462</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.4228171143884355</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.6077446621402327</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.9162394150268994</v>
       </c>
     </row>
     <row r="29">
@@ -5463,28 +6664,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.963062854398991</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.6078524808614333</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.1405968038522134</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.7385314946598888</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.8009322770576942</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.043954113888049</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.038955216433607</v>
       </c>
     </row>
     <row r="30">
@@ -5494,28 +6695,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-0.5258202812439103</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.490535634773234</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-1.478344573186251</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.7585361400627934</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4200465327436579</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-0.160983070741723</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.152896204244287</v>
       </c>
     </row>
     <row r="31">
@@ -5525,22 +6726,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>2.605555555555555</v>
+        <v>2.126388888888889</v>
       </c>
       <c r="D31" t="n">
-        <v>2.106092353150735</v>
+        <v>2.003626237012058</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1.35</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="G31" t="n">
-        <v>1.683333333333333</v>
+        <v>1.516666666666667</v>
       </c>
       <c r="H31" t="n">
         <v>4.1</v>
@@ -5556,13 +6757,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>1.201851851851852</v>
+        <v>0.6805555555555557</v>
       </c>
       <c r="D32" t="n">
-        <v>1.110412975117204</v>
+        <v>0.7362144962657177</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -5571,13 +6772,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.616666666666667</v>
+        <v>0.35</v>
       </c>
       <c r="H32" t="n">
-        <v>2.3</v>
+        <v>1.379166666666667</v>
       </c>
       <c r="I32" t="n">
-        <v>2.633333333333333</v>
+        <v>1.633333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -5587,25 +6788,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C33" t="n">
-        <v>1.403703703703704</v>
+        <v>1.445833333333333</v>
       </c>
       <c r="D33" t="n">
-        <v>2.770075432408758</v>
+        <v>2.072000996938257</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.3</v>
+        <v>-1.3</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.95</v>
+        <v>0.1375</v>
       </c>
       <c r="G33" t="n">
-        <v>1.35</v>
+        <v>1.141666666666667</v>
       </c>
       <c r="H33" t="n">
-        <v>3.649999999999999</v>
+        <v>2.774999999999999</v>
       </c>
       <c r="I33" t="n">
         <v>5.266666666666667</v>
@@ -5618,22 +6819,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2641883206179052</v>
+        <v>0.2070590675464231</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1681389844985325</v>
+        <v>0.1769576551298824</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1868101281681779</v>
+        <v>0.03854599653962131</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3011879778687425</v>
+        <v>0.2439990530184602</v>
       </c>
       <c r="H34" t="n">
         <v>0.3548232692194973</v>
@@ -5649,13 +6850,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1509703258668645</v>
+        <v>0.1010682087844285</v>
       </c>
       <c r="D35" t="n">
-        <v>0.117415389969911</v>
+        <v>0.1033606700185287</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -5664,10 +6865,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2122753364088935</v>
+        <v>0.1079082363261396</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2267712765180789</v>
+        <v>0.1671868728596241</v>
       </c>
       <c r="I35" t="n">
         <v>0.270112055303145</v>
@@ -5680,25 +6881,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1132179947510407</v>
+        <v>0.1059908587619946</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2202252212553933</v>
+        <v>0.1770802291797526</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.2122753364088935</v>
+        <v>-0.1200168116970698</v>
       </c>
       <c r="F36" t="n">
-        <v>0.07441670135066361</v>
+        <v>-0.01747170707841823</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1340011050091184</v>
+        <v>0.1093561594627353</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1868101281681779</v>
+        <v>0.1807903831171076</v>
       </c>
       <c r="I36" t="n">
         <v>0.4394311316082445</v>
@@ -5711,25 +6912,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>47.09218148148149</v>
+        <v>39.86130833333333</v>
       </c>
       <c r="D37" t="n">
-        <v>4.305031968066269</v>
+        <v>13.59300145338558</v>
       </c>
       <c r="E37" t="n">
-        <v>41.28333333333333</v>
+        <v>15.90041666666667</v>
       </c>
       <c r="F37" t="n">
-        <v>44.28333333333333</v>
+        <v>35.80202916666666</v>
       </c>
       <c r="G37" t="n">
-        <v>45.59391666666667</v>
+        <v>44.47499999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>48.91905</v>
+        <v>48.8422625</v>
       </c>
       <c r="I37" t="n">
         <v>54.2</v>
@@ -5742,28 +6943,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>41.12300740740741</v>
+        <v>33.52703611111111</v>
       </c>
       <c r="D38" t="n">
-        <v>5.020621991175156</v>
+        <v>13.30569191288631</v>
       </c>
       <c r="E38" t="n">
-        <v>31.65</v>
+        <v>10.95</v>
       </c>
       <c r="F38" t="n">
-        <v>39.51666666666667</v>
+        <v>27.53082083333334</v>
       </c>
       <c r="G38" t="n">
-        <v>43.73333333333333</v>
+        <v>39.18333333333333</v>
       </c>
       <c r="H38" t="n">
-        <v>45.5</v>
+        <v>43.09583333333333</v>
       </c>
       <c r="I38" t="n">
-        <v>45.67373333333333</v>
+        <v>45.25706666666667</v>
       </c>
     </row>
     <row r="39">
@@ -5773,28 +6974,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C39" t="n">
-        <v>5.969174074074075</v>
+        <v>6.334272222222221</v>
       </c>
       <c r="D39" t="n">
-        <v>5.199721228118546</v>
+        <v>4.838909668720534</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.93333333333333</v>
+        <v>-1.516666666666673</v>
       </c>
       <c r="F39" t="n">
-        <v>3.245316666666668</v>
+        <v>3.542695833333334</v>
       </c>
       <c r="G39" t="n">
-        <v>6.077249999999999</v>
+        <v>5.699999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>9.633333333333333</v>
+        <v>9.991666666666664</v>
       </c>
       <c r="I39" t="n">
-        <v>13.53333333333334</v>
+        <v>14.66666666666667</v>
       </c>
     </row>
     <row r="40">
@@ -5804,25 +7005,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>38.52159087231522</v>
+        <v>32.41967390213737</v>
       </c>
       <c r="D40" t="n">
-        <v>3.114895704149354</v>
+        <v>11.34780285089765</v>
       </c>
       <c r="E40" t="n">
-        <v>33.31093548904284</v>
+        <v>13.25093473030296</v>
       </c>
       <c r="F40" t="n">
-        <v>37.16754455699814</v>
+        <v>28.62761126951432</v>
       </c>
       <c r="G40" t="n">
-        <v>38.51537746372311</v>
+        <v>37.56539248437645</v>
       </c>
       <c r="H40" t="n">
-        <v>38.90083595250158</v>
+        <v>38.84667170775526</v>
       </c>
       <c r="I40" t="n">
         <v>43.32090510862054</v>
@@ -5835,28 +7036,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C41" t="n">
-        <v>30.31796513846833</v>
+        <v>24.78398503013909</v>
       </c>
       <c r="D41" t="n">
-        <v>3.602714880031066</v>
+        <v>9.840344264033039</v>
       </c>
       <c r="E41" t="n">
-        <v>24.16360873509058</v>
+        <v>8.219513195924231</v>
       </c>
       <c r="F41" t="n">
-        <v>28.52077529734963</v>
+        <v>20.74917642741186</v>
       </c>
       <c r="G41" t="n">
-        <v>31.2545285587253</v>
+        <v>28.21320161975721</v>
       </c>
       <c r="H41" t="n">
-        <v>34.12509917533455</v>
+        <v>31.41945980666805</v>
       </c>
       <c r="I41" t="n">
-        <v>34.23732716182031</v>
+        <v>33.99612977910262</v>
       </c>
     </row>
     <row r="42">
@@ -5866,28 +7067,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C42" t="n">
-        <v>8.203625733846891</v>
+        <v>7.635688871998281</v>
       </c>
       <c r="D42" t="n">
-        <v>3.336501759639888</v>
+        <v>3.503372695304343</v>
       </c>
       <c r="E42" t="n">
-        <v>3.896624105712</v>
+        <v>3.143077965718549</v>
       </c>
       <c r="F42" t="n">
-        <v>4.66350879068127</v>
+        <v>4.836398547825786</v>
       </c>
       <c r="G42" t="n">
-        <v>8.646769259648508</v>
+        <v>6.908560339477647</v>
       </c>
       <c r="H42" t="n">
-        <v>11.51187478135107</v>
+        <v>10.13369459670166</v>
       </c>
       <c r="I42" t="n">
-        <v>12.17032556980268</v>
+        <v>12.72292596393542</v>
       </c>
     </row>
     <row r="43">
@@ -5897,28 +7098,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>32.7258962962963</v>
+        <v>27.578475</v>
       </c>
       <c r="D43" t="n">
-        <v>3.518682016066941</v>
+        <v>9.11011503386081</v>
       </c>
       <c r="E43" t="n">
-        <v>28.4</v>
+        <v>12.59196666666667</v>
       </c>
       <c r="F43" t="n">
-        <v>29.13333333333333</v>
+        <v>24.39166666666667</v>
       </c>
       <c r="G43" t="n">
-        <v>32.13333333333333</v>
+        <v>30.09166666666667</v>
       </c>
       <c r="H43" t="n">
-        <v>35.46666666666667</v>
+        <v>34.97954583333333</v>
       </c>
       <c r="I43" t="n">
-        <v>38.05478333333333</v>
+        <v>37.47145</v>
       </c>
     </row>
     <row r="44">
@@ -5928,25 +7129,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C44" t="n">
-        <v>30.14461481481482</v>
+        <v>24.88762777777778</v>
       </c>
       <c r="D44" t="n">
-        <v>3.609017451626132</v>
+        <v>9.827656922894072</v>
       </c>
       <c r="E44" t="n">
-        <v>23.28333333333333</v>
+        <v>8.85</v>
       </c>
       <c r="F44" t="n">
+        <v>19.77083333333333</v>
+      </c>
+      <c r="G44" t="n">
         <v>29.80076666666667</v>
       </c>
-      <c r="G44" t="n">
-        <v>29.9</v>
-      </c>
       <c r="H44" t="n">
-        <v>30.8</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="I44" t="n">
         <v>34.95</v>
@@ -5959,28 +7160,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C45" t="n">
-        <v>2.581281481481479</v>
+        <v>2.690847222222221</v>
       </c>
       <c r="D45" t="n">
-        <v>3.519862242820542</v>
+        <v>3.063571806779568</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.06666666666667</v>
+        <v>-1.817433333333341</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3949499999999944</v>
+        <v>0.5570708333333325</v>
       </c>
       <c r="G45" t="n">
-        <v>2.332566666666661</v>
+        <v>2.952391666666667</v>
       </c>
       <c r="H45" t="n">
-        <v>5.56666666666667</v>
+        <v>4.570833333333336</v>
       </c>
       <c r="I45" t="n">
-        <v>8.449999999999999</v>
+        <v>8.116666666666664</v>
       </c>
     </row>
     <row r="46">
@@ -5990,28 +7191,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C46" t="n">
-        <v>26.56282755012352</v>
+        <v>22.304329760831</v>
       </c>
       <c r="D46" t="n">
-        <v>2.351901642622159</v>
+        <v>7.514777192979785</v>
       </c>
       <c r="E46" t="n">
-        <v>23.38414305111067</v>
+        <v>9.785494672181397</v>
       </c>
       <c r="F46" t="n">
-        <v>24.68780327217065</v>
+        <v>20.16559877346592</v>
       </c>
       <c r="G46" t="n">
-        <v>27.33010874041363</v>
+        <v>24.68244075501737</v>
       </c>
       <c r="H46" t="n">
-        <v>27.95827681357427</v>
+        <v>27.71428406489335</v>
       </c>
       <c r="I46" t="n">
-        <v>30.13874197108473</v>
+        <v>29.77502417243205</v>
       </c>
     </row>
     <row r="47">
@@ -6021,25 +7222,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C47" t="n">
-        <v>22.15924904618704</v>
+        <v>18.3625096913239</v>
       </c>
       <c r="D47" t="n">
-        <v>2.416711976546434</v>
+        <v>7.081807764687227</v>
       </c>
       <c r="E47" t="n">
-        <v>17.08447986676835</v>
+        <v>6.487184809227589</v>
       </c>
       <c r="F47" t="n">
-        <v>21.13389550628888</v>
+        <v>14.63188385588557</v>
       </c>
       <c r="G47" t="n">
-        <v>22.73451919053936</v>
+        <v>21.25827276473802</v>
       </c>
       <c r="H47" t="n">
-        <v>22.79241179514765</v>
+        <v>22.75816129262547</v>
       </c>
       <c r="I47" t="n">
         <v>25.11354425718663</v>
@@ -6052,28 +7253,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48" t="n">
-        <v>4.403578503936482</v>
+        <v>3.941820069507091</v>
       </c>
       <c r="D48" t="n">
-        <v>1.650088555238285</v>
+        <v>1.497254478426466</v>
       </c>
       <c r="E48" t="n">
-        <v>1.941058813719241</v>
+        <v>1.68209258184686</v>
       </c>
       <c r="F48" t="n">
-        <v>3.431438791742323</v>
+        <v>3.040154533247305</v>
       </c>
       <c r="G48" t="n">
-        <v>4.595589549874269</v>
+        <v>3.677038605439447</v>
       </c>
       <c r="H48" t="n">
-        <v>5.165865018426619</v>
+        <v>4.726578003870491</v>
       </c>
       <c r="I48" t="n">
-        <v>6.678872105096968</v>
+        <v>6.754582642415528</v>
       </c>
     </row>
     <row r="49">
@@ -6083,28 +7284,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" t="n">
-        <v>79.24718888888889</v>
+        <v>60.53088194444445</v>
       </c>
       <c r="D49" t="n">
-        <v>15.35360110737687</v>
+        <v>28.59511051675933</v>
       </c>
       <c r="E49" t="n">
-        <v>52.25386666666667</v>
+        <v>12.7</v>
       </c>
       <c r="F49" t="n">
-        <v>70.42728333333334</v>
+        <v>43.95835</v>
       </c>
       <c r="G49" t="n">
-        <v>77.23690000000001</v>
+        <v>68.91265833333333</v>
       </c>
       <c r="H49" t="n">
-        <v>91.02055</v>
+        <v>79.84941250000001</v>
       </c>
       <c r="I49" t="n">
-        <v>104.1833333333333</v>
+        <v>96.26666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -6114,28 +7315,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" t="n">
-        <v>97.71645555555554</v>
+        <v>79.64764444444444</v>
       </c>
       <c r="D50" t="n">
-        <v>17.61102997812694</v>
+        <v>33.59113836774855</v>
       </c>
       <c r="E50" t="n">
-        <v>73.19418333333333</v>
+        <v>25.52363333333333</v>
       </c>
       <c r="F50" t="n">
-        <v>86.75</v>
+        <v>62.79980416666667</v>
       </c>
       <c r="G50" t="n">
-        <v>89.67225000000001</v>
+        <v>86.35833333333333</v>
       </c>
       <c r="H50" t="n">
-        <v>103.2584</v>
+        <v>102.9250666666667</v>
       </c>
       <c r="I50" t="n">
-        <v>124.3324333333333</v>
+        <v>121.1324333333333</v>
       </c>
     </row>
     <row r="51">
@@ -6145,28 +7346,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" t="n">
-        <v>-18.46926666666666</v>
+        <v>-19.1167625</v>
       </c>
       <c r="D51" t="n">
-        <v>6.393199493254956</v>
+        <v>5.75775712942291</v>
       </c>
       <c r="E51" t="n">
-        <v>-30.59909999999996</v>
+        <v>-30.66576666666663</v>
       </c>
       <c r="F51" t="n">
-        <v>-20.94031666666666</v>
+        <v>-21.80149166666667</v>
       </c>
       <c r="G51" t="n">
-        <v>-17.31848333333333</v>
+        <v>-19.43650000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>-13.31003333333334</v>
+        <v>-15.48544583333334</v>
       </c>
       <c r="I51" t="n">
-        <v>-10.6631</v>
+        <v>-10.54255</v>
       </c>
     </row>
     <row r="52">
@@ -6176,28 +7377,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" t="n">
-        <v>61.9039035308103</v>
+        <v>50.11146258883713</v>
       </c>
       <c r="D52" t="n">
-        <v>6.310817088525668</v>
+        <v>21.15799851885745</v>
       </c>
       <c r="E52" t="n">
-        <v>49.37794399547691</v>
+        <v>11.33570954018739</v>
       </c>
       <c r="F52" t="n">
-        <v>59.39914312074116</v>
+        <v>41.58888660282788</v>
       </c>
       <c r="G52" t="n">
-        <v>61.83502876935029</v>
+        <v>59.21108225956439</v>
       </c>
       <c r="H52" t="n">
-        <v>63.6089992787075</v>
+        <v>62.81947283368351</v>
       </c>
       <c r="I52" t="n">
-        <v>70.9731865628885</v>
+        <v>70.67319504829489</v>
       </c>
     </row>
     <row r="53">
@@ -6207,28 +7408,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C53" t="n">
-        <v>74.76565274397242</v>
+        <v>61.52519910560456</v>
       </c>
       <c r="D53" t="n">
-        <v>7.665081901939467</v>
+        <v>23.65136279469588</v>
       </c>
       <c r="E53" t="n">
-        <v>65.37319291469859</v>
+        <v>19.4794811912292</v>
       </c>
       <c r="F53" t="n">
-        <v>69.26153371508154</v>
+        <v>55.71169973801662</v>
       </c>
       <c r="G53" t="n">
-        <v>74.17819311324479</v>
+        <v>68.9193035201415</v>
       </c>
       <c r="H53" t="n">
-        <v>77.94451962578719</v>
+        <v>74.62394432365585</v>
       </c>
       <c r="I53" t="n">
-        <v>86.63218730858281</v>
+        <v>85.25143440297076</v>
       </c>
     </row>
     <row r="54">
@@ -6238,28 +7439,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C54" t="n">
-        <v>-12.86174921316212</v>
+        <v>-11.41373651676744</v>
       </c>
       <c r="D54" t="n">
-        <v>4.268561610710579</v>
+        <v>4.267113267731867</v>
       </c>
       <c r="E54" t="n">
-        <v>-18.66566174465959</v>
+        <v>-18.35192888346221</v>
       </c>
       <c r="F54" t="n">
-        <v>-15.99524891922168</v>
+        <v>-14.9210977035496</v>
       </c>
       <c r="G54" t="n">
-        <v>-12.3431643438945</v>
+        <v>-10.71848677550264</v>
       </c>
       <c r="H54" t="n">
-        <v>-9.994969522752527</v>
+        <v>-8.508422789250375</v>
       </c>
       <c r="I54" t="n">
-        <v>-5.650855909881884</v>
+        <v>-5.553265360657583</v>
       </c>
     </row>
   </sheetData>
@@ -6277,32 +7478,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Pair_Count</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Mean_EV_TAT_min</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_ICE_TAT_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_TAT_Difference_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Median_TAT_Difference_min</t>
         </is>
@@ -6315,19 +7516,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>189.3113925925926</v>
+        <v>157.5605041666667</v>
       </c>
       <c r="D2" t="n">
-        <v>196.5470407407407</v>
+        <v>164.4859194444444</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.235648148148152</v>
+        <v>-6.92541527777778</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.305450000000008</v>
+        <v>-6.808650000000007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>16_clustered_phase_heatmap.png</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Constant phase dimensions omitted: charging_refueling_time_diff_min</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Data/Results/Visualizations/INTERCITY/Route_Wise/Pondicherry_to_Chennai/Average/Master_Results.xlsx
+++ b/Data/Results/Visualizations/INTERCITY/Route_Wise/Pondicherry_to_Chennai/Average/Master_Results.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF13"/>
+  <dimension ref="A1:BF17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,11 +728,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_010_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_011_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -914,11 +914,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -937,38 +937,38 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_011_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>171.54615</v>
+        <v>199.8837333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>188.0674333333333</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>126.503272181271</v>
+        <v>136.6906978560236</v>
       </c>
       <c r="J3" t="n">
-        <v>126.4504264596244</v>
+        <v>137.9070606846193</v>
       </c>
       <c r="K3" t="n">
-        <v>51.96681218238075</v>
+        <v>48.73228315978446</v>
       </c>
       <c r="L3" t="n">
-        <v>46.52364975832732</v>
+        <v>40.29552120062848</v>
       </c>
       <c r="M3" t="n">
-        <v>-16.52128333333329</v>
+        <v>-31.99959999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05284572164660517</v>
+        <v>-1.216362828595692</v>
       </c>
       <c r="O3" t="n">
-        <v>5.443162424053426</v>
+        <v>8.43676195915598</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9188666666666663</v>
+        <v>5.533733333333334</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1007,104 +1007,104 @@
         <v>0.8799619682745543</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.65</v>
+        <v>7.314866666666666</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.383333333333333</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.733333333333333</v>
+        <v>2.881533333333333</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3292747005187303</v>
+        <v>0.7053124928860509</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.7448250731105075</v>
+        <v>0.9643807655585078</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.4155503725917772</v>
+        <v>-0.2590682726724569</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.3</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1079082363261396</v>
+        <v>0.7793029599160757</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.1079082363261396</v>
+        <v>-0.7793029599160757</v>
       </c>
       <c r="AO3" t="n">
-        <v>43.56666666666667</v>
+        <v>48.73333333333333</v>
       </c>
       <c r="AP3" t="n">
-        <v>45.08333333333334</v>
+        <v>50.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.516666666666673</v>
+        <v>-1.916666666666671</v>
       </c>
       <c r="AR3" t="n">
-        <v>38.51537746372311</v>
+        <v>41.44402812668966</v>
       </c>
       <c r="AS3" t="n">
-        <v>33.88390179261686</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.631475671106251</v>
+        <v>4.731818681773476</v>
       </c>
       <c r="AU3" t="n">
-        <v>31.55</v>
+        <v>36.26666666666667</v>
       </c>
       <c r="AV3" t="n">
-        <v>29.80076666666667</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.749233333333329</v>
+        <v>2.033333333333346</v>
       </c>
       <c r="AX3" t="n">
-        <v>26.96639094176094</v>
+        <v>29.14338787898033</v>
       </c>
       <c r="AY3" t="n">
-        <v>22.73451919053936</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.231871751221583</v>
+        <v>4.10286052474455</v>
       </c>
       <c r="BA3" t="n">
-        <v>69.41061666666666</v>
+        <v>81.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>85.78333333333333</v>
+        <v>109.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>-16.37271666666668</v>
+        <v>-28.09999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>59.6952680647336</v>
+        <v>64.40100834693297</v>
       </c>
       <c r="BE3" t="n">
-        <v>68.86227312477148</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="BF3" t="n">
-        <v>-9.16700506003788</v>
+        <v>-9.892632770799693</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1123,38 +1123,38 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>183.89555</v>
+        <v>251.7108833333333</v>
       </c>
       <c r="H4" t="n">
-        <v>180.3055833333333</v>
+        <v>241.6157666666667</v>
       </c>
       <c r="I4" t="n">
-        <v>126.6046070482763</v>
+        <v>144.8690786295984</v>
       </c>
       <c r="J4" t="n">
-        <v>126.5641866441461</v>
+        <v>143.7246699364842</v>
       </c>
       <c r="K4" t="n">
-        <v>48.84353918109128</v>
+        <v>40.96312925103651</v>
       </c>
       <c r="L4" t="n">
-        <v>49.97551623726486</v>
+        <v>42.34189937201894</v>
       </c>
       <c r="M4" t="n">
-        <v>3.589966666666697</v>
+        <v>10.0951166666666</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04042040413020231</v>
+        <v>1.144408693114201</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.131977056173582</v>
+        <v>-1.378770120982431</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6631</v>
+        <v>0.5035666666666714</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1175,122 +1175,122 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>21.48333333333333</v>
+        <v>32.85</v>
       </c>
       <c r="X4" t="n">
-        <v>27.98333333333333</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="Y4" t="n">
-        <v>-6.5</v>
+        <v>-4.133333333333326</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.237667416199215</v>
+        <v>0.5585488688475958</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2139821779699679</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02368523822924709</v>
+        <v>0.1244708298392004</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.303566666666667</v>
+        <v>9.136899999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.466666666666667</v>
+        <v>4.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.8369</v>
+        <v>4.636899999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.9134082250757436</v>
+        <v>1.128019155324859</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.531702164179549</v>
+        <v>2.057469342854302</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.6182939391038054</v>
+        <v>-0.929450187529443</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.683333333333333</v>
+        <v>5.683333333333334</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.35</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.333333333333333</v>
+        <v>4.066666666666666</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.3011879778687425</v>
+        <v>0.8525702698606122</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1671868728596241</v>
+        <v>0.270112055303145</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.1340011050091184</v>
+        <v>0.5824582145574673</v>
       </c>
       <c r="AO4" t="n">
-        <v>48.81666666666667</v>
+        <v>57.61666666666667</v>
       </c>
       <c r="AP4" t="n">
-        <v>34.15</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.66666666666667</v>
+        <v>15.18333333333334</v>
       </c>
       <c r="AR4" t="n">
-        <v>38.82861695950649</v>
+        <v>43.55850382048747</v>
       </c>
       <c r="AS4" t="n">
-        <v>26.10973756311647</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.71887939639002</v>
+        <v>12.96052467580235</v>
       </c>
       <c r="AU4" t="n">
-        <v>35.13333333333333</v>
+        <v>44.19065</v>
       </c>
       <c r="AV4" t="n">
-        <v>27.01666666666667</v>
+        <v>34.95</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.116666666666664</v>
+        <v>9.240649999999995</v>
       </c>
       <c r="AX4" t="n">
-        <v>27.71428406489335</v>
+        <v>32.43894398667243</v>
       </c>
       <c r="AY4" t="n">
-        <v>21.58020657782552</v>
+        <v>25.11354425718663</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.134077487067827</v>
+        <v>7.325399729485799</v>
       </c>
       <c r="BA4" t="n">
-        <v>68.47531666666667</v>
+        <v>102.2333333333333</v>
       </c>
       <c r="BB4" t="n">
-        <v>88.33891666666666</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="BC4" t="n">
-        <v>-19.86359999999999</v>
+        <v>-18.89909999999999</v>
       </c>
       <c r="BD4" t="n">
-        <v>58.60944240473279</v>
+        <v>66.33249252840548</v>
       </c>
       <c r="BE4" t="n">
-        <v>76.961371288195</v>
+        <v>85.25148709744659</v>
       </c>
       <c r="BF4" t="n">
-        <v>-18.35192888346221</v>
+        <v>-18.9189945690411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1472,11 +1472,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1658,11 +1658,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1681,38 +1681,38 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_016_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>72.03223333333334</v>
+        <v>276.1022</v>
       </c>
       <c r="H7" t="n">
-        <v>78.34408333333334</v>
+        <v>291.3597166666667</v>
       </c>
       <c r="I7" t="n">
-        <v>44.14952488525887</v>
+        <v>152.2392917821083</v>
       </c>
       <c r="J7" t="n">
-        <v>44.09816148211158</v>
+        <v>153.9475902477031</v>
       </c>
       <c r="K7" t="n">
-        <v>49.19356496670422</v>
+        <v>40.35574549266031</v>
       </c>
       <c r="L7" t="n">
-        <v>48.98583197131639</v>
+        <v>36.02192303779674</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.311850000000007</v>
+        <v>-15.25751666666673</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05136340314729182</v>
+        <v>-1.708298465594794</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2077329953878362</v>
+        <v>4.333822454863572</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.033333333333328</v>
+        <v>16.68553333333335</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1733,126 +1733,126 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>14.45</v>
+        <v>43.48553333333334</v>
       </c>
       <c r="X7" t="n">
-        <v>23.88333333333333</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>-9.43333333333333</v>
+        <v>17.15220000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1157287174312111</v>
+        <v>1.349334550099321</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1004812886674145</v>
+        <v>0.322941086990129</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0152474287637966</v>
+        <v>1.026393463109192</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.05</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>-0.4666666666666686</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1431061962259462</v>
+        <v>0.8562634337407594</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.8813714304575493</v>
+        <v>0.5256426997626461</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.7382652342316031</v>
+        <v>0.3306207339781133</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.95</v>
+        <v>6.783333333333333</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.35</v>
+        <v>14.48333333333333</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.6</v>
+        <v>-7.699999999999998</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04717006116255434</v>
+        <v>0.6700482500107362</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.1671868728596241</v>
+        <v>1.222282616060936</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1200168116970698</v>
+        <v>-0.5522343660501997</v>
       </c>
       <c r="AO7" t="n">
-        <v>19.35811666666667</v>
+        <v>55.4</v>
       </c>
       <c r="AP7" t="n">
-        <v>11.07741666666667</v>
+        <v>52.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.280700000000001</v>
+        <v>2.799999999999997</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.57763861092875</v>
+        <v>44.02574476819412</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.407639114756291</v>
+        <v>30.18268163700424</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.169999496172458</v>
+        <v>13.84306313118988</v>
       </c>
       <c r="AU7" t="n">
-        <v>13.61666666666667</v>
+        <v>40.21666666666667</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.266666666666667</v>
+        <v>41.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.350000000000003</v>
+        <v>-1.68333333333333</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.50996594053165</v>
+        <v>31.17572674470658</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.155594247738707</v>
+        <v>24.79776882222491</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.354371692792943</v>
+        <v>6.37795792248167</v>
       </c>
       <c r="BA7" t="n">
-        <v>19.60745</v>
+        <v>120.6666666666667</v>
       </c>
       <c r="BB7" t="n">
-        <v>32.11666666666667</v>
+        <v>146.0263833333333</v>
       </c>
       <c r="BC7" t="n">
-        <v>-12.50921666666667</v>
+        <v>-25.35971666666661</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.75591535897876</v>
+        <v>74.16217403535677</v>
       </c>
       <c r="BE7" t="n">
-        <v>27.38588852763199</v>
+        <v>96.89627338566024</v>
       </c>
       <c r="BF7" t="n">
-        <v>-8.62997316865323</v>
+        <v>-22.73409935030347</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_020</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1867,38 +1867,38 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_020_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_017_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>184.8726166666667</v>
+        <v>242.5876</v>
       </c>
       <c r="H8" t="n">
-        <v>189.8237333333333</v>
+        <v>242.5281833333333</v>
       </c>
       <c r="I8" t="n">
-        <v>126.797111280885</v>
+        <v>145.5987620683535</v>
       </c>
       <c r="J8" t="n">
-        <v>126.7676219192398</v>
+        <v>143.8194371210736</v>
       </c>
       <c r="K8" t="n">
-        <v>48.60919773277766</v>
+        <v>44.70287136285296</v>
       </c>
       <c r="L8" t="n">
-        <v>46.13403705248899</v>
+        <v>42.18577398047646</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.951116666666621</v>
+        <v>0.05941666666672063</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02948936164520433</v>
+        <v>1.779324947279889</v>
       </c>
       <c r="O8" t="n">
-        <v>2.475160680288667</v>
+        <v>2.517097382376498</v>
       </c>
       <c r="P8" t="n">
-        <v>3.686899999999994</v>
+        <v>6.31666666666667</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1919,126 +1919,126 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>21.48333333333333</v>
+        <v>35.1</v>
       </c>
       <c r="X8" t="n">
-        <v>23.71666666666667</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.233333333333338</v>
+        <v>-1.883333333333326</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.237667416199215</v>
+        <v>0.1862366457606098</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1169990422600451</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1206683739391699</v>
+        <v>-0.2478413932477856</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.303566666666667</v>
+        <v>12.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.383333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>5.920233333333334</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.9162394150268994</v>
+        <v>0.2864416579452221</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.7633432107826125</v>
+        <v>2.031482381418694</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.152896204244287</v>
+        <v>-1.745040723473472</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.683333333333333</v>
+        <v>3.933333333333333</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.633333333333333</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.04999999999999982</v>
+        <v>2.316666666666666</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.3011879778687425</v>
+        <v>0.3063808251647893</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.122404176435325</v>
+        <v>0.270112055303145</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.1787838014334175</v>
+        <v>0.03626876986164429</v>
       </c>
       <c r="AO8" t="n">
-        <v>48.91905</v>
+        <v>68.01666666666667</v>
       </c>
       <c r="AP8" t="n">
-        <v>45.25706666666667</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.661983333333332</v>
+        <v>25.58333333333334</v>
       </c>
       <c r="AR8" t="n">
-        <v>38.90083595250158</v>
+        <v>51.04021071573327</v>
       </c>
       <c r="AS8" t="n">
-        <v>33.99612977910262</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.904706173398964</v>
+        <v>20.44223157104815</v>
       </c>
       <c r="AU8" t="n">
-        <v>35.13333333333333</v>
+        <v>51.25311666666666</v>
       </c>
       <c r="AV8" t="n">
-        <v>29.9</v>
+        <v>34.95</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.233333333333334</v>
+        <v>16.30311666666666</v>
       </c>
       <c r="AX8" t="n">
-        <v>27.71428406489335</v>
+        <v>36.75236971798009</v>
       </c>
       <c r="AY8" t="n">
-        <v>22.79241179514765</v>
+        <v>25.11354425718663</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.921872269745698</v>
+        <v>11.63882546079346</v>
       </c>
       <c r="BA8" t="n">
-        <v>69.34999999999999</v>
+        <v>71.58448333333334</v>
       </c>
       <c r="BB8" t="n">
-        <v>86.93333333333334</v>
+        <v>122.04485</v>
       </c>
       <c r="BC8" t="n">
-        <v>-17.58333333333334</v>
+        <v>-50.46036666666666</v>
       </c>
       <c r="BD8" t="n">
-        <v>58.72689645439518</v>
+        <v>57.02712250576948</v>
       </c>
       <c r="BE8" t="n">
-        <v>68.97633391551152</v>
+        <v>85.37224124347163</v>
       </c>
       <c r="BF8" t="n">
-        <v>-10.24943746111634</v>
+        <v>-28.34511873770215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_021</t>
+          <t>PAIR_023</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2053,38 +2053,38 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_021_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_023_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>139.3205333333333</v>
+        <v>223.05115</v>
       </c>
       <c r="H9" t="n">
-        <v>149.51085</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="I9" t="n">
-        <v>106.7510397234517</v>
+        <v>137.8478512787692</v>
       </c>
       <c r="J9" t="n">
-        <v>106.7303536725813</v>
+        <v>137.9112374368539</v>
       </c>
       <c r="K9" t="n">
-        <v>51.58938782842431</v>
+        <v>43.48920820013006</v>
       </c>
       <c r="L9" t="n">
-        <v>49.91426587048593</v>
+        <v>40.29129762507425</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.19031666666672</v>
+        <v>-8.83218333333329</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02068605087039543</v>
+        <v>-0.06338615808468262</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67512195793838</v>
+        <v>3.197910575055808</v>
       </c>
       <c r="P9" t="n">
-        <v>-6.571449999999992</v>
+        <v>6.634483333333325</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2105,122 +2105,122 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>15.21666666666667</v>
+        <v>24.65</v>
       </c>
       <c r="X9" t="n">
-        <v>21.38333333333333</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="Y9" t="n">
-        <v>-6.166666666666659</v>
+        <v>0.93333333333333</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1119981388984077</v>
+        <v>0.3429025418670396</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1090721560237224</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002925982874685304</v>
+        <v>0.2259034996069945</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.42855</v>
+        <v>10.13448333333333</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.8333333333333334</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.4047833333333334</v>
+        <v>5.701149999999997</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.3001436458890005</v>
+        <v>1.045477673383005</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.724686338784539</v>
+        <v>0.9828989032306129</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.4245426928955385</v>
+        <v>0.06257877015239199</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.35</v>
+        <v>-7.450000000000001</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1868101281681779</v>
+        <v>0.404320010061295</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>0.7649615744786004</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.1868101281681779</v>
+        <v>-0.3606415644173054</v>
       </c>
       <c r="AO9" t="n">
-        <v>41.28333333333333</v>
+        <v>53.91666666666666</v>
       </c>
       <c r="AP9" t="n">
-        <v>31.31666666666667</v>
+        <v>50.65</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.966666666666661</v>
+        <v>3.266666666666659</v>
       </c>
       <c r="AR9" t="n">
-        <v>33.31093548904284</v>
+        <v>41.47108157057156</v>
       </c>
       <c r="AS9" t="n">
-        <v>23.85603505749816</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.454900431544679</v>
+        <v>4.75887212565538</v>
       </c>
       <c r="AU9" t="n">
-        <v>28.96666666666667</v>
+        <v>40.75</v>
       </c>
       <c r="AV9" t="n">
-        <v>22.95</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.016666666666669</v>
+        <v>6.516666666666673</v>
       </c>
       <c r="AX9" t="n">
-        <v>23.64150595454553</v>
+        <v>30.61488043519312</v>
       </c>
       <c r="AY9" t="n">
-        <v>16.88692331213</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.754582642415528</v>
+        <v>5.574353080957337</v>
       </c>
       <c r="BA9" t="n">
-        <v>52.07531666666667</v>
+        <v>91.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>73.02751666666667</v>
+        <v>109.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>-20.9522</v>
+        <v>-17.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>49.1996463669077</v>
+        <v>63.96918904769321</v>
       </c>
       <c r="BE9" t="n">
-        <v>65.15363680814482</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="BF9" t="n">
-        <v>-15.95399044123712</v>
+        <v>-10.32445207003945</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_022</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2239,38 +2239,38 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_022_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_024_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>166.3452166666667</v>
+        <v>207.1358666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>188.0674333333333</v>
+        <v>194.5326</v>
       </c>
       <c r="I10" t="n">
-        <v>126.5111630773044</v>
+        <v>125.021511754306</v>
       </c>
       <c r="J10" t="n">
-        <v>126.4609732010443</v>
+        <v>123.8871365945718</v>
       </c>
       <c r="K10" t="n">
-        <v>54.3571101011709</v>
+        <v>41.52158885696085</v>
       </c>
       <c r="L10" t="n">
-        <v>46.52817854574852</v>
+        <v>42.83521220753777</v>
       </c>
       <c r="M10" t="n">
-        <v>-21.72221666666661</v>
+        <v>12.60326666666668</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05018987626010585</v>
+        <v>1.134375159734205</v>
       </c>
       <c r="O10" t="n">
-        <v>7.828931555422386</v>
+        <v>-1.313623350576925</v>
       </c>
       <c r="P10" t="n">
-        <v>1.430366666666671</v>
+        <v>5.461883333333333</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2291,122 +2291,122 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>23.84703333333334</v>
+        <v>26.58333333333333</v>
       </c>
       <c r="X10" t="n">
-        <v>23.71666666666667</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1303666666666707</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1926372453796382</v>
+        <v>0.4328795915467885</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1169990422600451</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0756382031195931</v>
+        <v>0.3238074355230661</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.683333333333333</v>
+        <v>1.261883333333333</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.383333333333333</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>0.261883333333333</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.5589577464659954</v>
+        <v>0.5147545761381157</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.7431465466183387</v>
+        <v>0.8772249545701249</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.1841888001523433</v>
+        <v>-0.3624703784320092</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.3</v>
+        <v>5.35</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>0.7381924201600477</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.1079082363261396</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.1079082363261396</v>
+        <v>0.7381924201600477</v>
       </c>
       <c r="AO10" t="n">
-        <v>44.66666666666666</v>
+        <v>50.08333333333334</v>
       </c>
       <c r="AP10" t="n">
-        <v>45.08333333333334</v>
+        <v>39.18333333333333</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.4166666666666856</v>
+        <v>10.90000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>38.02172328104655</v>
+        <v>38.04082235002382</v>
       </c>
       <c r="AS10" t="n">
-        <v>33.88390179261686</v>
+        <v>28.21320161975721</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.137821488429687</v>
+        <v>9.827620730266606</v>
       </c>
       <c r="AU10" t="n">
-        <v>27.98333333333333</v>
+        <v>38.02398333333333</v>
       </c>
       <c r="AV10" t="n">
-        <v>29.80076666666667</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AW10" t="n">
-        <v>-1.817433333333341</v>
+        <v>7.557316666666658</v>
       </c>
       <c r="AX10" t="n">
-        <v>24.42883704029827</v>
+        <v>28.34973504817535</v>
       </c>
       <c r="AY10" t="n">
-        <v>22.74674445845141</v>
+        <v>20.93633895165053</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.68209258184686</v>
+        <v>7.413396096524821</v>
       </c>
       <c r="BA10" t="n">
-        <v>66.16485</v>
+        <v>85.83333333333333</v>
       </c>
       <c r="BB10" t="n">
-        <v>85.78333333333333</v>
+        <v>102.4992666666667</v>
       </c>
       <c r="BC10" t="n">
-        <v>-19.61848333333333</v>
+        <v>-16.66593333333337</v>
       </c>
       <c r="BD10" t="n">
-        <v>63.30900776411389</v>
+        <v>56.94512776826193</v>
       </c>
       <c r="BE10" t="n">
-        <v>68.86227312477148</v>
+        <v>73.75129891257018</v>
       </c>
       <c r="BF10" t="n">
-        <v>-5.553265360657583</v>
+        <v>-16.80617114430824</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_023</t>
+          <t>PAIR_025</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2425,38 +2425,38 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_023_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_025_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>72.03223333333334</v>
+        <v>189.99105</v>
       </c>
       <c r="H11" t="n">
-        <v>81.07328333333334</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="I11" t="n">
-        <v>44.14425672881129</v>
+        <v>136.7168885797278</v>
       </c>
       <c r="J11" t="n">
-        <v>44.07790624114242</v>
+        <v>137.9082545861779</v>
       </c>
       <c r="K11" t="n">
-        <v>49.18766031137466</v>
+        <v>50.21471932710446</v>
       </c>
       <c r="L11" t="n">
-        <v>46.38866788428458</v>
+        <v>40.29636713820891</v>
       </c>
       <c r="M11" t="n">
-        <v>-9.041049999999998</v>
+        <v>-41.8922833333333</v>
       </c>
       <c r="N11" t="n">
-        <v>0.06635048766887053</v>
+        <v>-1.191366006450096</v>
       </c>
       <c r="O11" t="n">
-        <v>2.798992427090077</v>
+        <v>9.918352188895554</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.016666666666669</v>
+        <v>-0.6196333333333293</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2477,112 +2477,112 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>14.45</v>
+        <v>23.84703333333334</v>
       </c>
       <c r="X11" t="n">
         <v>23.71666666666667</v>
       </c>
       <c r="Y11" t="n">
-        <v>-9.266666666666669</v>
+        <v>0.1303666666666707</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1157287174312111</v>
+        <v>0.1926372453796382</v>
       </c>
       <c r="AA11" t="n">
         <v>0.1169990422600451</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.001270324828833991</v>
+        <v>0.0756382031195931</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.05</v>
+        <v>3.683333333333333</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.8</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.25</v>
+        <v>-0.7500000000000004</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1431061962259462</v>
+        <v>0.5589577464659954</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.2344720787358082</v>
+        <v>0.9627022390663391</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.091365882509862</v>
+        <v>-0.4037444926003437</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.95</v>
+        <v>0.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.95</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.04717006116255434</v>
+        <v>0.1091649650425091</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>0.7821753879669284</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.04717006116255434</v>
+        <v>-0.6730104229244194</v>
       </c>
       <c r="AO11" t="n">
-        <v>19.35811666666667</v>
+        <v>50.55</v>
       </c>
       <c r="AP11" t="n">
-        <v>16.17328333333333</v>
+        <v>50.65</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.184833333333341</v>
+        <v>-0.1000000000000014</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.5716785028715</v>
+        <v>41.38421268521648</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.42860053715295</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.143077965718549</v>
+        <v>4.672003240300299</v>
       </c>
       <c r="AU11" t="n">
-        <v>13.61666666666667</v>
+        <v>32.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.23333333333333</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.38333333333334</v>
+        <v>-1.533333333333324</v>
       </c>
       <c r="AX11" t="n">
-        <v>10.50996594053165</v>
+        <v>26.98832105344299</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.866765487152254</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.643200453379396</v>
+        <v>1.94779369920721</v>
       </c>
       <c r="BA11" t="n">
-        <v>19.60745</v>
+        <v>78.96068333333332</v>
       </c>
       <c r="BB11" t="n">
-        <v>30.15</v>
+        <v>109.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>-10.54255</v>
+        <v>-30.33931666666668</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.75660731058842</v>
+        <v>67.48359488418018</v>
       </c>
       <c r="BE11" t="n">
-        <v>24.43106909584137</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="BF11" t="n">
-        <v>-5.674461785252948</v>
+        <v>-6.810046233552484</v>
       </c>
     </row>
     <row r="12">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2611,38 +2611,38 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_026_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_026_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>187.65295</v>
+        <v>281.0869</v>
       </c>
       <c r="H12" t="n">
-        <v>194.9584</v>
+        <v>291.75</v>
       </c>
       <c r="I12" t="n">
-        <v>123.9926446469637</v>
+        <v>153.3729275658394</v>
       </c>
       <c r="J12" t="n">
-        <v>123.9802750677086</v>
+        <v>154.0634351764531</v>
       </c>
       <c r="K12" t="n">
-        <v>46.88285886366883</v>
+        <v>38.12896580160068</v>
       </c>
       <c r="L12" t="n">
-        <v>42.76169445348732</v>
+        <v>35.98974180825657</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.305450000000008</v>
+        <v>-10.66309999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0123695792550933</v>
+        <v>-0.6905076106137074</v>
       </c>
       <c r="O12" t="n">
-        <v>4.121164410181507</v>
+        <v>2.13922399334411</v>
       </c>
       <c r="P12" t="n">
-        <v>7.210583333333336</v>
+        <v>6.386900000000004</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2663,122 +2663,122 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>29.48333333333333</v>
+        <v>32.85</v>
       </c>
       <c r="X12" t="n">
-        <v>21.38333333333333</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.100000000000001</v>
+        <v>6.516666666666673</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4298392460953699</v>
+        <v>0.5585488688475958</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1090721560237224</v>
+        <v>0.3414581795449143</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3207670900716475</v>
+        <v>0.2170906893026815</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1105833333333333</v>
+        <v>9.886899999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.8894166666666667</v>
+        <v>-0.1297666666666704</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05848286929177889</v>
+        <v>1.34706205013313</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.8778317268481433</v>
+        <v>0.5256426997626461</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.8193488575563643</v>
+        <v>0.821419350370484</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.266666666666667</v>
+        <v>7.933333333333334</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>14.48333333333333</v>
       </c>
       <c r="AK12" t="n">
-        <v>5.266666666666667</v>
+        <v>-6.549999999999997</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.3548232692194973</v>
+        <v>1.158895058334316</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.222282616060936</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.3548232692194973</v>
+        <v>-0.06338755772661986</v>
       </c>
       <c r="AO12" t="n">
-        <v>45.48333333333333</v>
+        <v>61.06666666666667</v>
       </c>
       <c r="AP12" t="n">
-        <v>39.18333333333333</v>
+        <v>52.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.299999999999997</v>
+        <v>8.466666666666669</v>
       </c>
       <c r="AR12" t="n">
-        <v>37.10906168770636</v>
+        <v>45.26405758465819</v>
       </c>
       <c r="AS12" t="n">
-        <v>28.21320161975721</v>
+        <v>30.18268163700424</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.895860067949148</v>
+        <v>15.08137594765395</v>
       </c>
       <c r="AU12" t="n">
-        <v>28.73333333333333</v>
+        <v>46.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>30.46666666666667</v>
+        <v>42.23333333333333</v>
       </c>
       <c r="AW12" t="n">
-        <v>-1.733333333333338</v>
+        <v>4.56666666666667</v>
       </c>
       <c r="AX12" t="n">
-        <v>23.38414305111067</v>
+        <v>33.58518042089994</v>
       </c>
       <c r="AY12" t="n">
-        <v>20.93633895165053</v>
+        <v>24.88861936987865</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.447804099460139</v>
+        <v>8.696561051021288</v>
       </c>
       <c r="BA12" t="n">
-        <v>78.57570000000001</v>
+        <v>122.55</v>
       </c>
       <c r="BB12" t="n">
-        <v>102.9250666666667</v>
+        <v>146.0833333333333</v>
       </c>
       <c r="BC12" t="n">
-        <v>-24.34936666666668</v>
+        <v>-23.53333333333329</v>
       </c>
       <c r="BD12" t="n">
-        <v>62.65629452354004</v>
+        <v>71.45918358296625</v>
       </c>
       <c r="BE12" t="n">
-        <v>73.84383061342899</v>
+        <v>96.90275067420166</v>
       </c>
       <c r="BF12" t="n">
-        <v>-11.18753608988895</v>
+        <v>-25.44356709123541</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_029</t>
+          <t>PAIR_027</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2797,38 +2797,38 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_029_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_027_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>42.85905</v>
+        <v>219.9088</v>
       </c>
       <c r="H13" t="n">
-        <v>45.4903</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="I13" t="n">
-        <v>34.43958194459641</v>
+        <v>138.2944646000696</v>
       </c>
       <c r="J13" t="n">
-        <v>34.32677600023323</v>
+        <v>137.8693466671948</v>
       </c>
       <c r="K13" t="n">
-        <v>49.88240215190034</v>
+        <v>46.48372876031184</v>
       </c>
       <c r="L13" t="n">
-        <v>45.25609711599014</v>
+        <v>40.28662307790311</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.631249999999994</v>
+        <v>-11.97453333333328</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1128059443631813</v>
+        <v>0.425117932874798</v>
       </c>
       <c r="O13" t="n">
-        <v>4.6263050359102</v>
+        <v>6.197105682408733</v>
       </c>
       <c r="P13" t="n">
-        <v>1.333333333333333</v>
+        <v>13.85</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2849,112 +2849,856 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>31.03333333333333</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>7.316666666666663</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>0.1769495542483206</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>0.0599505119882755</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.5</v>
+        <v>10.96666666666667</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1666666666666667</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.333333333333333</v>
+        <v>6.533333333333337</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.05476919925384444</v>
+        <v>0.2864416579452221</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1405968038522134</v>
+        <v>0.9568808181881884</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.08582760459836897</v>
+        <v>-0.6704391602429662</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.1666666666666667</v>
+        <v>2.933333333333333</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.1666666666666667</v>
+        <v>-6.616666666666667</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01267380267082223</v>
+        <v>0.2376855524103972</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>0.7490888898619357</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.01267380267082223</v>
+        <v>-0.5114033374515384</v>
       </c>
       <c r="AO13" t="n">
-        <v>15.90041666666667</v>
+        <v>62.68333333333333</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.95</v>
+        <v>50.65</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.950416666666671</v>
+        <v>12.03333333333333</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.25093473030296</v>
+        <v>48.51346678639188</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.219513195924231</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.03142153437873</v>
+        <v>11.8012573414757</v>
       </c>
       <c r="AU13" t="n">
-        <v>12.59196666666667</v>
+        <v>46.94098333333333</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.85</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.74196666666667</v>
+        <v>12.70765</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.785494672181397</v>
+        <v>34.6641680603018</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.487184809227589</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.298309862953808</v>
+        <v>9.623640706066016</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.7</v>
+        <v>65.35115</v>
       </c>
       <c r="BB13" t="n">
-        <v>25.52363333333333</v>
+        <v>109.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>-12.82363333333333</v>
+        <v>-43.94884999999999</v>
       </c>
       <c r="BD13" t="n">
-        <v>11.33570954018739</v>
+        <v>54.41575298877198</v>
       </c>
       <c r="BE13" t="n">
-        <v>19.4794811912292</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="BF13" t="n">
-        <v>-8.143771651041812</v>
+        <v>-19.87788812896068</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>31</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_031_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>187.65295</v>
+      </c>
+      <c r="H14" t="n">
+        <v>194.9584</v>
+      </c>
+      <c r="I14" t="n">
+        <v>123.9926446469637</v>
+      </c>
+      <c r="J14" t="n">
+        <v>123.9802750677086</v>
+      </c>
+      <c r="K14" t="n">
+        <v>46.88285886366883</v>
+      </c>
+      <c r="L14" t="n">
+        <v>42.76169445348732</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-7.305450000000008</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0123695792550933</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.121164410181507</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7.210583333333336</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>29.48333333333333</v>
+      </c>
+      <c r="X14" t="n">
+        <v>21.38333333333333</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.4298392460953699</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.1090721560237224</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.3207670900716475</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.1105833333333333</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.8894166666666667</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.05848286929177889</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.8778317268481433</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.8193488575563643</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.3548232692194973</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.3548232692194973</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>45.48333333333333</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>39.18333333333333</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.299999999999997</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>37.10906168770636</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>28.21320161975721</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8.895860067949148</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>28.73333333333333</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-1.733333333333338</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>23.38414305111067</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>20.93633895165053</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.447804099460139</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>78.57570000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>102.9250666666667</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-24.34936666666668</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>62.65629452354004</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>73.84383061342899</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-11.18753608988895</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>34</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_034_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>252.8470333333333</v>
+      </c>
+      <c r="H15" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>152.3946794802466</v>
+      </c>
+      <c r="J15" t="n">
+        <v>154.0323598514136</v>
+      </c>
+      <c r="K15" t="n">
+        <v>42.28793493991633</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35.98718333260023</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-38.90296666666671</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1.637680371166994</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6.300751607316101</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.830366666666663</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>34.49703333333333</v>
+      </c>
+      <c r="X15" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.163699999999999</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.5388878376354634</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.321273432549297</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.2176144050861664</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.683333333333333</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>10.01666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-6.333333333333336</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.5589577464659954</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.5256426997626461</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.03331504670334928</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>14.48333333333333</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-7.133333333333331</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.6798850900122044</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.222282616060936</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.5423975260487315</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.949999999999996</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>44.66597796080278</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>30.18268163700424</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>14.48329632379854</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>37.36666666666667</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>42.23333333333333</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-4.86666666666666</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>29.46179071078489</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>24.87772879183483</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.584061918950059</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>146.0833333333333</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-33.68333333333328</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>76.48918013454522</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>96.90275067420166</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-20.41357053965643</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>35</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_035_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>194.9381166666667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>194.9584</v>
+      </c>
+      <c r="I16" t="n">
+        <v>125.7416693023907</v>
+      </c>
+      <c r="J16" t="n">
+        <v>123.9823800042885</v>
+      </c>
+      <c r="K16" t="n">
+        <v>45.47510257059169</v>
+      </c>
+      <c r="L16" t="n">
+        <v>42.7689234538736</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.02028333333331034</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.759289298102203</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.70617911671809</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6.935000000000002</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="X16" t="n">
+        <v>21.38333333333333</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.7333333333333307</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.07050792832939867</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.1090721560237224</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.03856422769432373</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.668333333333333</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>7.668333333333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.1448841273528465</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.8591442430348036</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.7142601156819571</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.983333333333333</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.983333333333333</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.259210764002235</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.259210764002235</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>56.78333333333333</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>39.18333333333333</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>43.79816613863036</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>28.21320161975721</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>15.58496451887315</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>43.36978333333333</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>12.90311666666666</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>31.32770704550355</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>20.93633895165053</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10.39136809385302</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>62.48333333333333</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>102.9250666666667</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-40.44173333333337</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>50.14119329857225</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>73.86462303382228</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-23.72342973525004</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>52</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\26-09-2026\PAIR_052_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>263.95295</v>
+      </c>
+      <c r="H17" t="n">
+        <v>286.3403666666666</v>
+      </c>
+      <c r="I17" t="n">
+        <v>151.560156776244</v>
+      </c>
+      <c r="J17" t="n">
+        <v>152.1093053055016</v>
+      </c>
+      <c r="K17" t="n">
+        <v>42.41012053032751</v>
+      </c>
+      <c r="L17" t="n">
+        <v>36.29360732288521</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22.38741666666664</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.5491485292575931</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6.116513207442303</v>
+      </c>
+      <c r="P17" t="n">
+        <v>13.86666666666667</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.766666666666673</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.1862366457606098</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.3661259006707928</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.179889254910183</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>15.11666666666667</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>10.01666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.297561165968511</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.5256426997626461</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.2280815337941351</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-7.550000000000001</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.420813179835343</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.205289753214544</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.215523426620799</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>73.30295</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>51.26666666666667</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>22.03628333333332</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>52.75602854613859</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>29.79516392210389</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>22.9608646240347</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>55.48333333333333</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>41.04036666666666</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>14.44296666666667</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>37.95304168068559</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>24.54736075797758</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>13.40568092270801</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>143.5333333333333</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-65.18333333333331</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>58.94647555785541</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>95.66972227177216</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-36.72324671391675</v>
       </c>
     </row>
   </sheetData>
@@ -2968,7 +3712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3016,7 +3760,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3046,7 +3790,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3076,7 +3820,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3106,7 +3850,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3136,7 +3880,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3166,7 +3910,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3196,7 +3940,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3226,7 +3970,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3256,7 +4000,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3286,7 +4030,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3295,28 +4039,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.65</v>
+        <v>7.314866666666666</v>
       </c>
       <c r="D11" t="n">
-        <v>2.383333333333333</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.733333333333333</v>
+        <v>2.881533333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3292747005187303</v>
+        <v>0.7053124928860509</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7448250731105075</v>
+        <v>0.9643807655585078</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4155503725917772</v>
+        <v>-0.2590682726724569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3328,25 +4072,25 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1079082363261396</v>
+        <v>0.7793029599160757</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1079082363261396</v>
+        <v>-0.7793029599160757</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3355,28 +4099,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>43.56666666666667</v>
+        <v>48.73333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>45.08333333333334</v>
+        <v>50.65</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.516666666666673</v>
+        <v>-1.916666666666671</v>
       </c>
       <c r="F13" t="n">
-        <v>38.51537746372311</v>
+        <v>41.44402812668966</v>
       </c>
       <c r="G13" t="n">
-        <v>33.88390179261686</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="H13" t="n">
-        <v>4.631475671106251</v>
+        <v>4.731818681773476</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3385,28 +4129,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>31.55</v>
+        <v>36.26666666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80076666666667</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="E14" t="n">
-        <v>1.749233333333329</v>
+        <v>2.033333333333346</v>
       </c>
       <c r="F14" t="n">
-        <v>26.96639094176094</v>
+        <v>29.14338787898033</v>
       </c>
       <c r="G14" t="n">
-        <v>22.73451919053936</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="H14" t="n">
-        <v>4.231871751221583</v>
+        <v>4.10286052474455</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_012</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3415,28 +4159,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69.41061666666666</v>
+        <v>81.2</v>
       </c>
       <c r="D15" t="n">
-        <v>85.78333333333333</v>
+        <v>109.3</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.37271666666668</v>
+        <v>-28.09999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>59.6952680647336</v>
+        <v>64.40100834693297</v>
       </c>
       <c r="G15" t="n">
-        <v>68.86227312477148</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.16700506003788</v>
+        <v>-9.892632770799693</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3466,7 +4210,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3475,28 +4219,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.48333333333333</v>
+        <v>32.85</v>
       </c>
       <c r="D17" t="n">
-        <v>27.98333333333333</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.5</v>
+        <v>-4.133333333333326</v>
       </c>
       <c r="F17" t="n">
-        <v>0.237667416199215</v>
+        <v>0.5585488688475958</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2139821779699679</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02368523822924709</v>
+        <v>0.1244708298392004</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3505,28 +4249,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.303566666666667</v>
+        <v>9.136899999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>2.466666666666667</v>
+        <v>4.5</v>
       </c>
       <c r="E18" t="n">
-        <v>5.8369</v>
+        <v>4.636899999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9134082250757436</v>
+        <v>1.128019155324859</v>
       </c>
       <c r="G18" t="n">
-        <v>1.531702164179549</v>
+        <v>2.057469342854302</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6182939391038054</v>
+        <v>-0.929450187529443</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3535,28 +4279,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.683333333333333</v>
+        <v>5.683333333333334</v>
       </c>
       <c r="D19" t="n">
-        <v>0.35</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="E19" t="n">
-        <v>1.333333333333333</v>
+        <v>4.066666666666666</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3011879778687425</v>
+        <v>0.8525702698606122</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1671868728596241</v>
+        <v>0.270112055303145</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1340011050091184</v>
+        <v>0.5824582145574673</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3565,28 +4309,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48.81666666666667</v>
+        <v>57.61666666666667</v>
       </c>
       <c r="D20" t="n">
-        <v>34.15</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="E20" t="n">
-        <v>14.66666666666667</v>
+        <v>15.18333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>38.82861695950649</v>
+        <v>43.55850382048747</v>
       </c>
       <c r="G20" t="n">
-        <v>26.10973756311647</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="H20" t="n">
-        <v>12.71887939639002</v>
+        <v>12.96052467580235</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3595,28 +4339,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35.13333333333333</v>
+        <v>44.19065</v>
       </c>
       <c r="D21" t="n">
-        <v>27.01666666666667</v>
+        <v>34.95</v>
       </c>
       <c r="E21" t="n">
-        <v>8.116666666666664</v>
+        <v>9.240649999999995</v>
       </c>
       <c r="F21" t="n">
-        <v>27.71428406489335</v>
+        <v>32.43894398667243</v>
       </c>
       <c r="G21" t="n">
-        <v>21.58020657782552</v>
+        <v>25.11354425718663</v>
       </c>
       <c r="H21" t="n">
-        <v>6.134077487067827</v>
+        <v>7.325399729485799</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_013</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3625,28 +4369,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>68.47531666666667</v>
+        <v>102.2333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>88.33891666666666</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>-19.86359999999999</v>
+        <v>-18.89909999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>58.60944240473279</v>
+        <v>66.33249252840548</v>
       </c>
       <c r="G22" t="n">
-        <v>76.961371288195</v>
+        <v>85.25148709744659</v>
       </c>
       <c r="H22" t="n">
-        <v>-18.35192888346221</v>
+        <v>-18.9189945690411</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3676,7 +4420,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3706,7 +4450,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3736,7 +4480,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3766,7 +4510,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3796,7 +4540,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3826,7 +4570,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_014</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3856,7 +4600,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3886,7 +4630,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3916,7 +4660,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3946,7 +4690,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3976,7 +4720,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4006,7 +4750,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4036,7 +4780,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_015</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4066,7 +4810,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4096,7 +4840,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4105,28 +4849,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>14.45</v>
+        <v>43.48553333333334</v>
       </c>
       <c r="D38" t="n">
-        <v>23.88333333333333</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="E38" t="n">
-        <v>-9.43333333333333</v>
+        <v>17.15220000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1157287174312111</v>
+        <v>1.349334550099321</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1004812886674145</v>
+        <v>0.322941086990129</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0152474287637966</v>
+        <v>1.026393463109192</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4135,28 +4879,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.05</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>1.65</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="E39" t="n">
-        <v>2.4</v>
+        <v>-0.4666666666666686</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1431061962259462</v>
+        <v>0.8562634337407594</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8813714304575493</v>
+        <v>0.5256426997626461</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7382652342316031</v>
+        <v>0.3306207339781133</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4165,28 +4909,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.95</v>
+        <v>6.783333333333333</v>
       </c>
       <c r="D40" t="n">
-        <v>0.35</v>
+        <v>14.48333333333333</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6</v>
+        <v>-7.699999999999998</v>
       </c>
       <c r="F40" t="n">
-        <v>0.04717006116255434</v>
+        <v>0.6700482500107362</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1671868728596241</v>
+        <v>1.222282616060936</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.1200168116970698</v>
+        <v>-0.5522343660501997</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4195,28 +4939,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>19.35811666666667</v>
+        <v>55.4</v>
       </c>
       <c r="D41" t="n">
-        <v>11.07741666666667</v>
+        <v>52.6</v>
       </c>
       <c r="E41" t="n">
-        <v>8.280700000000001</v>
+        <v>2.799999999999997</v>
       </c>
       <c r="F41" t="n">
-        <v>14.57763861092875</v>
+        <v>44.02574476819412</v>
       </c>
       <c r="G41" t="n">
-        <v>8.407639114756291</v>
+        <v>30.18268163700424</v>
       </c>
       <c r="H41" t="n">
-        <v>6.169999496172458</v>
+        <v>13.84306313118988</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4225,28 +4969,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>13.61666666666667</v>
+        <v>40.21666666666667</v>
       </c>
       <c r="D42" t="n">
-        <v>9.266666666666667</v>
+        <v>41.9</v>
       </c>
       <c r="E42" t="n">
-        <v>4.350000000000003</v>
+        <v>-1.68333333333333</v>
       </c>
       <c r="F42" t="n">
-        <v>10.50996594053165</v>
+        <v>31.17572674470658</v>
       </c>
       <c r="G42" t="n">
-        <v>7.155594247738707</v>
+        <v>24.79776882222491</v>
       </c>
       <c r="H42" t="n">
-        <v>3.354371692792943</v>
+        <v>6.37795792248167</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PAIR_015</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4255,28 +4999,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>19.60745</v>
+        <v>120.6666666666667</v>
       </c>
       <c r="D43" t="n">
-        <v>32.11666666666667</v>
+        <v>146.0263833333333</v>
       </c>
       <c r="E43" t="n">
-        <v>-12.50921666666667</v>
+        <v>-25.35971666666661</v>
       </c>
       <c r="F43" t="n">
-        <v>18.75591535897876</v>
+        <v>74.16217403535677</v>
       </c>
       <c r="G43" t="n">
-        <v>27.38588852763199</v>
+        <v>96.89627338566024</v>
       </c>
       <c r="H43" t="n">
-        <v>-8.62997316865323</v>
+        <v>-22.73409935030347</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PAIR_020</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4306,7 +5050,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PAIR_020</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4315,28 +5059,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>21.48333333333333</v>
+        <v>35.1</v>
       </c>
       <c r="D45" t="n">
-        <v>23.71666666666667</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.233333333333338</v>
+        <v>-1.883333333333326</v>
       </c>
       <c r="F45" t="n">
-        <v>0.237667416199215</v>
+        <v>0.1862366457606098</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1169990422600451</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1206683739391699</v>
+        <v>-0.2478413932477856</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PAIR_020</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4345,28 +5089,28 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.303566666666667</v>
+        <v>12.7</v>
       </c>
       <c r="D46" t="n">
-        <v>2.383333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="E46" t="n">
-        <v>5.920233333333334</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9162394150268994</v>
+        <v>0.2864416579452221</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7633432107826125</v>
+        <v>2.031482381418694</v>
       </c>
       <c r="H46" t="n">
-        <v>0.152896204244287</v>
+        <v>-1.745040723473472</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PAIR_020</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4375,28 +5119,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.683333333333333</v>
+        <v>3.933333333333333</v>
       </c>
       <c r="D47" t="n">
-        <v>1.633333333333333</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="E47" t="n">
-        <v>0.04999999999999982</v>
+        <v>2.316666666666666</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3011879778687425</v>
+        <v>0.3063808251647893</v>
       </c>
       <c r="G47" t="n">
-        <v>0.122404176435325</v>
+        <v>0.270112055303145</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1787838014334175</v>
+        <v>0.03626876986164429</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PAIR_020</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4405,28 +5149,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>48.91905</v>
+        <v>68.01666666666667</v>
       </c>
       <c r="D48" t="n">
-        <v>45.25706666666667</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="E48" t="n">
-        <v>3.661983333333332</v>
+        <v>25.58333333333334</v>
       </c>
       <c r="F48" t="n">
-        <v>38.90083595250158</v>
+        <v>51.04021071573327</v>
       </c>
       <c r="G48" t="n">
-        <v>33.99612977910262</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="H48" t="n">
-        <v>4.904706173398964</v>
+        <v>20.44223157104815</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PAIR_020</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4435,28 +5179,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35.13333333333333</v>
+        <v>51.25311666666666</v>
       </c>
       <c r="D49" t="n">
-        <v>29.9</v>
+        <v>34.95</v>
       </c>
       <c r="E49" t="n">
-        <v>5.233333333333334</v>
+        <v>16.30311666666666</v>
       </c>
       <c r="F49" t="n">
-        <v>27.71428406489335</v>
+        <v>36.75236971798009</v>
       </c>
       <c r="G49" t="n">
-        <v>22.79241179514765</v>
+        <v>25.11354425718663</v>
       </c>
       <c r="H49" t="n">
-        <v>4.921872269745698</v>
+        <v>11.63882546079346</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PAIR_020</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,28 +5209,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>69.34999999999999</v>
+        <v>71.58448333333334</v>
       </c>
       <c r="D50" t="n">
-        <v>86.93333333333334</v>
+        <v>122.04485</v>
       </c>
       <c r="E50" t="n">
-        <v>-17.58333333333334</v>
+        <v>-50.46036666666666</v>
       </c>
       <c r="F50" t="n">
-        <v>58.72689645439518</v>
+        <v>57.02712250576948</v>
       </c>
       <c r="G50" t="n">
-        <v>68.97633391551152</v>
+        <v>85.37224124347163</v>
       </c>
       <c r="H50" t="n">
-        <v>-10.24943746111634</v>
+        <v>-28.34511873770215</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PAIR_021</t>
+          <t>PAIR_023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4516,7 +5260,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PAIR_021</t>
+          <t>PAIR_023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4525,28 +5269,28 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>15.21666666666667</v>
+        <v>24.65</v>
       </c>
       <c r="D52" t="n">
-        <v>21.38333333333333</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="E52" t="n">
-        <v>-6.166666666666659</v>
+        <v>0.93333333333333</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1119981388984077</v>
+        <v>0.3429025418670396</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1090721560237224</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="H52" t="n">
-        <v>0.002925982874685304</v>
+        <v>0.2259034996069945</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PAIR_021</t>
+          <t>PAIR_023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4555,28 +5299,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.42855</v>
+        <v>10.13448333333333</v>
       </c>
       <c r="D53" t="n">
-        <v>0.8333333333333334</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.4047833333333334</v>
+        <v>5.701149999999997</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3001436458890005</v>
+        <v>1.045477673383005</v>
       </c>
       <c r="G53" t="n">
-        <v>0.724686338784539</v>
+        <v>0.9828989032306129</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.4245426928955385</v>
+        <v>0.06257877015239199</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PAIR_021</t>
+          <t>PAIR_023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4585,28 +5329,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>1.35</v>
+        <v>-7.450000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1868101281681779</v>
+        <v>0.404320010061295</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.7649615744786004</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1868101281681779</v>
+        <v>-0.3606415644173054</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PAIR_021</t>
+          <t>PAIR_023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4615,28 +5359,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>41.28333333333333</v>
+        <v>53.91666666666666</v>
       </c>
       <c r="D55" t="n">
-        <v>31.31666666666667</v>
+        <v>50.65</v>
       </c>
       <c r="E55" t="n">
-        <v>9.966666666666661</v>
+        <v>3.266666666666659</v>
       </c>
       <c r="F55" t="n">
-        <v>33.31093548904284</v>
+        <v>41.47108157057156</v>
       </c>
       <c r="G55" t="n">
-        <v>23.85603505749816</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="H55" t="n">
-        <v>9.454900431544679</v>
+        <v>4.75887212565538</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PAIR_021</t>
+          <t>PAIR_023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4645,28 +5389,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>28.96666666666667</v>
+        <v>40.75</v>
       </c>
       <c r="D56" t="n">
-        <v>22.95</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="E56" t="n">
-        <v>6.016666666666669</v>
+        <v>6.516666666666673</v>
       </c>
       <c r="F56" t="n">
-        <v>23.64150595454553</v>
+        <v>30.61488043519312</v>
       </c>
       <c r="G56" t="n">
-        <v>16.88692331213</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="H56" t="n">
-        <v>6.754582642415528</v>
+        <v>5.574353080957337</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PAIR_021</t>
+          <t>PAIR_023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4675,28 +5419,28 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>52.07531666666667</v>
+        <v>91.5</v>
       </c>
       <c r="D57" t="n">
-        <v>73.02751666666667</v>
+        <v>109.3</v>
       </c>
       <c r="E57" t="n">
-        <v>-20.9522</v>
+        <v>-17.8</v>
       </c>
       <c r="F57" t="n">
-        <v>49.1996463669077</v>
+        <v>63.96918904769321</v>
       </c>
       <c r="G57" t="n">
-        <v>65.15363680814482</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="H57" t="n">
-        <v>-15.95399044123712</v>
+        <v>-10.32445207003945</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PAIR_022</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4726,7 +5470,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PAIR_022</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4735,28 +5479,28 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23.84703333333334</v>
+        <v>26.58333333333333</v>
       </c>
       <c r="D59" t="n">
-        <v>23.71666666666667</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1303666666666707</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1926372453796382</v>
+        <v>0.4328795915467885</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1169990422600451</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0756382031195931</v>
+        <v>0.3238074355230661</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PAIR_022</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4765,28 +5509,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3.683333333333333</v>
+        <v>1.261883333333333</v>
       </c>
       <c r="D60" t="n">
-        <v>2.383333333333333</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>1.3</v>
+        <v>0.261883333333333</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5589577464659954</v>
+        <v>0.5147545761381157</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7431465466183387</v>
+        <v>0.8772249545701249</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1841888001523433</v>
+        <v>-0.3624703784320092</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PAIR_022</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4795,28 +5539,28 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="D61" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.3</v>
+        <v>5.35</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>0.7381924201600477</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1079082363261396</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.1079082363261396</v>
+        <v>0.7381924201600477</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PAIR_022</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4825,28 +5569,28 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>44.66666666666666</v>
+        <v>50.08333333333334</v>
       </c>
       <c r="D62" t="n">
-        <v>45.08333333333334</v>
+        <v>39.18333333333333</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4166666666666856</v>
+        <v>10.90000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>38.02172328104655</v>
+        <v>38.04082235002382</v>
       </c>
       <c r="G62" t="n">
-        <v>33.88390179261686</v>
+        <v>28.21320161975721</v>
       </c>
       <c r="H62" t="n">
-        <v>4.137821488429687</v>
+        <v>9.827620730266606</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PAIR_022</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4855,28 +5599,28 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>27.98333333333333</v>
+        <v>38.02398333333333</v>
       </c>
       <c r="D63" t="n">
-        <v>29.80076666666667</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.817433333333341</v>
+        <v>7.557316666666658</v>
       </c>
       <c r="F63" t="n">
-        <v>24.42883704029827</v>
+        <v>28.34973504817535</v>
       </c>
       <c r="G63" t="n">
-        <v>22.74674445845141</v>
+        <v>20.93633895165053</v>
       </c>
       <c r="H63" t="n">
-        <v>1.68209258184686</v>
+        <v>7.413396096524821</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PAIR_022</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4885,28 +5629,28 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>66.16485</v>
+        <v>85.83333333333333</v>
       </c>
       <c r="D64" t="n">
-        <v>85.78333333333333</v>
+        <v>102.4992666666667</v>
       </c>
       <c r="E64" t="n">
-        <v>-19.61848333333333</v>
+        <v>-16.66593333333337</v>
       </c>
       <c r="F64" t="n">
-        <v>63.30900776411389</v>
+        <v>56.94512776826193</v>
       </c>
       <c r="G64" t="n">
-        <v>68.86227312477148</v>
+        <v>73.75129891257018</v>
       </c>
       <c r="H64" t="n">
-        <v>-5.553265360657583</v>
+        <v>-16.80617114430824</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PAIR_023</t>
+          <t>PAIR_025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4936,7 +5680,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PAIR_023</t>
+          <t>PAIR_025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4945,28 +5689,28 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>14.45</v>
+        <v>23.84703333333334</v>
       </c>
       <c r="D66" t="n">
         <v>23.71666666666667</v>
       </c>
       <c r="E66" t="n">
-        <v>-9.266666666666669</v>
+        <v>0.1303666666666707</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1157287174312111</v>
+        <v>0.1926372453796382</v>
       </c>
       <c r="G66" t="n">
         <v>0.1169990422600451</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.001270324828833991</v>
+        <v>0.0756382031195931</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PAIR_023</t>
+          <t>PAIR_025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4975,28 +5719,28 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4.05</v>
+        <v>3.683333333333333</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="E67" t="n">
-        <v>3.25</v>
+        <v>-0.7500000000000004</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1431061962259462</v>
+        <v>0.5589577464659954</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2344720787358082</v>
+        <v>0.9627022390663391</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.091365882509862</v>
+        <v>-0.4037444926003437</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PAIR_023</t>
+          <t>PAIR_025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5005,28 +5749,28 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.95</v>
+        <v>0.25</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>0.95</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="F68" t="n">
-        <v>0.04717006116255434</v>
+        <v>0.1091649650425091</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>0.7821753879669284</v>
       </c>
       <c r="H68" t="n">
-        <v>0.04717006116255434</v>
+        <v>-0.6730104229244194</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PAIR_023</t>
+          <t>PAIR_025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5035,28 +5779,28 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>19.35811666666667</v>
+        <v>50.55</v>
       </c>
       <c r="D69" t="n">
-        <v>16.17328333333333</v>
+        <v>50.65</v>
       </c>
       <c r="E69" t="n">
-        <v>3.184833333333341</v>
+        <v>-0.1000000000000014</v>
       </c>
       <c r="F69" t="n">
-        <v>14.5716785028715</v>
+        <v>41.38421268521648</v>
       </c>
       <c r="G69" t="n">
-        <v>11.42860053715295</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="H69" t="n">
-        <v>3.143077965718549</v>
+        <v>4.672003240300299</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PAIR_023</t>
+          <t>PAIR_025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5065,28 +5809,28 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>13.61666666666667</v>
+        <v>32.7</v>
       </c>
       <c r="D70" t="n">
-        <v>10.23333333333333</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="E70" t="n">
-        <v>3.38333333333334</v>
+        <v>-1.533333333333324</v>
       </c>
       <c r="F70" t="n">
-        <v>10.50996594053165</v>
+        <v>26.98832105344299</v>
       </c>
       <c r="G70" t="n">
-        <v>7.866765487152254</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="H70" t="n">
-        <v>2.643200453379396</v>
+        <v>1.94779369920721</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PAIR_023</t>
+          <t>PAIR_025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5095,22 +5839,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>19.60745</v>
+        <v>78.96068333333332</v>
       </c>
       <c r="D71" t="n">
-        <v>30.15</v>
+        <v>109.3</v>
       </c>
       <c r="E71" t="n">
-        <v>-10.54255</v>
+        <v>-30.33931666666668</v>
       </c>
       <c r="F71" t="n">
-        <v>18.75660731058842</v>
+        <v>67.48359488418018</v>
       </c>
       <c r="G71" t="n">
-        <v>24.43106909584137</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="H71" t="n">
-        <v>-5.674461785252948</v>
+        <v>-6.810046233552484</v>
       </c>
     </row>
     <row r="72">
@@ -5155,22 +5899,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>29.48333333333333</v>
+        <v>32.85</v>
       </c>
       <c r="D73" t="n">
-        <v>21.38333333333333</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="E73" t="n">
-        <v>8.100000000000001</v>
+        <v>6.516666666666673</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4298392460953699</v>
+        <v>0.5585488688475958</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1090721560237224</v>
+        <v>0.3414581795449143</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3207670900716475</v>
+        <v>0.2170906893026815</v>
       </c>
     </row>
     <row r="74">
@@ -5185,22 +5929,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.1105833333333333</v>
+        <v>9.886899999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.8894166666666667</v>
+        <v>-0.1297666666666704</v>
       </c>
       <c r="F74" t="n">
-        <v>0.05848286929177889</v>
+        <v>1.34706205013313</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8778317268481433</v>
+        <v>0.5256426997626461</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.8193488575563643</v>
+        <v>0.821419350370484</v>
       </c>
     </row>
     <row r="75">
@@ -5215,22 +5959,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5.266666666666667</v>
+        <v>7.933333333333334</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>14.48333333333333</v>
       </c>
       <c r="E75" t="n">
-        <v>5.266666666666667</v>
+        <v>-6.549999999999997</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3548232692194973</v>
+        <v>1.158895058334316</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1.222282616060936</v>
       </c>
       <c r="H75" t="n">
-        <v>0.3548232692194973</v>
+        <v>-0.06338755772661986</v>
       </c>
     </row>
     <row r="76">
@@ -5245,22 +5989,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>45.48333333333333</v>
+        <v>61.06666666666667</v>
       </c>
       <c r="D76" t="n">
-        <v>39.18333333333333</v>
+        <v>52.6</v>
       </c>
       <c r="E76" t="n">
-        <v>6.299999999999997</v>
+        <v>8.466666666666669</v>
       </c>
       <c r="F76" t="n">
-        <v>37.10906168770636</v>
+        <v>45.26405758465819</v>
       </c>
       <c r="G76" t="n">
-        <v>28.21320161975721</v>
+        <v>30.18268163700424</v>
       </c>
       <c r="H76" t="n">
-        <v>8.895860067949148</v>
+        <v>15.08137594765395</v>
       </c>
     </row>
     <row r="77">
@@ -5275,22 +6019,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>28.73333333333333</v>
+        <v>46.8</v>
       </c>
       <c r="D77" t="n">
-        <v>30.46666666666667</v>
+        <v>42.23333333333333</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.733333333333338</v>
+        <v>4.56666666666667</v>
       </c>
       <c r="F77" t="n">
-        <v>23.38414305111067</v>
+        <v>33.58518042089994</v>
       </c>
       <c r="G77" t="n">
-        <v>20.93633895165053</v>
+        <v>24.88861936987865</v>
       </c>
       <c r="H77" t="n">
-        <v>2.447804099460139</v>
+        <v>8.696561051021288</v>
       </c>
     </row>
     <row r="78">
@@ -5305,28 +6049,28 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>78.57570000000001</v>
+        <v>122.55</v>
       </c>
       <c r="D78" t="n">
-        <v>102.9250666666667</v>
+        <v>146.0833333333333</v>
       </c>
       <c r="E78" t="n">
-        <v>-24.34936666666668</v>
+        <v>-23.53333333333329</v>
       </c>
       <c r="F78" t="n">
-        <v>62.65629452354004</v>
+        <v>71.45918358296625</v>
       </c>
       <c r="G78" t="n">
-        <v>73.84383061342899</v>
+        <v>96.90275067420166</v>
       </c>
       <c r="H78" t="n">
-        <v>-11.18753608988895</v>
+        <v>-25.44356709123541</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PAIR_029</t>
+          <t>PAIR_027</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5356,7 +6100,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PAIR_029</t>
+          <t>PAIR_027</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5365,28 +6109,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>31.03333333333333</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>7.316666666666663</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>0.1769495542483206</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>0.0599505119882755</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PAIR_029</t>
+          <t>PAIR_027</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5395,28 +6139,28 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.5</v>
+        <v>10.96666666666667</v>
       </c>
       <c r="D81" t="n">
-        <v>0.1666666666666667</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="E81" t="n">
-        <v>1.333333333333333</v>
+        <v>6.533333333333337</v>
       </c>
       <c r="F81" t="n">
-        <v>0.05476919925384444</v>
+        <v>0.2864416579452221</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1405968038522134</v>
+        <v>0.9568808181881884</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.08582760459836897</v>
+        <v>-0.6704391602429662</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PAIR_029</t>
+          <t>PAIR_027</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5425,28 +6169,28 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.1666666666666667</v>
+        <v>2.933333333333333</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1666666666666667</v>
+        <v>-6.616666666666667</v>
       </c>
       <c r="F82" t="n">
-        <v>0.01267380267082223</v>
+        <v>0.2376855524103972</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>0.7490888898619357</v>
       </c>
       <c r="H82" t="n">
-        <v>0.01267380267082223</v>
+        <v>-0.5114033374515384</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PAIR_029</t>
+          <t>PAIR_027</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5455,28 +6199,28 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>15.90041666666667</v>
+        <v>62.68333333333333</v>
       </c>
       <c r="D83" t="n">
-        <v>10.95</v>
+        <v>50.65</v>
       </c>
       <c r="E83" t="n">
-        <v>4.950416666666671</v>
+        <v>12.03333333333333</v>
       </c>
       <c r="F83" t="n">
-        <v>13.25093473030296</v>
+        <v>48.51346678639188</v>
       </c>
       <c r="G83" t="n">
-        <v>8.219513195924231</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="H83" t="n">
-        <v>5.03142153437873</v>
+        <v>11.8012573414757</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PAIR_029</t>
+          <t>PAIR_027</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5485,28 +6229,28 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>12.59196666666667</v>
+        <v>46.94098333333333</v>
       </c>
       <c r="D84" t="n">
-        <v>8.85</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="E84" t="n">
-        <v>3.74196666666667</v>
+        <v>12.70765</v>
       </c>
       <c r="F84" t="n">
-        <v>9.785494672181397</v>
+        <v>34.6641680603018</v>
       </c>
       <c r="G84" t="n">
-        <v>6.487184809227589</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="H84" t="n">
-        <v>3.298309862953808</v>
+        <v>9.623640706066016</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PAIR_029</t>
+          <t>PAIR_027</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5515,22 +6259,862 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>12.7</v>
+        <v>65.35115</v>
       </c>
       <c r="D85" t="n">
-        <v>25.52363333333333</v>
+        <v>109.3</v>
       </c>
       <c r="E85" t="n">
-        <v>-12.82363333333333</v>
+        <v>-43.94884999999999</v>
       </c>
       <c r="F85" t="n">
-        <v>11.33570954018739</v>
+        <v>54.41575298877198</v>
       </c>
       <c r="G85" t="n">
-        <v>19.4794811912292</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="H85" t="n">
-        <v>-8.143771651041812</v>
+        <v>-19.87788812896068</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>29.48333333333333</v>
+      </c>
+      <c r="D87" t="n">
+        <v>21.38333333333333</v>
+      </c>
+      <c r="E87" t="n">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.4298392460953699</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.1090721560237224</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.3207670900716475</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0.1105833333333333</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-0.8894166666666667</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.05848286929177889</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.8778317268481433</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0.8193488575563643</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5.266666666666667</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.3548232692194973</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.3548232692194973</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>45.48333333333333</v>
+      </c>
+      <c r="D90" t="n">
+        <v>39.18333333333333</v>
+      </c>
+      <c r="E90" t="n">
+        <v>6.299999999999997</v>
+      </c>
+      <c r="F90" t="n">
+        <v>37.10906168770636</v>
+      </c>
+      <c r="G90" t="n">
+        <v>28.21320161975721</v>
+      </c>
+      <c r="H90" t="n">
+        <v>8.895860067949148</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>28.73333333333333</v>
+      </c>
+      <c r="D91" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-1.733333333333338</v>
+      </c>
+      <c r="F91" t="n">
+        <v>23.38414305111067</v>
+      </c>
+      <c r="G91" t="n">
+        <v>20.93633895165053</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.447804099460139</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>78.57570000000001</v>
+      </c>
+      <c r="D92" t="n">
+        <v>102.9250666666667</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-24.34936666666668</v>
+      </c>
+      <c r="F92" t="n">
+        <v>62.65629452354004</v>
+      </c>
+      <c r="G92" t="n">
+        <v>73.84383061342899</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-11.18753608988895</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>34.49703333333333</v>
+      </c>
+      <c r="D94" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="E94" t="n">
+        <v>8.163699999999999</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.5388878376354634</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.321273432549297</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.2176144050861664</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>3.683333333333333</v>
+      </c>
+      <c r="D95" t="n">
+        <v>10.01666666666667</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-6.333333333333336</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.5589577464659954</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.5256426997626461</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.03331504670334928</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="D96" t="n">
+        <v>14.48333333333333</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-7.133333333333331</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.6798850900122044</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.222282616060936</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-0.5423975260487315</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="D97" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E97" t="n">
+        <v>4.949999999999996</v>
+      </c>
+      <c r="F97" t="n">
+        <v>44.66597796080278</v>
+      </c>
+      <c r="G97" t="n">
+        <v>30.18268163700424</v>
+      </c>
+      <c r="H97" t="n">
+        <v>14.48329632379854</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>37.36666666666667</v>
+      </c>
+      <c r="D98" t="n">
+        <v>42.23333333333333</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-4.86666666666666</v>
+      </c>
+      <c r="F98" t="n">
+        <v>29.46179071078489</v>
+      </c>
+      <c r="G98" t="n">
+        <v>24.87772879183483</v>
+      </c>
+      <c r="H98" t="n">
+        <v>4.584061918950059</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="D99" t="n">
+        <v>146.0833333333333</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-33.68333333333328</v>
+      </c>
+      <c r="F99" t="n">
+        <v>76.48918013454522</v>
+      </c>
+      <c r="G99" t="n">
+        <v>96.90275067420166</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-20.41357053965643</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="D101" t="n">
+        <v>21.38333333333333</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-0.7333333333333307</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.07050792832939867</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.1090721560237224</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-0.03856422769432373</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>8.668333333333333</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>7.668333333333333</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.1448841273528465</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.8591442430348036</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-0.7142601156819571</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2.983333333333333</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2.983333333333333</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.259210764002235</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.259210764002235</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>56.78333333333333</v>
+      </c>
+      <c r="D104" t="n">
+        <v>39.18333333333333</v>
+      </c>
+      <c r="E104" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F104" t="n">
+        <v>43.79816613863036</v>
+      </c>
+      <c r="G104" t="n">
+        <v>28.21320161975721</v>
+      </c>
+      <c r="H104" t="n">
+        <v>15.58496451887315</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>43.36978333333333</v>
+      </c>
+      <c r="D105" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="E105" t="n">
+        <v>12.90311666666666</v>
+      </c>
+      <c r="F105" t="n">
+        <v>31.32770704550355</v>
+      </c>
+      <c r="G105" t="n">
+        <v>20.93633895165053</v>
+      </c>
+      <c r="H105" t="n">
+        <v>10.39136809385302</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>62.48333333333333</v>
+      </c>
+      <c r="D106" t="n">
+        <v>102.9250666666667</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-40.44173333333337</v>
+      </c>
+      <c r="F106" t="n">
+        <v>50.14119329857225</v>
+      </c>
+      <c r="G106" t="n">
+        <v>73.86462303382228</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-23.72342973525004</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="E108" t="n">
+        <v>8.766666666666673</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.1862366457606098</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.3661259006707928</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-0.179889254910183</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>15.11666666666667</v>
+      </c>
+      <c r="D109" t="n">
+        <v>10.01666666666667</v>
+      </c>
+      <c r="E109" t="n">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.297561165968511</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.5256426997626461</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-0.2280815337941351</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D110" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-7.550000000000001</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.420813179835343</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1.205289753214544</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.215523426620799</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>73.30295</v>
+      </c>
+      <c r="D111" t="n">
+        <v>51.26666666666667</v>
+      </c>
+      <c r="E111" t="n">
+        <v>22.03628333333332</v>
+      </c>
+      <c r="F111" t="n">
+        <v>52.75602854613859</v>
+      </c>
+      <c r="G111" t="n">
+        <v>29.79516392210389</v>
+      </c>
+      <c r="H111" t="n">
+        <v>22.9608646240347</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>55.48333333333333</v>
+      </c>
+      <c r="D112" t="n">
+        <v>41.04036666666666</v>
+      </c>
+      <c r="E112" t="n">
+        <v>14.44296666666667</v>
+      </c>
+      <c r="F112" t="n">
+        <v>37.95304168068559</v>
+      </c>
+      <c r="G112" t="n">
+        <v>24.54736075797758</v>
+      </c>
+      <c r="H112" t="n">
+        <v>13.40568092270801</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="D113" t="n">
+        <v>143.5333333333333</v>
+      </c>
+      <c r="E113" t="n">
+        <v>-65.18333333333331</v>
+      </c>
+      <c r="F113" t="n">
+        <v>58.94647555785541</v>
+      </c>
+      <c r="G113" t="n">
+        <v>95.66972227177216</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-36.72324671391675</v>
       </c>
     </row>
   </sheetData>
@@ -5616,22 +7200,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.35542777777778</v>
+        <v>31.87381458333333</v>
       </c>
       <c r="C3" t="n">
-        <v>23.7375</v>
+        <v>27.10416666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3820722222222197</v>
+        <v>4.769647916666671</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.116666666666669</v>
+        <v>5.851100000000008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4540391302755695</v>
+        <v>0.5644195118806448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1648193484804601</v>
+        <v>0.2495247218077365</v>
       </c>
     </row>
     <row r="4">
@@ -5641,22 +7225,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.108022222222222</v>
+        <v>7.526913541666667</v>
       </c>
       <c r="C4" t="n">
-        <v>2.005555555555556</v>
+        <v>4.987500000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>2.102466666666667</v>
+        <v>2.539413541666666</v>
       </c>
       <c r="E4" t="n">
-        <v>1.866666666666667</v>
+        <v>2.965766666666666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4372425731550805</v>
+        <v>0.6011274398080357</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9630628543989909</v>
+        <v>1.099210315827433</v>
       </c>
     </row>
     <row r="5">
@@ -5666,22 +7250,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.126388888888889</v>
+        <v>4.414583333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6805555555555555</v>
+        <v>6.391666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>1.445833333333333</v>
+        <v>-1.977083333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>1.141666666666667</v>
+        <v>-2.116666666666665</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2070590675464231</v>
+        <v>0.526604699159373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1010682087844285</v>
+        <v>0.564257164677092</v>
       </c>
     </row>
     <row r="6">
@@ -5691,22 +7275,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.86130833333333</v>
+        <v>55.76060104166667</v>
       </c>
       <c r="C6" t="n">
-        <v>33.52703611111111</v>
+        <v>46.13333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>6.334272222222221</v>
+        <v>9.627267708333333</v>
       </c>
       <c r="E6" t="n">
-        <v>5.699999999999999</v>
+        <v>9.266666666666669</v>
       </c>
       <c r="F6" t="n">
-        <v>32.41967390213737</v>
+        <v>43.43879043057893</v>
       </c>
       <c r="G6" t="n">
-        <v>24.78398503013909</v>
+        <v>31.40229810440942</v>
       </c>
     </row>
     <row r="7">
@@ -5716,22 +7300,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.578475</v>
+        <v>40.35697395833333</v>
       </c>
       <c r="C7" t="n">
-        <v>24.88762777777778</v>
+        <v>35.37543958333333</v>
       </c>
       <c r="D7" t="n">
-        <v>2.690847222222221</v>
+        <v>4.981534375000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.952391666666667</v>
+        <v>3.544058333333332</v>
       </c>
       <c r="F7" t="n">
-        <v>22.30432976083099</v>
+        <v>30.5522800808539</v>
       </c>
       <c r="G7" t="n">
-        <v>18.3625096913239</v>
+        <v>23.96706999963798</v>
       </c>
     </row>
     <row r="8">
@@ -5741,22 +7325,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60.53088194444445</v>
+        <v>88.88078541666667</v>
       </c>
       <c r="C8" t="n">
-        <v>79.64764444444445</v>
+        <v>119.7276875</v>
       </c>
       <c r="D8" t="n">
-        <v>-19.1167625</v>
+        <v>-30.84690208333332</v>
       </c>
       <c r="E8" t="n">
-        <v>-19.43650000000001</v>
+        <v>-26.7298583333333</v>
       </c>
       <c r="F8" t="n">
-        <v>50.11146258883712</v>
+        <v>64.04509703004493</v>
       </c>
       <c r="G8" t="n">
-        <v>61.52519910560456</v>
+        <v>82.49848587220218</v>
       </c>
     </row>
   </sheetData>
@@ -5827,28 +7411,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>23.4375</v>
       </c>
       <c r="D2" t="n">
-        <v>6.310164959664828</v>
+        <v>10.9298902098786</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>12.75</v>
+        <v>14.75</v>
       </c>
       <c r="G2" t="n">
-        <v>17.5</v>
+        <v>23.5</v>
       </c>
       <c r="H2" t="n">
-        <v>22.25</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -5858,28 +7442,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>157.5605041666666</v>
+        <v>228.813671875</v>
       </c>
       <c r="D3" t="n">
-        <v>63.51246875352096</v>
+        <v>30.53546080169482</v>
       </c>
       <c r="E3" t="n">
-        <v>42.85905</v>
+        <v>187.65295</v>
       </c>
       <c r="F3" t="n">
-        <v>122.4984583333333</v>
+        <v>204.2863458333333</v>
       </c>
       <c r="G3" t="n">
-        <v>177.72085</v>
+        <v>223.0465666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>192.1781833333333</v>
+        <v>251.9949208333333</v>
       </c>
       <c r="I3" t="n">
-        <v>241.37365</v>
+        <v>281.0869</v>
       </c>
     </row>
     <row r="4">
@@ -5889,28 +7473,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>164.4859194444444</v>
+        <v>239.71979375</v>
       </c>
       <c r="D4" t="n">
-        <v>63.61954168314264</v>
+        <v>35.18653664162109</v>
       </c>
       <c r="E4" t="n">
-        <v>45.4903</v>
+        <v>194.5326</v>
       </c>
       <c r="F4" t="n">
-        <v>132.4014583333333</v>
+        <v>222.6521</v>
       </c>
       <c r="G4" t="n">
-        <v>188.0674333333333</v>
+        <v>236.74955</v>
       </c>
       <c r="H4" t="n">
-        <v>194.9584</v>
+        <v>253.4812291666666</v>
       </c>
       <c r="I4" t="n">
-        <v>241.6157666666667</v>
+        <v>291.75</v>
       </c>
     </row>
     <row r="5">
@@ -5920,28 +7504,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>105.9338070227826</v>
+        <v>139.7283191923258</v>
       </c>
       <c r="D5" t="n">
-        <v>40.40489612793964</v>
+        <v>10.54792972478002</v>
       </c>
       <c r="E5" t="n">
-        <v>34.43958194459641</v>
+        <v>123.9185956857711</v>
       </c>
       <c r="F5" t="n">
-        <v>91.10066101390349</v>
+        <v>133.9534407176154</v>
       </c>
       <c r="G5" t="n">
-        <v>125.2479584141173</v>
+        <v>140.9863960288643</v>
       </c>
       <c r="H5" t="n">
-        <v>126.6527331064285</v>
+        <v>147.0891107453261</v>
       </c>
       <c r="I5" t="n">
-        <v>143.715559613142</v>
+        <v>153.3729275658394</v>
       </c>
     </row>
     <row r="6">
@@ -5951,28 +7535,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>105.9006442387314</v>
+        <v>139.7808461785618</v>
       </c>
       <c r="D6" t="n">
-        <v>40.4330773390023</v>
+        <v>11.07350625294342</v>
       </c>
       <c r="E6" t="n">
-        <v>34.32677600023323</v>
+        <v>123.8871365945718</v>
       </c>
       <c r="F6" t="n">
-        <v>91.07230562496387</v>
+        <v>134.3976050014682</v>
       </c>
       <c r="G6" t="n">
-        <v>125.2153507636665</v>
+        <v>140.8071242126524</v>
       </c>
       <c r="H6" t="n">
-        <v>126.6150454629195</v>
+        <v>145.8919041671806</v>
       </c>
       <c r="I6" t="n">
-        <v>143.7061031155876</v>
+        <v>154.0634351764531</v>
       </c>
     </row>
     <row r="7">
@@ -5982,28 +7566,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>48.86374072263951</v>
+        <v>44.21878827932048</v>
       </c>
       <c r="D7" t="n">
-        <v>2.899695284002024</v>
+        <v>3.191198183218266</v>
       </c>
       <c r="E7" t="n">
-        <v>44.63387255371435</v>
+        <v>38.12896580160068</v>
       </c>
       <c r="F7" t="n">
-        <v>46.73579660317592</v>
+        <v>42.09634841917746</v>
       </c>
       <c r="G7" t="n">
-        <v>49.01559974623297</v>
+        <v>44.66837195828366</v>
       </c>
       <c r="H7" t="n">
-        <v>50.30914857103133</v>
+        <v>46.34188955635086</v>
       </c>
       <c r="I7" t="n">
-        <v>54.3571101011709</v>
+        <v>50.21471932710446</v>
       </c>
     </row>
     <row r="8">
@@ -6013,28 +7597,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>45.82610889459411</v>
+        <v>40.36257099103018</v>
       </c>
       <c r="D8" t="n">
-        <v>2.839526058759173</v>
+        <v>2.734669043377738</v>
       </c>
       <c r="E8" t="n">
-        <v>42.3414520907443</v>
+        <v>35.98718333260023</v>
       </c>
       <c r="F8" t="n">
-        <v>42.76194774901236</v>
+        <v>39.28836913914864</v>
       </c>
       <c r="G8" t="n">
-        <v>46.26135246838679</v>
+        <v>41.24107055934269</v>
       </c>
       <c r="H8" t="n">
-        <v>47.14259190214048</v>
+        <v>42.44684814238604</v>
       </c>
       <c r="I8" t="n">
-        <v>49.97551623726486</v>
+        <v>42.83521220753777</v>
       </c>
     </row>
     <row r="9">
@@ -6044,28 +7628,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.92541527777778</v>
+        <v>-10.906121875</v>
       </c>
       <c r="D9" t="n">
-        <v>9.312623735961781</v>
+        <v>16.80095894513357</v>
       </c>
       <c r="E9" t="n">
-        <v>-21.72221666666661</v>
+        <v>-41.8922833333333</v>
       </c>
       <c r="F9" t="n">
-        <v>-11.77305833333336</v>
+        <v>-19.52719166666672</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.808650000000007</v>
+        <v>-9.747641666666638</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.033966666666672</v>
+        <v>-0.0003583333333025962</v>
       </c>
       <c r="I9" t="n">
-        <v>10.79548333333329</v>
+        <v>12.60326666666668</v>
       </c>
     </row>
     <row r="10">
@@ -6075,28 +7659,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03316278405113652</v>
+        <v>-0.05252698623603003</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03865735028547934</v>
+        <v>1.103851916888581</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02777565792860059</v>
+        <v>-1.708298465594794</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01250386333216724</v>
+        <v>-0.8157222095728045</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03495488288770332</v>
+        <v>-0.02555802253225181</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05173398277212016</v>
+        <v>0.6024322395896498</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1128059443631813</v>
+        <v>1.779324947279889</v>
       </c>
     </row>
     <row r="11">
@@ -6106,28 +7690,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>3.037631828045396</v>
+        <v>3.856217288290297</v>
       </c>
       <c r="D11" t="n">
-        <v>2.378424959438441</v>
+        <v>3.061049332477627</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.131977056173582</v>
+        <v>-1.378770120982431</v>
       </c>
       <c r="F11" t="n">
-        <v>2.040161086421307</v>
+        <v>2.259451933661909</v>
       </c>
       <c r="G11" t="n">
-        <v>2.637076553689372</v>
+        <v>3.575534153004355</v>
       </c>
       <c r="H11" t="n">
-        <v>4.24744956661368</v>
+        <v>6.13666132618391</v>
       </c>
       <c r="I11" t="n">
-        <v>7.828931555422386</v>
+        <v>9.918352188895554</v>
       </c>
     </row>
     <row r="12">
@@ -6137,25 +7721,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>1.720394444444447</v>
+        <v>7.309061458333337</v>
       </c>
       <c r="D12" t="n">
-        <v>7.805548885961061</v>
+        <v>6.341177739782109</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.033333333333328</v>
+        <v>-3.30296666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.98139166666667</v>
+        <v>4.554004166666665</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1261</v>
+        <v>6.510691666666665</v>
       </c>
       <c r="H12" t="n">
-        <v>4.56782083333333</v>
+        <v>10.62665000000001</v>
       </c>
       <c r="I12" t="n">
         <v>20.1</v>
@@ -6168,7 +7752,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -6199,7 +7783,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -6230,7 +7814,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -6261,7 +7845,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -6292,7 +7876,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -6323,7 +7907,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -6354,25 +7938,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>23.35542777777778</v>
+        <v>31.87381458333333</v>
       </c>
       <c r="D19" t="n">
-        <v>11.68160588698122</v>
+        <v>6.463226233116077</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>20.65</v>
       </c>
       <c r="F19" t="n">
-        <v>15.025</v>
+        <v>26.52971666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>22.66518333333334</v>
+        <v>32.85</v>
       </c>
       <c r="H19" t="n">
-        <v>30.73675833333333</v>
+        <v>35.1</v>
       </c>
       <c r="I19" t="n">
         <v>43.48553333333334</v>
@@ -6385,25 +7969,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>23.7375</v>
+        <v>27.10416666666666</v>
       </c>
       <c r="D20" t="n">
-        <v>9.288553629890583</v>
+        <v>6.16214699236845</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="F20" t="n">
-        <v>21.38333333333333</v>
+        <v>23.13333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>23.71666666666667</v>
+        <v>25.025</v>
       </c>
       <c r="H20" t="n">
-        <v>24.90833333333333</v>
+        <v>28.99583333333333</v>
       </c>
       <c r="I20" t="n">
         <v>36.98333333333333</v>
@@ -6416,28 +8000,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.3820722222222199</v>
+        <v>4.769647916666671</v>
       </c>
       <c r="D21" t="n">
-        <v>7.253678846338935</v>
+        <v>5.995488920513105</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.43333333333333</v>
+        <v>-4.133333333333326</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.249999999999995</v>
+        <v>-0.08555833333332963</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.116666666666669</v>
+        <v>5.851100000000008</v>
       </c>
       <c r="H21" t="n">
-        <v>3.614700000000004</v>
+        <v>8.115925000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>14.11666666666667</v>
+        <v>17.15220000000001</v>
       </c>
     </row>
     <row r="22">
@@ -6447,28 +8031,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4540391302755695</v>
+        <v>0.5644195118806448</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4551076812848201</v>
+        <v>0.4201931989563314</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.07050792832939867</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1157287174312111</v>
+        <v>0.1910370954748811</v>
       </c>
       <c r="G22" t="n">
-        <v>0.237667416199215</v>
+        <v>0.4772706075156733</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6404864702470684</v>
+        <v>0.6681519042693467</v>
       </c>
       <c r="I22" t="n">
-        <v>1.332101358262426</v>
+        <v>1.349334550099321</v>
       </c>
     </row>
     <row r="23">
@@ -6478,25 +8062,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1648193484804601</v>
+        <v>0.2495247218077365</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1338902696497004</v>
+        <v>0.1455987772824271</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1090721560237224</v>
+        <v>0.1150173207009644</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1169990422600451</v>
+        <v>0.2191362374046711</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1412448261875258</v>
+        <v>0.3831139352551934</v>
       </c>
       <c r="I23" t="n">
         <v>0.4340780390083954</v>
@@ -6509,25 +8093,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2892197817951094</v>
+        <v>0.3148947900729082</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4051610710295109</v>
+        <v>0.4183933223436378</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.001270324828833991</v>
+        <v>-0.2478413932477856</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01216706729151878</v>
+        <v>0.07171628033676369</v>
       </c>
       <c r="G24" t="n">
-        <v>0.08161089379787785</v>
+        <v>0.217352547194424</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4605658096223742</v>
+        <v>0.4628460687109381</v>
       </c>
       <c r="I24" t="n">
         <v>1.04740651736726</v>
@@ -6540,28 +8124,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>4.108022222222221</v>
+        <v>7.526913541666667</v>
       </c>
       <c r="D25" t="n">
-        <v>3.074306972100168</v>
+        <v>4.126876690267687</v>
       </c>
       <c r="E25" t="n">
         <v>0.1105833333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2875</v>
+        <v>3.683333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>3.866666666666666</v>
+        <v>8.109166666666667</v>
       </c>
       <c r="H25" t="n">
-        <v>7.125</v>
+        <v>9.948795833333332</v>
       </c>
       <c r="I25" t="n">
-        <v>8.303566666666667</v>
+        <v>15.11666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -6571,28 +8155,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>2.005555555555556</v>
+        <v>4.987500000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>1.396194925273785</v>
+        <v>3.336162688101629</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9583333333333334</v>
+        <v>3.575</v>
       </c>
       <c r="G26" t="n">
-        <v>2.016666666666667</v>
+        <v>4.466666666666667</v>
       </c>
       <c r="H26" t="n">
-        <v>2.404166666666666</v>
+        <v>5.879166666666667</v>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>10.01666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -6602,28 +8186,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>2.102466666666667</v>
+        <v>2.539413541666666</v>
       </c>
       <c r="D27" t="n">
-        <v>2.7894855719308</v>
+        <v>4.011688132242893</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.733333333333333</v>
+        <v>-6.333333333333336</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5077541666666667</v>
+        <v>-0.5375000000000015</v>
       </c>
       <c r="G27" t="n">
-        <v>1.866666666666667</v>
+        <v>2.965766666666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3.896725</v>
+        <v>5.771695833333331</v>
       </c>
       <c r="I27" t="n">
-        <v>5.983333333333333</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -6633,28 +8217,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4372425731550805</v>
+        <v>0.6011274398080357</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3141645208409238</v>
+        <v>0.3599666824810086</v>
       </c>
       <c r="E28" t="n">
-        <v>0.05476919925384444</v>
+        <v>0.05848286929177889</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1431061962259462</v>
+        <v>0.2947812889626888</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4228171143884355</v>
+        <v>0.5589577464659954</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6077446621402327</v>
+        <v>0.7796449153073984</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9162394150268994</v>
+        <v>1.34706205013313</v>
       </c>
     </row>
     <row r="29">
@@ -6664,28 +8248,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>0.963062854398991</v>
+        <v>1.099210315827433</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6078524808614333</v>
+        <v>0.5865676333274932</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1405968038522134</v>
+        <v>0.5256426997626461</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7385314946598888</v>
+        <v>0.7603016824402435</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8009322770576942</v>
+        <v>0.9173562725181659</v>
       </c>
       <c r="H29" t="n">
-        <v>1.043954113888049</v>
+        <v>1.245044772777633</v>
       </c>
       <c r="I29" t="n">
-        <v>2.038955216433607</v>
+        <v>2.057469342854302</v>
       </c>
     </row>
     <row r="30">
@@ -6695,28 +8279,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5258202812439103</v>
+        <v>-0.4980828760193974</v>
       </c>
       <c r="D30" t="n">
-        <v>0.490535634773234</v>
+        <v>0.6689980760302886</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.478344573186251</v>
+        <v>-1.745040723473472</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7585361400627934</v>
+        <v>-0.8468741900496339</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4200465327436579</v>
+        <v>-0.3831074355161765</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.160983070741723</v>
+        <v>-0.162732388669764</v>
       </c>
       <c r="I30" t="n">
-        <v>0.152896204244287</v>
+        <v>0.821419350370484</v>
       </c>
     </row>
     <row r="31">
@@ -6726,28 +8310,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>2.126388888888889</v>
+        <v>4.414583333333333</v>
       </c>
       <c r="D31" t="n">
-        <v>2.003626237012058</v>
+        <v>2.340709571112208</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7541666666666667</v>
+        <v>2.970833333333333</v>
       </c>
       <c r="G31" t="n">
-        <v>1.516666666666667</v>
+        <v>4.683333333333334</v>
       </c>
       <c r="H31" t="n">
-        <v>4.1</v>
+        <v>5.9125</v>
       </c>
       <c r="I31" t="n">
-        <v>5.266666666666667</v>
+        <v>7.933333333333334</v>
       </c>
     </row>
     <row r="32">
@@ -6757,28 +8341,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6805555555555557</v>
+        <v>6.391666666666667</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7362144962657177</v>
+        <v>6.061536292246563</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1.2125</v>
       </c>
       <c r="G32" t="n">
-        <v>0.35</v>
+        <v>5.583333333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1.379166666666667</v>
+        <v>10.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1.633333333333333</v>
+        <v>14.48333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -6788,28 +8372,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>1.445833333333333</v>
+        <v>-1.977083333333333</v>
       </c>
       <c r="D33" t="n">
-        <v>2.072000996938257</v>
+        <v>6.04415810698415</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.3</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1375</v>
+        <v>-7.475000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>1.141666666666667</v>
+        <v>-2.116666666666665</v>
       </c>
       <c r="H33" t="n">
-        <v>2.774999999999999</v>
+        <v>3.754166666666666</v>
       </c>
       <c r="I33" t="n">
-        <v>5.266666666666667</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="34">
@@ -6819,28 +8403,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2070590675464231</v>
+        <v>0.526604699159373</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1769576551298824</v>
+        <v>0.3775980459308475</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03854599653962131</v>
+        <v>0.2945883098741507</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2439990530184602</v>
+        <v>0.4218755708347697</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3548232692194973</v>
+        <v>0.6944619225491653</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4394311316082445</v>
+        <v>1.420813179835343</v>
       </c>
     </row>
     <row r="35">
@@ -6850,28 +8434,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1010682087844285</v>
+        <v>0.564257164677092</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1033606700185287</v>
+        <v>0.4828887594085048</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.2025840414773588</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1079082363261396</v>
+        <v>0.5096004725825404</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1671868728596241</v>
+        <v>0.8879539792788322</v>
       </c>
       <c r="I35" t="n">
-        <v>0.270112055303145</v>
+        <v>1.222282616060936</v>
       </c>
     </row>
     <row r="36">
@@ -6881,28 +8465,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1059908587619946</v>
+        <v>-0.03765246551771895</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1770802291797526</v>
+        <v>0.4751371865608629</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.1200168116970698</v>
+        <v>-0.7793029599160757</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.01747170707841823</v>
+        <v>-0.5191518846008367</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1093561594627353</v>
+        <v>0.06048999188899828</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1807903831171076</v>
+        <v>0.2831138903065505</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4394311316082445</v>
+        <v>0.7381924201600477</v>
       </c>
     </row>
     <row r="37">
@@ -6912,28 +8496,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>39.86130833333333</v>
+        <v>55.76060104166666</v>
       </c>
       <c r="D37" t="n">
-        <v>13.59300145338558</v>
+        <v>7.764997817987504</v>
       </c>
       <c r="E37" t="n">
-        <v>15.90041666666667</v>
+        <v>44.28333333333333</v>
       </c>
       <c r="F37" t="n">
-        <v>35.80202916666666</v>
+        <v>50.43333333333334</v>
       </c>
       <c r="G37" t="n">
-        <v>44.47499999999999</v>
+        <v>54.8</v>
       </c>
       <c r="H37" t="n">
-        <v>48.8422625</v>
+        <v>58.47916666666667</v>
       </c>
       <c r="I37" t="n">
-        <v>54.2</v>
+        <v>73.30295</v>
       </c>
     </row>
     <row r="38">
@@ -6943,28 +8527,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>33.52703611111111</v>
+        <v>46.13333333333333</v>
       </c>
       <c r="D38" t="n">
-        <v>13.30569191288631</v>
+        <v>5.6649539895487</v>
       </c>
       <c r="E38" t="n">
-        <v>10.95</v>
+        <v>39.18333333333333</v>
       </c>
       <c r="F38" t="n">
-        <v>27.53082083333334</v>
+        <v>41.62083333333333</v>
       </c>
       <c r="G38" t="n">
-        <v>39.18333333333333</v>
+        <v>46.54166666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>43.09583333333333</v>
+        <v>50.80416666666667</v>
       </c>
       <c r="I38" t="n">
-        <v>45.25706666666667</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="39">
@@ -6974,28 +8558,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>6.334272222222221</v>
+        <v>9.627267708333333</v>
       </c>
       <c r="D39" t="n">
-        <v>4.838909668720534</v>
+        <v>7.680862808547037</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.516666666666673</v>
+        <v>-1.916666666666671</v>
       </c>
       <c r="F39" t="n">
-        <v>3.542695833333334</v>
+        <v>4.529166666666661</v>
       </c>
       <c r="G39" t="n">
-        <v>5.699999999999999</v>
+        <v>9.266666666666669</v>
       </c>
       <c r="H39" t="n">
-        <v>9.991666666666664</v>
+        <v>12.82083333333333</v>
       </c>
       <c r="I39" t="n">
-        <v>14.66666666666667</v>
+        <v>25.58333333333334</v>
       </c>
     </row>
     <row r="40">
@@ -7005,28 +8589,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>32.41967390213737</v>
+        <v>43.43879043057893</v>
       </c>
       <c r="D40" t="n">
-        <v>11.34780285089765</v>
+        <v>4.581434755984813</v>
       </c>
       <c r="E40" t="n">
-        <v>13.25093473030296</v>
+        <v>35.86032280254005</v>
       </c>
       <c r="F40" t="n">
-        <v>28.62761126951432</v>
+        <v>41.42907426632136</v>
       </c>
       <c r="G40" t="n">
-        <v>37.56539248437645</v>
+        <v>43.43970446455401</v>
       </c>
       <c r="H40" t="n">
-        <v>38.84667170775526</v>
+        <v>44.81549786676663</v>
       </c>
       <c r="I40" t="n">
-        <v>43.32090510862054</v>
+        <v>52.75602854613859</v>
       </c>
     </row>
     <row r="41">
@@ -7036,28 +8620,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>24.78398503013909</v>
+        <v>31.40229810440941</v>
       </c>
       <c r="D41" t="n">
-        <v>9.840344264033039</v>
+        <v>3.297422918466016</v>
       </c>
       <c r="E41" t="n">
-        <v>8.219513195924231</v>
+        <v>28.21320161975721</v>
       </c>
       <c r="F41" t="n">
-        <v>20.74917642741186</v>
+        <v>29.39967334651722</v>
       </c>
       <c r="G41" t="n">
-        <v>28.21320161975721</v>
+        <v>30.39033039084468</v>
       </c>
       <c r="H41" t="n">
-        <v>31.41945980666805</v>
+        <v>32.12653671974289</v>
       </c>
       <c r="I41" t="n">
-        <v>33.99612977910262</v>
+        <v>36.71220944491618</v>
       </c>
     </row>
     <row r="42">
@@ -7067,28 +8651,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>7.635688871998281</v>
+        <v>12.03649232616951</v>
       </c>
       <c r="D42" t="n">
-        <v>3.503372695304343</v>
+        <v>5.27305771373222</v>
       </c>
       <c r="E42" t="n">
-        <v>3.143077965718549</v>
+        <v>4.672003240300299</v>
       </c>
       <c r="F42" t="n">
-        <v>4.836398547825786</v>
+        <v>8.58367534665757</v>
       </c>
       <c r="G42" t="n">
-        <v>6.908560339477647</v>
+        <v>12.44650152805402</v>
       </c>
       <c r="H42" t="n">
-        <v>10.13369459670166</v>
+        <v>14.63281622976239</v>
       </c>
       <c r="I42" t="n">
-        <v>12.72292596393542</v>
+        <v>22.9608646240347</v>
       </c>
     </row>
     <row r="43">
@@ -7098,28 +8682,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>27.578475</v>
+        <v>40.35697395833333</v>
       </c>
       <c r="D43" t="n">
-        <v>9.11011503386081</v>
+        <v>7.314544879388697</v>
       </c>
       <c r="E43" t="n">
-        <v>12.59196666666667</v>
+        <v>28.73333333333333</v>
       </c>
       <c r="F43" t="n">
-        <v>24.39166666666667</v>
+        <v>35.93207083333334</v>
       </c>
       <c r="G43" t="n">
-        <v>30.09166666666667</v>
+        <v>39.12032499999999</v>
       </c>
       <c r="H43" t="n">
-        <v>34.97954583333333</v>
+        <v>44.8429875</v>
       </c>
       <c r="I43" t="n">
-        <v>37.47145</v>
+        <v>55.48333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -7129,28 +8713,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>24.88762777777778</v>
+        <v>35.37543958333333</v>
       </c>
       <c r="D44" t="n">
-        <v>9.827656922894072</v>
+        <v>4.250870727696614</v>
       </c>
       <c r="E44" t="n">
-        <v>8.85</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="F44" t="n">
-        <v>19.77083333333333</v>
+        <v>33.29166666666666</v>
       </c>
       <c r="G44" t="n">
-        <v>29.80076666666667</v>
+        <v>34.59166666666667</v>
       </c>
       <c r="H44" t="n">
-        <v>30.46666666666667</v>
+        <v>36.47259166666667</v>
       </c>
       <c r="I44" t="n">
-        <v>34.95</v>
+        <v>42.23333333333333</v>
       </c>
     </row>
     <row r="45">
@@ -7160,28 +8744,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>2.690847222222221</v>
+        <v>4.981534375000001</v>
       </c>
       <c r="D45" t="n">
-        <v>3.063571806779568</v>
+        <v>6.603370379495241</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.817433333333341</v>
+        <v>-4.86666666666666</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5570708333333325</v>
+        <v>-0.3996208333333335</v>
       </c>
       <c r="G45" t="n">
-        <v>2.952391666666667</v>
+        <v>3.544058333333332</v>
       </c>
       <c r="H45" t="n">
-        <v>4.570833333333336</v>
+        <v>10.1074</v>
       </c>
       <c r="I45" t="n">
-        <v>8.116666666666664</v>
+        <v>16.30311666666666</v>
       </c>
     </row>
     <row r="46">
@@ -7191,28 +8775,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>22.304329760831</v>
+        <v>30.5522800808539</v>
       </c>
       <c r="D46" t="n">
-        <v>7.514777192979785</v>
+        <v>3.943462124662598</v>
       </c>
       <c r="E46" t="n">
-        <v>9.785494672181397</v>
+        <v>23.38414305111067</v>
       </c>
       <c r="F46" t="n">
-        <v>20.16559877346592</v>
+        <v>28.33380549039565</v>
       </c>
       <c r="G46" t="n">
-        <v>24.68244075501737</v>
+        <v>30.19495230381258</v>
       </c>
       <c r="H46" t="n">
-        <v>27.71428406489335</v>
+        <v>32.72550309522931</v>
       </c>
       <c r="I46" t="n">
-        <v>29.77502417243205</v>
+        <v>37.95304168068559</v>
       </c>
     </row>
     <row r="47">
@@ -7222,25 +8806,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>18.3625096913239</v>
+        <v>23.96706999963799</v>
       </c>
       <c r="D47" t="n">
-        <v>7.081807764687227</v>
+        <v>1.813165353335539</v>
       </c>
       <c r="E47" t="n">
-        <v>6.487184809227589</v>
+        <v>20.93633895165053</v>
       </c>
       <c r="F47" t="n">
-        <v>14.63188385588557</v>
+        <v>23.64460530639582</v>
       </c>
       <c r="G47" t="n">
-        <v>21.25827276473802</v>
+        <v>24.96457336205722</v>
       </c>
       <c r="H47" t="n">
-        <v>22.75816129262547</v>
+        <v>25.05878157997349</v>
       </c>
       <c r="I47" t="n">
         <v>25.11354425718663</v>
@@ -7253,28 +8837,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>3.941820069507091</v>
+        <v>6.585210081215918</v>
       </c>
       <c r="D48" t="n">
-        <v>1.497254478426466</v>
+        <v>3.399567351470305</v>
       </c>
       <c r="E48" t="n">
-        <v>1.68209258184686</v>
+        <v>1.94779369920721</v>
       </c>
       <c r="F48" t="n">
-        <v>3.040154533247305</v>
+        <v>4.0770717730799</v>
       </c>
       <c r="G48" t="n">
-        <v>3.677038605439447</v>
+        <v>5.976155501719504</v>
       </c>
       <c r="H48" t="n">
-        <v>4.726578003870491</v>
+        <v>8.92833096478247</v>
       </c>
       <c r="I48" t="n">
-        <v>6.754582642415528</v>
+        <v>13.40568092270801</v>
       </c>
     </row>
     <row r="49">
@@ -7284,28 +8868,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>60.53088194444445</v>
+        <v>88.88078541666667</v>
       </c>
       <c r="D49" t="n">
-        <v>28.59511051675933</v>
+        <v>18.07371703787726</v>
       </c>
       <c r="E49" t="n">
-        <v>12.7</v>
+        <v>62.48333333333333</v>
       </c>
       <c r="F49" t="n">
-        <v>43.95835</v>
+        <v>78.51927500000001</v>
       </c>
       <c r="G49" t="n">
-        <v>68.91265833333333</v>
+        <v>84.75194166666667</v>
       </c>
       <c r="H49" t="n">
-        <v>79.84941250000001</v>
+        <v>97.75833333333333</v>
       </c>
       <c r="I49" t="n">
-        <v>96.26666666666667</v>
+        <v>122.55</v>
       </c>
     </row>
     <row r="50">
@@ -7315,28 +8899,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>79.64764444444444</v>
+        <v>119.7276875</v>
       </c>
       <c r="D50" t="n">
-        <v>33.59113836774855</v>
+        <v>16.80795215899911</v>
       </c>
       <c r="E50" t="n">
-        <v>25.52363333333333</v>
+        <v>102.4992666666667</v>
       </c>
       <c r="F50" t="n">
-        <v>62.79980416666667</v>
+        <v>107.7062666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>86.35833333333333</v>
+        <v>115.2162166666666</v>
       </c>
       <c r="H50" t="n">
-        <v>102.9250666666667</v>
+        <v>127.4169708333333</v>
       </c>
       <c r="I50" t="n">
-        <v>121.1324333333333</v>
+        <v>146.0833333333333</v>
       </c>
     </row>
     <row r="51">
@@ -7346,28 +8930,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-19.1167625</v>
+        <v>-30.84690208333332</v>
       </c>
       <c r="D51" t="n">
-        <v>5.75775712942291</v>
+        <v>13.29993969438273</v>
       </c>
       <c r="E51" t="n">
-        <v>-30.66576666666663</v>
+        <v>-65.18333333333331</v>
       </c>
       <c r="F51" t="n">
-        <v>-21.80149166666667</v>
+        <v>-35.3729333333333</v>
       </c>
       <c r="G51" t="n">
-        <v>-19.43650000000001</v>
+        <v>-26.7298583333333</v>
       </c>
       <c r="H51" t="n">
-        <v>-15.48544583333334</v>
+        <v>-22.46362916666664</v>
       </c>
       <c r="I51" t="n">
-        <v>-10.54255</v>
+        <v>-16.66593333333337</v>
       </c>
     </row>
     <row r="52">
@@ -7377,28 +8961,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>50.11146258883713</v>
+        <v>64.04509703004493</v>
       </c>
       <c r="D52" t="n">
-        <v>21.15799851885745</v>
+        <v>7.380038739302593</v>
       </c>
       <c r="E52" t="n">
-        <v>11.33570954018739</v>
+        <v>50.14119329857225</v>
       </c>
       <c r="F52" t="n">
-        <v>41.58888660282788</v>
+        <v>58.46663729483393</v>
       </c>
       <c r="G52" t="n">
-        <v>59.21108225956439</v>
+        <v>64.18509869731309</v>
       </c>
       <c r="H52" t="n">
-        <v>62.81947283368351</v>
+        <v>69.1255056240754</v>
       </c>
       <c r="I52" t="n">
-        <v>70.67319504829489</v>
+        <v>76.48918013454522</v>
       </c>
     </row>
     <row r="53">
@@ -7408,28 +8992,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>61.52519910560456</v>
+        <v>82.49848587220217</v>
       </c>
       <c r="D53" t="n">
-        <v>23.65136279469588</v>
+        <v>9.650058847631758</v>
       </c>
       <c r="E53" t="n">
-        <v>19.4794811912292</v>
+        <v>73.75129891257018</v>
       </c>
       <c r="F53" t="n">
-        <v>55.71169973801662</v>
+        <v>74.18638659675507</v>
       </c>
       <c r="G53" t="n">
-        <v>68.9193035201415</v>
+        <v>79.771818145174</v>
       </c>
       <c r="H53" t="n">
-        <v>74.62394432365585</v>
+        <v>87.94661150054677</v>
       </c>
       <c r="I53" t="n">
-        <v>85.25143440297076</v>
+        <v>96.90275067420166</v>
       </c>
     </row>
     <row r="54">
@@ -7439,28 +9023,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-11.41373651676744</v>
+        <v>-18.45338884215725</v>
       </c>
       <c r="D54" t="n">
-        <v>4.267113267731867</v>
+        <v>7.801709298199603</v>
       </c>
       <c r="E54" t="n">
-        <v>-18.35192888346221</v>
+        <v>-36.72324671391675</v>
       </c>
       <c r="F54" t="n">
-        <v>-14.9210977035496</v>
+        <v>-22.98143194654011</v>
       </c>
       <c r="G54" t="n">
-        <v>-10.71848677550264</v>
+        <v>-17.86258285667467</v>
       </c>
       <c r="H54" t="n">
-        <v>-8.508422789250375</v>
+        <v>-12.42301621390142</v>
       </c>
       <c r="I54" t="n">
-        <v>-5.553265360657583</v>
+        <v>-6.810046233552484</v>
       </c>
     </row>
   </sheetData>
@@ -7516,19 +9100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>157.5605041666667</v>
+        <v>228.813671875</v>
       </c>
       <c r="D2" t="n">
-        <v>164.4859194444444</v>
+        <v>239.71979375</v>
       </c>
       <c r="E2" t="n">
-        <v>-6.92541527777778</v>
+        <v>-10.906121875</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.808650000000007</v>
+        <v>-9.747641666666638</v>
       </c>
     </row>
   </sheetData>
